--- a/upload/orgao2023.xlsx
+++ b/upload/orgao2023.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m11483500\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m11483500\Documents\transparencia-mg\portal_despesa_empenho\upload\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11130"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="8430"/>
   </bookViews>
   <sheets>
     <sheet name="orgao" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="81">
   <si>
     <t>Ano de Exercício</t>
   </si>
@@ -30,6 +30,12 @@
     <t>Unidade Orçamentária - Nome</t>
   </si>
   <si>
+    <t>Valor Despesa Empenhada</t>
+  </si>
+  <si>
+    <t>Valor Despesa Liquidada</t>
+  </si>
+  <si>
     <t>Valor Pago Financeiro</t>
   </si>
   <si>
@@ -204,6 +210,12 @@
     <t>AGENCIA DE DESENVOLVIMENTO DA REGIAO METROPOLITANA DO VALE DO ACO</t>
   </si>
   <si>
+    <t>EMPRESA DE ASSISTENCIA TECNICA E EXTENSAO RURAL DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>EMPRESA DE PESQUISA AGROPECUARIA DE MINAS GERAIS</t>
+  </si>
+  <si>
     <t>FUNDO PARA A INFANCIA E A ADOLESCENCIA</t>
   </si>
   <si>
@@ -241,9 +253,6 @@
   </si>
   <si>
     <t>FUNDO ESTADUAL DOS DIREITOS DO IDOSO</t>
-  </si>
-  <si>
-    <t>FUNDO DE PAGAMENTO DE PARCERIAS PUBLICO - PRIVADAS DE MINAS GERAIS</t>
   </si>
   <si>
     <t>FUNDO ESTADUAL DE SEGURANCA PUBLICA DE MINAS GERAIS</t>
@@ -272,7 +281,6 @@
       <sz val="9"/>
       <color rgb="FF333333"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -625,20 +633,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G73"/>
+  <dimension ref="A1:I74"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
     <col min="2" max="2" width="13.28515625" customWidth="1"/>
     <col min="3" max="3" width="33.7109375" customWidth="1"/>
-    <col min="4" max="4" width="17.28515625" customWidth="1"/>
-    <col min="5" max="5" width="21.28515625" customWidth="1"/>
-    <col min="6" max="6" width="25.140625" customWidth="1"/>
-    <col min="7" max="7" width="16.42578125" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="4" max="6" width="17.28515625" customWidth="1"/>
+    <col min="7" max="7" width="21.28515625" customWidth="1"/>
+    <col min="8" max="8" width="25.140625" customWidth="1"/>
+    <col min="9" max="9" width="16.42578125" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="1" customFormat="1" ht="45.4" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" s="1" customFormat="1" ht="45.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -651,17 +659,23 @@
       <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="4">
         <v>2023</v>
       </c>
@@ -669,22 +683,28 @@
         <v>1071</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D2" s="6">
+        <v>46143197.210000001</v>
+      </c>
+      <c r="E2" s="6">
+        <v>35398463.109999999</v>
+      </c>
+      <c r="F2" s="6">
         <v>34050957.789999999</v>
       </c>
-      <c r="E2" s="6">
+      <c r="G2" s="6">
         <v>211337.1</v>
       </c>
-      <c r="F2" s="6">
+      <c r="H2" s="6">
         <v>3943260.33</v>
       </c>
-      <c r="G2" s="7">
+      <c r="I2" s="7">
         <v>4154597.43</v>
       </c>
     </row>
-    <row r="3" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="4">
         <v>2023</v>
       </c>
@@ -692,22 +712,28 @@
         <v>1081</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D3" s="6">
+        <v>1163303001.26</v>
+      </c>
+      <c r="E3" s="6">
+        <v>1160222383.6400001</v>
+      </c>
+      <c r="F3" s="6">
         <v>1001681057.22</v>
       </c>
-      <c r="E3" s="6">
+      <c r="G3" s="6">
         <v>29087656.780000001</v>
       </c>
-      <c r="F3" s="6">
+      <c r="H3" s="6">
         <v>3000988.94</v>
       </c>
-      <c r="G3" s="7">
+      <c r="I3" s="7">
         <v>32088645.719999999</v>
       </c>
     </row>
-    <row r="4" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="4">
         <v>2023</v>
       </c>
@@ -715,22 +741,28 @@
         <v>1101</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D4" s="6">
+        <v>14788301.67</v>
+      </c>
+      <c r="E4" s="6">
+        <v>14630579.609999999</v>
+      </c>
+      <c r="F4" s="6">
         <v>14490566</v>
       </c>
-      <c r="E4" s="6">
+      <c r="G4" s="6">
         <v>0</v>
       </c>
-      <c r="F4" s="6">
+      <c r="H4" s="6">
         <v>94372.77</v>
       </c>
-      <c r="G4" s="7">
+      <c r="I4" s="7">
         <v>94372.77</v>
       </c>
     </row>
-    <row r="5" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="4">
         <v>2023</v>
       </c>
@@ -738,22 +770,28 @@
         <v>1191</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D5" s="6">
+        <v>1549832807.1400001</v>
+      </c>
+      <c r="E5" s="6">
+        <v>1487682339.6400001</v>
+      </c>
+      <c r="F5" s="6">
         <v>1468478278.25</v>
       </c>
-      <c r="E5" s="6">
+      <c r="G5" s="6">
         <v>5469083</v>
       </c>
-      <c r="F5" s="6">
+      <c r="H5" s="6">
         <v>34680028.149999999</v>
       </c>
-      <c r="G5" s="7">
+      <c r="I5" s="7">
         <v>40149111.149999999</v>
       </c>
     </row>
-    <row r="6" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="4">
         <v>2023</v>
       </c>
@@ -761,22 +799,28 @@
         <v>1221</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D6" s="6">
+        <v>71019848</v>
+      </c>
+      <c r="E6" s="6">
+        <v>49587285.619999997</v>
+      </c>
+      <c r="F6" s="6">
         <v>28903226.949999999</v>
       </c>
-      <c r="E6" s="6">
+      <c r="G6" s="6">
         <v>468159.26</v>
       </c>
-      <c r="F6" s="6">
+      <c r="H6" s="6">
         <v>8730755.2300000004</v>
       </c>
-      <c r="G6" s="7">
+      <c r="I6" s="7">
         <v>9198914.4900000002</v>
       </c>
     </row>
-    <row r="7" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="4">
         <v>2023</v>
       </c>
@@ -784,22 +828,28 @@
         <v>1231</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D7" s="6">
+        <v>157335344.34</v>
+      </c>
+      <c r="E7" s="6">
+        <v>140995120.88999999</v>
+      </c>
+      <c r="F7" s="6">
         <v>122957383.2</v>
       </c>
-      <c r="E7" s="6">
+      <c r="G7" s="6">
         <v>7823519.9500000002</v>
       </c>
-      <c r="F7" s="6">
+      <c r="H7" s="6">
         <v>3775929.39</v>
       </c>
-      <c r="G7" s="7">
+      <c r="I7" s="7">
         <v>11599449.34</v>
       </c>
     </row>
-    <row r="8" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="4">
         <v>2023</v>
       </c>
@@ -807,22 +857,28 @@
         <v>1251</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D8" s="6">
+        <v>13028366670.83</v>
+      </c>
+      <c r="E8" s="6">
+        <v>12841769394.379999</v>
+      </c>
+      <c r="F8" s="6">
         <v>12810307610.08</v>
       </c>
-      <c r="E8" s="6">
+      <c r="G8" s="6">
         <v>36489178.109999999</v>
       </c>
-      <c r="F8" s="6">
+      <c r="H8" s="6">
         <v>226080162.78999999</v>
       </c>
-      <c r="G8" s="7">
+      <c r="I8" s="7">
         <v>262569340.90000001</v>
       </c>
     </row>
-    <row r="9" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="4">
         <v>2023</v>
       </c>
@@ -830,22 +886,28 @@
         <v>1261</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D9" s="6">
+        <v>17449007243.25</v>
+      </c>
+      <c r="E9" s="6">
+        <v>16913371691.709999</v>
+      </c>
+      <c r="F9" s="6">
         <v>16658293209.57</v>
       </c>
-      <c r="E9" s="6">
+      <c r="G9" s="6">
         <v>258732199.34</v>
       </c>
-      <c r="F9" s="6">
+      <c r="H9" s="6">
         <v>420280749.50999999</v>
       </c>
-      <c r="G9" s="7">
+      <c r="I9" s="7">
         <v>679012948.85000002</v>
       </c>
     </row>
-    <row r="10" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="4">
         <v>2023</v>
       </c>
@@ -853,22 +915,28 @@
         <v>1271</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D10" s="6">
+        <v>89313458.840000004</v>
+      </c>
+      <c r="E10" s="6">
+        <v>86513089.769999996</v>
+      </c>
+      <c r="F10" s="6">
         <v>82380637.920000002</v>
       </c>
-      <c r="E10" s="6">
+      <c r="G10" s="6">
         <v>1333330.75</v>
       </c>
-      <c r="F10" s="6">
+      <c r="H10" s="6">
         <v>896505.38</v>
       </c>
-      <c r="G10" s="7">
+      <c r="I10" s="7">
         <v>2229836.13</v>
       </c>
     </row>
-    <row r="11" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="4">
         <v>2023</v>
       </c>
@@ -876,22 +944,28 @@
         <v>1301</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D11" s="6">
+        <v>1210413287.27</v>
+      </c>
+      <c r="E11" s="6">
+        <v>948715257.75</v>
+      </c>
+      <c r="F11" s="6">
         <v>820248138.33000004</v>
       </c>
-      <c r="E11" s="6">
+      <c r="G11" s="6">
         <v>79551005.900000006</v>
       </c>
-      <c r="F11" s="6">
+      <c r="H11" s="6">
         <v>47275927.880000003</v>
       </c>
-      <c r="G11" s="7">
+      <c r="I11" s="7">
         <v>126826933.78</v>
       </c>
     </row>
-    <row r="12" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="4">
         <v>2023</v>
       </c>
@@ -899,22 +973,28 @@
         <v>1371</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D12" s="6">
+        <v>208856328.28</v>
+      </c>
+      <c r="E12" s="6">
+        <v>202130317.06</v>
+      </c>
+      <c r="F12" s="6">
         <v>183745409.62</v>
       </c>
-      <c r="E12" s="6">
+      <c r="G12" s="6">
         <v>3452019.16</v>
       </c>
-      <c r="F12" s="6">
+      <c r="H12" s="6">
         <v>2453491.44</v>
       </c>
-      <c r="G12" s="7">
+      <c r="I12" s="7">
         <v>5905510.5999999996</v>
       </c>
     </row>
-    <row r="13" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
         <v>2023</v>
       </c>
@@ -922,22 +1002,28 @@
         <v>1401</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D13" s="6">
+        <v>1564505806.6600001</v>
+      </c>
+      <c r="E13" s="6">
+        <v>1472603650.0899999</v>
+      </c>
+      <c r="F13" s="6">
         <v>1466343606.9100001</v>
       </c>
-      <c r="E13" s="6">
+      <c r="G13" s="6">
         <v>7744878.5300000003</v>
       </c>
-      <c r="F13" s="6">
+      <c r="H13" s="6">
         <v>30546600.960000001</v>
       </c>
-      <c r="G13" s="7">
+      <c r="I13" s="7">
         <v>38291479.490000002</v>
       </c>
     </row>
-    <row r="14" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="4">
         <v>2023</v>
       </c>
@@ -945,22 +1031,28 @@
         <v>1451</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D14" s="6">
+        <v>3781312622.1199999</v>
+      </c>
+      <c r="E14" s="6">
+        <v>3625298484.23</v>
+      </c>
+      <c r="F14" s="6">
         <v>3596218710.3899999</v>
       </c>
-      <c r="E14" s="6">
+      <c r="G14" s="6">
         <v>19811807.260000002</v>
       </c>
-      <c r="F14" s="6">
+      <c r="H14" s="6">
         <v>100572066.62</v>
       </c>
-      <c r="G14" s="7">
+      <c r="I14" s="7">
         <v>120383873.88</v>
       </c>
     </row>
-    <row r="15" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="4">
         <v>2023</v>
       </c>
@@ -968,22 +1060,28 @@
         <v>1481</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D15" s="6">
+        <v>278200685.86000001</v>
+      </c>
+      <c r="E15" s="6">
+        <v>258721057.71000001</v>
+      </c>
+      <c r="F15" s="6">
         <v>187380767.61000001</v>
       </c>
-      <c r="E15" s="6">
+      <c r="G15" s="6">
         <v>13128483.789999999</v>
       </c>
-      <c r="F15" s="6">
+      <c r="H15" s="6">
         <v>14858520.74</v>
       </c>
-      <c r="G15" s="7">
+      <c r="I15" s="7">
         <v>27987004.530000001</v>
       </c>
     </row>
-    <row r="16" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="4">
         <v>2023</v>
       </c>
@@ -991,22 +1089,28 @@
         <v>1491</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D16" s="6">
+        <v>614122774.96000004</v>
+      </c>
+      <c r="E16" s="6">
+        <v>581433110.22000003</v>
+      </c>
+      <c r="F16" s="6">
         <v>577033471.5</v>
       </c>
-      <c r="E16" s="6">
+      <c r="G16" s="6">
         <v>8649196.5299999993</v>
       </c>
-      <c r="F16" s="6">
+      <c r="H16" s="6">
         <v>27927671.890000001</v>
       </c>
-      <c r="G16" s="7">
+      <c r="I16" s="7">
         <v>36576868.420000002</v>
       </c>
     </row>
-    <row r="17" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="4">
         <v>2023</v>
       </c>
@@ -1014,22 +1118,28 @@
         <v>1501</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D17" s="6">
+        <v>558633697.67999995</v>
+      </c>
+      <c r="E17" s="6">
+        <v>499616023.56999999</v>
+      </c>
+      <c r="F17" s="6">
         <v>469179324</v>
       </c>
-      <c r="E17" s="6">
+      <c r="G17" s="6">
         <v>3809874.58</v>
       </c>
-      <c r="F17" s="6">
+      <c r="H17" s="6">
         <v>18299317.449999999</v>
       </c>
-      <c r="G17" s="7">
+      <c r="I17" s="7">
         <v>22109192.030000001</v>
       </c>
     </row>
-    <row r="18" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="4">
         <v>2023</v>
       </c>
@@ -1037,22 +1147,28 @@
         <v>1511</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D18" s="6">
+        <v>3065566676.29</v>
+      </c>
+      <c r="E18" s="6">
+        <v>2994754625.6799998</v>
+      </c>
+      <c r="F18" s="6">
         <v>2978077582.9699998</v>
       </c>
-      <c r="E18" s="6">
+      <c r="G18" s="6">
         <v>12864618.77</v>
       </c>
-      <c r="F18" s="6">
+      <c r="H18" s="6">
         <v>79194935.120000005</v>
       </c>
-      <c r="G18" s="7">
+      <c r="I18" s="7">
         <v>92059553.890000001</v>
       </c>
     </row>
-    <row r="19" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="4">
         <v>2023</v>
       </c>
@@ -1060,22 +1176,28 @@
         <v>1521</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D19" s="6">
+        <v>60102963.539999999</v>
+      </c>
+      <c r="E19" s="6">
+        <v>59580613.899999999</v>
+      </c>
+      <c r="F19" s="6">
         <v>59323104.460000001</v>
       </c>
-      <c r="E19" s="6">
+      <c r="G19" s="6">
         <v>77665.009999999995</v>
       </c>
-      <c r="F19" s="6">
+      <c r="H19" s="6">
         <v>197493.6</v>
       </c>
-      <c r="G19" s="7">
+      <c r="I19" s="7">
         <v>275158.61</v>
       </c>
     </row>
-    <row r="20" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="4">
         <v>2023</v>
       </c>
@@ -1083,22 +1205,28 @@
         <v>1541</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D20" s="6">
+        <v>19938984.920000002</v>
+      </c>
+      <c r="E20" s="6">
+        <v>19458800.920000002</v>
+      </c>
+      <c r="F20" s="6">
         <v>19168057.699999999</v>
       </c>
-      <c r="E20" s="6">
+      <c r="G20" s="6">
         <v>8211.5</v>
       </c>
-      <c r="F20" s="6">
+      <c r="H20" s="6">
         <v>116097.68</v>
       </c>
-      <c r="G20" s="7">
+      <c r="I20" s="7">
         <v>124309.18</v>
       </c>
     </row>
-    <row r="21" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="4">
         <v>2023</v>
       </c>
@@ -1106,22 +1234,28 @@
         <v>1631</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D21" s="6">
+        <v>64901564.210000001</v>
+      </c>
+      <c r="E21" s="6">
+        <v>59419458.57</v>
+      </c>
+      <c r="F21" s="6">
         <v>57509982.390000001</v>
       </c>
-      <c r="E21" s="6">
+      <c r="G21" s="6">
         <v>777.25</v>
       </c>
-      <c r="F21" s="6">
+      <c r="H21" s="6">
         <v>22162487.859999999</v>
       </c>
-      <c r="G21" s="7">
+      <c r="I21" s="7">
         <v>22163265.109999999</v>
       </c>
     </row>
-    <row r="22" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="4">
         <v>2023</v>
       </c>
@@ -1129,16 +1263,22 @@
         <v>1711</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D22" s="6">
+        <v>85247066.049999997</v>
+      </c>
+      <c r="E22" s="6">
+        <v>32467458.600000001</v>
+      </c>
+      <c r="F22" s="6">
         <v>31192326.84</v>
       </c>
-      <c r="E22" s="6"/>
-      <c r="F22" s="6"/>
-      <c r="G22" s="7"/>
-    </row>
-    <row r="23" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G22" s="6"/>
+      <c r="H22" s="6"/>
+      <c r="I22" s="7"/>
+    </row>
+    <row r="23" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="4">
         <v>2023</v>
       </c>
@@ -1146,16 +1286,22 @@
         <v>1721</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D23" s="6">
+        <v>5572590.71</v>
+      </c>
+      <c r="E23" s="6">
+        <v>5270468.4000000004</v>
+      </c>
+      <c r="F23" s="6">
         <v>4983565.3</v>
       </c>
-      <c r="E23" s="6"/>
-      <c r="F23" s="6"/>
-      <c r="G23" s="7"/>
-    </row>
-    <row r="24" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G23" s="6"/>
+      <c r="H23" s="6"/>
+      <c r="I23" s="7"/>
+    </row>
+    <row r="24" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
         <v>2023</v>
       </c>
@@ -1163,22 +1309,28 @@
         <v>1911</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D24" s="6">
+        <v>854860168.33000004</v>
+      </c>
+      <c r="E24" s="6">
+        <v>765439410.10000002</v>
+      </c>
+      <c r="F24" s="6">
         <v>765416129.62</v>
       </c>
-      <c r="E24" s="6">
+      <c r="G24" s="6">
         <v>25335200.02</v>
       </c>
-      <c r="F24" s="6">
+      <c r="H24" s="6">
         <v>609616599.35000002</v>
       </c>
-      <c r="G24" s="7">
+      <c r="I24" s="7">
         <v>634951799.37</v>
       </c>
     </row>
-    <row r="25" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="4">
         <v>2023</v>
       </c>
@@ -1186,22 +1338,28 @@
         <v>1915</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D25" s="6">
+        <v>508647503.19999999</v>
+      </c>
+      <c r="E25" s="6">
         <v>3647503.2</v>
       </c>
-      <c r="E25" s="6">
+      <c r="F25" s="6">
+        <v>3647503.2</v>
+      </c>
+      <c r="G25" s="6">
         <v>0</v>
       </c>
-      <c r="F25" s="6">
+      <c r="H25" s="6">
         <v>75202844.75</v>
       </c>
-      <c r="G25" s="7">
+      <c r="I25" s="7">
         <v>75202844.75</v>
       </c>
     </row>
-    <row r="26" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="4">
         <v>2023</v>
       </c>
@@ -1209,22 +1367,28 @@
         <v>1916</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D26" s="6">
+        <v>4151422885</v>
+      </c>
+      <c r="E26" s="6">
+        <v>4151422885</v>
+      </c>
+      <c r="F26" s="6">
         <v>3992987258.5500002</v>
       </c>
-      <c r="E26" s="6">
+      <c r="G26" s="6">
         <v>316225142.58999997</v>
       </c>
-      <c r="F26" s="6">
+      <c r="H26" s="6">
         <v>123029711.28</v>
       </c>
-      <c r="G26" s="7">
+      <c r="I26" s="7">
         <v>439254853.87</v>
       </c>
     </row>
-    <row r="27" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="4">
         <v>2023</v>
       </c>
@@ -1232,22 +1396,28 @@
         <v>1941</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D27" s="6">
+        <v>196770413.59</v>
+      </c>
+      <c r="E27" s="6">
+        <v>196243687.53999999</v>
+      </c>
+      <c r="F27" s="6">
         <v>196240526.91999999</v>
       </c>
-      <c r="E27" s="6">
+      <c r="G27" s="6">
         <v>0</v>
       </c>
-      <c r="F27" s="6">
+      <c r="H27" s="6">
         <v>0</v>
       </c>
-      <c r="G27" s="7">
+      <c r="I27" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="4">
         <v>2023</v>
       </c>
@@ -1255,22 +1425,28 @@
         <v>2011</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D28" s="6">
+        <v>1616992072.96</v>
+      </c>
+      <c r="E28" s="6">
+        <v>1414919735.8</v>
+      </c>
+      <c r="F28" s="6">
         <v>1379497007.6900001</v>
       </c>
-      <c r="E28" s="6">
+      <c r="G28" s="6">
         <v>2730465.24</v>
       </c>
-      <c r="F28" s="6">
+      <c r="H28" s="6">
         <v>139505498.50999999</v>
       </c>
-      <c r="G28" s="7">
+      <c r="I28" s="7">
         <v>142235963.75</v>
       </c>
     </row>
-    <row r="29" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="4">
         <v>2023</v>
       </c>
@@ -1278,22 +1454,28 @@
         <v>2041</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D29" s="6">
+        <v>3423162.82</v>
+      </c>
+      <c r="E29" s="6">
+        <v>3283189.87</v>
+      </c>
+      <c r="F29" s="6">
         <v>3280441.52</v>
       </c>
-      <c r="E29" s="6">
+      <c r="G29" s="6">
         <v>0</v>
       </c>
-      <c r="F29" s="6">
+      <c r="H29" s="6">
         <v>6507</v>
       </c>
-      <c r="G29" s="7">
+      <c r="I29" s="7">
         <v>6507</v>
       </c>
     </row>
-    <row r="30" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="4">
         <v>2023</v>
       </c>
@@ -1301,22 +1483,28 @@
         <v>2061</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D30" s="6">
+        <v>65473442.710000001</v>
+      </c>
+      <c r="E30" s="6">
+        <v>62245323.490000002</v>
+      </c>
+      <c r="F30" s="6">
         <v>61139568.079999998</v>
       </c>
-      <c r="E30" s="6">
+      <c r="G30" s="6">
         <v>658090.65</v>
       </c>
-      <c r="F30" s="6">
+      <c r="H30" s="6">
         <v>5690027.0800000001</v>
       </c>
-      <c r="G30" s="7">
+      <c r="I30" s="7">
         <v>6348117.7300000004</v>
       </c>
     </row>
-    <row r="31" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="4">
         <v>2023</v>
       </c>
@@ -1324,22 +1512,28 @@
         <v>2071</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D31" s="6">
+        <v>475574938.69</v>
+      </c>
+      <c r="E31" s="6">
+        <v>469867300.36000001</v>
+      </c>
+      <c r="F31" s="6">
         <v>420221524.10000002</v>
       </c>
-      <c r="E31" s="6">
+      <c r="G31" s="6">
         <v>12738999.810000001</v>
       </c>
-      <c r="F31" s="6">
+      <c r="H31" s="6">
         <v>7274018.25</v>
       </c>
-      <c r="G31" s="7">
+      <c r="I31" s="7">
         <v>20013018.059999999</v>
       </c>
     </row>
-    <row r="32" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="4">
         <v>2023</v>
       </c>
@@ -1347,22 +1541,28 @@
         <v>2091</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D32" s="6">
+        <v>43259418.770000003</v>
+      </c>
+      <c r="E32" s="6">
+        <v>38126464.75</v>
+      </c>
+      <c r="F32" s="6">
         <v>37435935.060000002</v>
       </c>
-      <c r="E32" s="6">
+      <c r="G32" s="6">
         <v>95.91</v>
       </c>
-      <c r="F32" s="6">
+      <c r="H32" s="6">
         <v>37153.49</v>
       </c>
-      <c r="G32" s="7">
+      <c r="I32" s="7">
         <v>37249.4</v>
       </c>
     </row>
-    <row r="33" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="4">
         <v>2023</v>
       </c>
@@ -1370,22 +1570,28 @@
         <v>2101</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D33" s="6">
+        <v>206253448.78999999</v>
+      </c>
+      <c r="E33" s="6">
+        <v>201049210.28</v>
+      </c>
+      <c r="F33" s="6">
         <v>193758815.18000001</v>
       </c>
-      <c r="E33" s="6">
+      <c r="G33" s="6">
         <v>2044943.53</v>
       </c>
-      <c r="F33" s="6">
+      <c r="H33" s="6">
         <v>3790350.53</v>
       </c>
-      <c r="G33" s="7">
+      <c r="I33" s="7">
         <v>5835294.0599999996</v>
       </c>
     </row>
-    <row r="34" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="4">
         <v>2023</v>
       </c>
@@ -1393,22 +1599,28 @@
         <v>2121</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D34" s="6">
+        <v>2900878606.77</v>
+      </c>
+      <c r="E34" s="6">
+        <v>2876463795.1700001</v>
+      </c>
+      <c r="F34" s="6">
         <v>2327341436.54</v>
       </c>
-      <c r="E34" s="6">
+      <c r="G34" s="6">
         <v>102308456.42</v>
       </c>
-      <c r="F34" s="6">
+      <c r="H34" s="6">
         <v>33347552.640000001</v>
       </c>
-      <c r="G34" s="7">
+      <c r="I34" s="7">
         <v>135656009.06</v>
       </c>
     </row>
-    <row r="35" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
         <v>2023</v>
       </c>
@@ -1416,22 +1628,28 @@
         <v>2151</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D35" s="6">
+        <v>64938007.380000003</v>
+      </c>
+      <c r="E35" s="6">
+        <v>62329642.07</v>
+      </c>
+      <c r="F35" s="6">
         <v>61232129.219999999</v>
       </c>
-      <c r="E35" s="6">
+      <c r="G35" s="6">
         <v>0</v>
       </c>
-      <c r="F35" s="6">
+      <c r="H35" s="6">
         <v>2676209.5</v>
       </c>
-      <c r="G35" s="7">
+      <c r="I35" s="7">
         <v>2676209.5</v>
       </c>
     </row>
-    <row r="36" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="4">
         <v>2023</v>
       </c>
@@ -1439,22 +1657,28 @@
         <v>2161</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D36" s="6">
+        <v>10901641.689999999</v>
+      </c>
+      <c r="E36" s="6">
+        <v>10318773.130000001</v>
+      </c>
+      <c r="F36" s="6">
         <v>8998548.6099999994</v>
       </c>
-      <c r="E36" s="6">
+      <c r="G36" s="6">
         <v>121569.88</v>
       </c>
-      <c r="F36" s="6">
+      <c r="H36" s="6">
         <v>1346214.75</v>
       </c>
-      <c r="G36" s="7">
+      <c r="I36" s="7">
         <v>1467784.63</v>
       </c>
     </row>
-    <row r="37" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="4">
         <v>2023</v>
       </c>
@@ -1462,22 +1686,28 @@
         <v>2171</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D37" s="6">
+        <v>4750004.05</v>
+      </c>
+      <c r="E37" s="6">
+        <v>4345485.2699999996</v>
+      </c>
+      <c r="F37" s="6">
         <v>4163957.5</v>
       </c>
-      <c r="E37" s="6">
+      <c r="G37" s="6">
         <v>27405.599999999999</v>
       </c>
-      <c r="F37" s="6">
+      <c r="H37" s="6">
         <v>295215.94</v>
       </c>
-      <c r="G37" s="7">
+      <c r="I37" s="7">
         <v>322621.53999999998</v>
       </c>
     </row>
-    <row r="38" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="4">
         <v>2023</v>
       </c>
@@ -1485,22 +1715,28 @@
         <v>2181</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D38" s="6">
+        <v>49628398.030000001</v>
+      </c>
+      <c r="E38" s="6">
+        <v>47405823.659999996</v>
+      </c>
+      <c r="F38" s="6">
         <v>46275247.850000001</v>
       </c>
-      <c r="E38" s="6">
+      <c r="G38" s="6">
         <v>253.4</v>
       </c>
-      <c r="F38" s="6">
+      <c r="H38" s="6">
         <v>878433.07</v>
       </c>
-      <c r="G38" s="7">
+      <c r="I38" s="7">
         <v>878686.47</v>
       </c>
     </row>
-    <row r="39" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="4">
         <v>2023</v>
       </c>
@@ -1508,22 +1744,28 @@
         <v>2201</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D39" s="6">
+        <v>20854647.149999999</v>
+      </c>
+      <c r="E39" s="6">
+        <v>19794515.120000001</v>
+      </c>
+      <c r="F39" s="6">
         <v>18916412.23</v>
       </c>
-      <c r="E39" s="6">
+      <c r="G39" s="6">
         <v>0</v>
       </c>
-      <c r="F39" s="6">
+      <c r="H39" s="6">
         <v>2810067.14</v>
       </c>
-      <c r="G39" s="7">
+      <c r="I39" s="7">
         <v>2810067.14</v>
       </c>
     </row>
-    <row r="40" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="4">
         <v>2023</v>
       </c>
@@ -1531,22 +1773,28 @@
         <v>2211</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D40" s="6">
+        <v>16156823.34</v>
+      </c>
+      <c r="E40" s="6">
+        <v>15396119.26</v>
+      </c>
+      <c r="F40" s="6">
         <v>14519942.390000001</v>
       </c>
-      <c r="E40" s="6">
+      <c r="G40" s="6">
         <v>113058.43</v>
       </c>
-      <c r="F40" s="6">
+      <c r="H40" s="6">
         <v>599716.37</v>
       </c>
-      <c r="G40" s="7">
+      <c r="I40" s="7">
         <v>712774.8</v>
       </c>
     </row>
-    <row r="41" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="4">
         <v>2023</v>
       </c>
@@ -1554,22 +1802,28 @@
         <v>2241</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D41" s="6">
+        <v>106797429.43000001</v>
+      </c>
+      <c r="E41" s="6">
+        <v>101404974.15000001</v>
+      </c>
+      <c r="F41" s="6">
         <v>100479945.84</v>
       </c>
-      <c r="E41" s="6">
+      <c r="G41" s="6">
         <v>10446834.76</v>
       </c>
-      <c r="F41" s="6">
+      <c r="H41" s="6">
         <v>3875281.47</v>
       </c>
-      <c r="G41" s="7">
+      <c r="I41" s="7">
         <v>14322116.23</v>
       </c>
     </row>
-    <row r="42" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="4">
         <v>2023</v>
       </c>
@@ -1577,22 +1831,28 @@
         <v>2251</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D42" s="6">
+        <v>30826852.399999999</v>
+      </c>
+      <c r="E42" s="6">
+        <v>29563968.030000001</v>
+      </c>
+      <c r="F42" s="6">
         <v>29011549.300000001</v>
       </c>
-      <c r="E42" s="6">
+      <c r="G42" s="6">
         <v>565.47</v>
       </c>
-      <c r="F42" s="6">
+      <c r="H42" s="6">
         <v>746119.06</v>
       </c>
-      <c r="G42" s="7">
+      <c r="I42" s="7">
         <v>746684.53</v>
       </c>
     </row>
-    <row r="43" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="4">
         <v>2023</v>
       </c>
@@ -1600,22 +1860,28 @@
         <v>2261</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D43" s="6">
+        <v>368684570.20999998</v>
+      </c>
+      <c r="E43" s="6">
+        <v>273219748.01999998</v>
+      </c>
+      <c r="F43" s="6">
         <v>269618135.06999999</v>
       </c>
-      <c r="E43" s="6">
+      <c r="G43" s="6">
         <v>8154203.5999999996</v>
       </c>
-      <c r="F43" s="6">
+      <c r="H43" s="6">
         <v>41399163.159999996</v>
       </c>
-      <c r="G43" s="7">
+      <c r="I43" s="7">
         <v>49553366.759999998</v>
       </c>
     </row>
-    <row r="44" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="4">
         <v>2023</v>
       </c>
@@ -1623,22 +1889,28 @@
         <v>2271</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D44" s="6">
+        <v>2164150549.4200001</v>
+      </c>
+      <c r="E44" s="6">
+        <v>2059482648.7</v>
+      </c>
+      <c r="F44" s="6">
         <v>2019538042.3699999</v>
       </c>
-      <c r="E44" s="6">
+      <c r="G44" s="6">
         <v>3347619.96</v>
       </c>
-      <c r="F44" s="6">
+      <c r="H44" s="6">
         <v>95082172.209999993</v>
       </c>
-      <c r="G44" s="7">
+      <c r="I44" s="7">
         <v>98429792.170000002</v>
       </c>
     </row>
-    <row r="45" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="4">
         <v>2023</v>
       </c>
@@ -1646,22 +1918,28 @@
         <v>2281</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D45" s="6">
+        <v>6125588.9400000004</v>
+      </c>
+      <c r="E45" s="6">
+        <v>5821567.3399999999</v>
+      </c>
+      <c r="F45" s="6">
         <v>5483571.3300000001</v>
       </c>
-      <c r="E45" s="6">
+      <c r="G45" s="6">
         <v>24344.67</v>
       </c>
-      <c r="F45" s="6">
+      <c r="H45" s="6">
         <v>193381.66</v>
       </c>
-      <c r="G45" s="7">
+      <c r="I45" s="7">
         <v>217726.33</v>
       </c>
     </row>
-    <row r="46" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
         <v>2023</v>
       </c>
@@ -1669,22 +1947,28 @@
         <v>2301</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D46" s="6">
+        <v>1914847566.8499999</v>
+      </c>
+      <c r="E46" s="6">
+        <v>1044533400.24</v>
+      </c>
+      <c r="F46" s="6">
         <v>966297540.78999996</v>
       </c>
-      <c r="E46" s="6">
+      <c r="G46" s="6">
         <v>16445711.300000001</v>
       </c>
-      <c r="F46" s="6">
+      <c r="H46" s="6">
         <v>318972727.75999999</v>
       </c>
-      <c r="G46" s="7">
+      <c r="I46" s="7">
         <v>335418439.06</v>
       </c>
     </row>
-    <row r="47" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="4">
         <v>2023</v>
       </c>
@@ -1692,22 +1976,28 @@
         <v>2311</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D47" s="6">
+        <v>469927618.13</v>
+      </c>
+      <c r="E47" s="6">
+        <v>414313756.02999997</v>
+      </c>
+      <c r="F47" s="6">
         <v>405713436.11000001</v>
       </c>
-      <c r="E47" s="6">
+      <c r="G47" s="6">
         <v>1205407.47</v>
       </c>
-      <c r="F47" s="6">
+      <c r="H47" s="6">
         <v>16962260.800000001</v>
       </c>
-      <c r="G47" s="7">
+      <c r="I47" s="7">
         <v>18167668.27</v>
       </c>
     </row>
-    <row r="48" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="4">
         <v>2023</v>
       </c>
@@ -1715,22 +2005,28 @@
         <v>2321</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D48" s="6">
+        <v>355203535.23000002</v>
+      </c>
+      <c r="E48" s="6">
+        <v>320246686.79000002</v>
+      </c>
+      <c r="F48" s="6">
         <v>311999002.94</v>
       </c>
-      <c r="E48" s="6">
+      <c r="G48" s="6">
         <v>1679096.03</v>
       </c>
-      <c r="F48" s="6">
+      <c r="H48" s="6">
         <v>28146659.989999998</v>
       </c>
-      <c r="G48" s="7">
+      <c r="I48" s="7">
         <v>29825756.02</v>
       </c>
     </row>
-    <row r="49" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="4">
         <v>2023</v>
       </c>
@@ -1738,22 +2034,28 @@
         <v>2331</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D49" s="6">
+        <v>30989568.550000001</v>
+      </c>
+      <c r="E49" s="6">
+        <v>30394216.460000001</v>
+      </c>
+      <c r="F49" s="6">
         <v>28953199.859999999</v>
       </c>
-      <c r="E49" s="6">
+      <c r="G49" s="6">
         <v>78441.509999999995</v>
       </c>
-      <c r="F49" s="6">
+      <c r="H49" s="6">
         <v>108549.11</v>
       </c>
-      <c r="G49" s="7">
+      <c r="I49" s="7">
         <v>186990.62</v>
       </c>
     </row>
-    <row r="50" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="4">
         <v>2023</v>
       </c>
@@ -1761,22 +2063,28 @@
         <v>2351</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D50" s="6">
+        <v>404521667.47000003</v>
+      </c>
+      <c r="E50" s="6">
+        <v>384928295.56999999</v>
+      </c>
+      <c r="F50" s="6">
         <v>374712336.29000002</v>
       </c>
-      <c r="E50" s="6">
+      <c r="G50" s="6">
         <v>6005270.7599999998</v>
       </c>
-      <c r="F50" s="6">
+      <c r="H50" s="6">
         <v>21210103.710000001</v>
       </c>
-      <c r="G50" s="7">
+      <c r="I50" s="7">
         <v>27215374.469999999</v>
       </c>
     </row>
-    <row r="51" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="4">
         <v>2023</v>
       </c>
@@ -1784,22 +2092,28 @@
         <v>2371</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D51" s="6">
+        <v>247119982.84</v>
+      </c>
+      <c r="E51" s="6">
+        <v>242894139.49000001</v>
+      </c>
+      <c r="F51" s="6">
         <v>242543975.53</v>
       </c>
-      <c r="E51" s="6">
+      <c r="G51" s="6">
         <v>378714.11</v>
       </c>
-      <c r="F51" s="6">
+      <c r="H51" s="6">
         <v>3948517.78</v>
       </c>
-      <c r="G51" s="7">
+      <c r="I51" s="7">
         <v>4327231.8899999997</v>
       </c>
     </row>
-    <row r="52" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="4">
         <v>2023</v>
       </c>
@@ -1807,22 +2121,28 @@
         <v>2421</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D52" s="6">
+        <v>100992421.23999999</v>
+      </c>
+      <c r="E52" s="6">
+        <v>76969361.799999997</v>
+      </c>
+      <c r="F52" s="6">
         <v>75625489.049999997</v>
       </c>
-      <c r="E52" s="6">
+      <c r="G52" s="6">
         <v>163906.26999999999</v>
       </c>
-      <c r="F52" s="6">
+      <c r="H52" s="6">
         <v>6105648.21</v>
       </c>
-      <c r="G52" s="7">
+      <c r="I52" s="7">
         <v>6269554.4800000004</v>
       </c>
     </row>
-    <row r="53" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="4">
         <v>2023</v>
       </c>
@@ -1830,22 +2150,28 @@
         <v>2431</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D53" s="6">
+        <v>6692249.8799999999</v>
+      </c>
+      <c r="E53" s="6">
+        <v>5732550.6900000004</v>
+      </c>
+      <c r="F53" s="6">
         <v>5640278.6500000004</v>
       </c>
-      <c r="E53" s="6">
+      <c r="G53" s="6">
         <v>44191.45</v>
       </c>
-      <c r="F53" s="6">
+      <c r="H53" s="6">
         <v>9439.76</v>
       </c>
-      <c r="G53" s="7">
+      <c r="I53" s="7">
         <v>53631.21</v>
       </c>
     </row>
-    <row r="54" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="4">
         <v>2023</v>
       </c>
@@ -1853,22 +2179,28 @@
         <v>2441</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D54" s="6">
+        <v>17351140.010000002</v>
+      </c>
+      <c r="E54" s="6">
+        <v>16698417.52</v>
+      </c>
+      <c r="F54" s="6">
         <v>16573785.26</v>
       </c>
-      <c r="E54" s="6">
+      <c r="G54" s="6">
         <v>0</v>
       </c>
-      <c r="F54" s="6">
+      <c r="H54" s="6">
         <v>611025.34</v>
       </c>
-      <c r="G54" s="7">
+      <c r="I54" s="7">
         <v>611025.34</v>
       </c>
     </row>
-    <row r="55" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="4">
         <v>2023</v>
       </c>
@@ -1876,407 +2208,532 @@
         <v>2461</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D55" s="6">
+        <v>3919274.27</v>
+      </c>
+      <c r="E55" s="6">
+        <v>3274957.97</v>
+      </c>
+      <c r="F55" s="6">
         <v>2995203.29</v>
       </c>
-      <c r="E55" s="6">
+      <c r="G55" s="6">
         <v>0</v>
       </c>
-      <c r="F55" s="6">
+      <c r="H55" s="6">
         <v>526357.61</v>
       </c>
-      <c r="G55" s="7">
+      <c r="I55" s="7">
         <v>526357.61</v>
       </c>
     </row>
-    <row r="56" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="4">
         <v>2023</v>
       </c>
       <c r="B56" s="4">
+        <v>3041</v>
+      </c>
+      <c r="C56" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="D56" s="6">
+        <v>360362919.20999998</v>
+      </c>
+      <c r="E56" s="6">
+        <v>360362919.20999998</v>
+      </c>
+      <c r="F56" s="6">
+        <v>360362919.20999998</v>
+      </c>
+      <c r="G56" s="6"/>
+      <c r="H56" s="6"/>
+      <c r="I56" s="7"/>
+    </row>
+    <row r="57" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="4">
+        <v>2023</v>
+      </c>
+      <c r="B57" s="4">
+        <v>3051</v>
+      </c>
+      <c r="C57" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="D57" s="6">
+        <v>129507075.06</v>
+      </c>
+      <c r="E57" s="6">
+        <v>129507075.06</v>
+      </c>
+      <c r="F57" s="6">
+        <v>129507075.06</v>
+      </c>
+      <c r="G57" s="6"/>
+      <c r="H57" s="6"/>
+      <c r="I57" s="7"/>
+    </row>
+    <row r="58" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="4">
+        <v>2023</v>
+      </c>
+      <c r="B58" s="4">
         <v>4091</v>
       </c>
-      <c r="C56" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="D56" s="6">
+      <c r="C58" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="D58" s="6">
+        <v>7031581.25</v>
+      </c>
+      <c r="E58" s="6">
+        <v>5241364.07</v>
+      </c>
+      <c r="F58" s="6">
         <v>3380577.21</v>
       </c>
-      <c r="E56" s="6">
+      <c r="G58" s="6">
         <v>0</v>
       </c>
-      <c r="F56" s="6">
+      <c r="H58" s="6">
         <v>0</v>
       </c>
-      <c r="G56" s="7">
+      <c r="I58" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="4">
-        <v>2023</v>
-      </c>
-      <c r="B57" s="4">
+    <row r="59" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="4">
+        <v>2023</v>
+      </c>
+      <c r="B59" s="4">
         <v>4101</v>
       </c>
-      <c r="C57" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="D57" s="6">
+      <c r="C59" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="D59" s="6">
+        <v>16882559.960000001</v>
+      </c>
+      <c r="E59" s="6">
         <v>15883952.890000001</v>
       </c>
-      <c r="E57" s="6">
+      <c r="F59" s="6">
+        <v>15883952.890000001</v>
+      </c>
+      <c r="G59" s="6">
         <v>0</v>
       </c>
-      <c r="F57" s="6">
+      <c r="H59" s="6">
         <v>707987.39</v>
       </c>
-      <c r="G57" s="7">
+      <c r="I59" s="7">
         <v>707987.39</v>
       </c>
     </row>
-    <row r="58" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="4">
-        <v>2023</v>
-      </c>
-      <c r="B58" s="4">
+    <row r="60" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A60" s="4">
+        <v>2023</v>
+      </c>
+      <c r="B60" s="4">
         <v>4141</v>
       </c>
-      <c r="C58" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="D58" s="6">
+      <c r="C60" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D60" s="6">
+        <v>40613382.549999997</v>
+      </c>
+      <c r="E60" s="6">
+        <v>23565562.32</v>
+      </c>
+      <c r="F60" s="6">
         <v>22676692.219999999</v>
       </c>
-      <c r="E58" s="6">
+      <c r="G60" s="6">
         <v>0</v>
       </c>
-      <c r="F58" s="6">
+      <c r="H60" s="6">
         <v>11408560.880000001</v>
       </c>
-      <c r="G58" s="7">
+      <c r="I60" s="7">
         <v>11408560.880000001</v>
       </c>
     </row>
-    <row r="59" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="4">
-        <v>2023</v>
-      </c>
-      <c r="B59" s="4">
+    <row r="61" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="4">
+        <v>2023</v>
+      </c>
+      <c r="B61" s="4">
         <v>4251</v>
       </c>
-      <c r="C59" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="D59" s="6">
+      <c r="C61" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D61" s="6">
+        <v>110854339.84999999</v>
+      </c>
+      <c r="E61" s="6">
+        <v>106583471.83</v>
+      </c>
+      <c r="F61" s="6">
         <v>105151900.42</v>
       </c>
-      <c r="E59" s="6">
+      <c r="G61" s="6">
         <v>12672808.300000001</v>
       </c>
-      <c r="F59" s="6">
+      <c r="H61" s="6">
         <v>17248454.850000001</v>
       </c>
-      <c r="G59" s="7">
+      <c r="I61" s="7">
         <v>29921263.149999999</v>
       </c>
     </row>
-    <row r="60" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="4">
-        <v>2023</v>
-      </c>
-      <c r="B60" s="4">
+    <row r="62" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A62" s="4">
+        <v>2023</v>
+      </c>
+      <c r="B62" s="4">
         <v>4291</v>
       </c>
-      <c r="C60" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="D60" s="6">
+      <c r="C62" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="D62" s="6">
+        <v>11302215537.530001</v>
+      </c>
+      <c r="E62" s="6">
+        <v>10567487751.92</v>
+      </c>
+      <c r="F62" s="6">
         <v>10368587376.49</v>
       </c>
-      <c r="E60" s="6">
+      <c r="G62" s="6">
         <v>876192598.35000002</v>
       </c>
-      <c r="F60" s="6">
+      <c r="H62" s="6">
         <v>462749484.48000002</v>
       </c>
-      <c r="G60" s="7">
+      <c r="I62" s="7">
         <v>1338942082.8299999</v>
       </c>
     </row>
-    <row r="61" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="4">
-        <v>2023</v>
-      </c>
-      <c r="B61" s="4">
+    <row r="63" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A63" s="4">
+        <v>2023</v>
+      </c>
+      <c r="B63" s="4">
         <v>4331</v>
       </c>
-      <c r="C61" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="D61" s="6">
+      <c r="C63" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="D63" s="6">
+        <v>652279.16</v>
+      </c>
+      <c r="E63" s="6">
+        <v>254203.16</v>
+      </c>
+      <c r="F63" s="6">
         <v>245243.42</v>
       </c>
-      <c r="E61" s="6"/>
-      <c r="F61" s="6"/>
-      <c r="G61" s="7"/>
-    </row>
-    <row r="62" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="4">
-        <v>2023</v>
-      </c>
-      <c r="B62" s="4">
+      <c r="G63" s="6"/>
+      <c r="H63" s="6"/>
+      <c r="I63" s="7"/>
+    </row>
+    <row r="64" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="4">
+        <v>2023</v>
+      </c>
+      <c r="B64" s="4">
         <v>4341</v>
       </c>
-      <c r="C62" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="D62" s="6">
+      <c r="C64" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D64" s="6">
+        <v>3424799.42</v>
+      </c>
+      <c r="E64" s="6">
+        <v>2738104.88</v>
+      </c>
+      <c r="F64" s="6">
         <v>2250014.71</v>
       </c>
-      <c r="E62" s="6">
+      <c r="G64" s="6">
         <v>68971.199999999997</v>
       </c>
-      <c r="F62" s="6">
+      <c r="H64" s="6">
         <v>75798.710000000006</v>
       </c>
-      <c r="G62" s="7">
+      <c r="I64" s="7">
         <v>144769.91</v>
       </c>
     </row>
-    <row r="63" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="4">
-        <v>2023</v>
-      </c>
-      <c r="B63" s="4">
+    <row r="65" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="4">
+        <v>2023</v>
+      </c>
+      <c r="B65" s="4">
         <v>4381</v>
       </c>
-      <c r="C63" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="D63" s="6">
+      <c r="C65" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="D65" s="6">
+        <v>93182744.760000005</v>
+      </c>
+      <c r="E65" s="6">
+        <v>73453457.049999997</v>
+      </c>
+      <c r="F65" s="6">
         <v>71188066.920000002</v>
       </c>
-      <c r="E63" s="6">
+      <c r="G65" s="6">
         <v>0</v>
       </c>
-      <c r="F63" s="6">
+      <c r="H65" s="6">
         <v>8330157.7599999998</v>
       </c>
-      <c r="G63" s="7">
+      <c r="I65" s="7">
         <v>8330157.7599999998</v>
       </c>
     </row>
-    <row r="64" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="4">
-        <v>2023</v>
-      </c>
-      <c r="B64" s="4">
+    <row r="66" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="4">
+        <v>2023</v>
+      </c>
+      <c r="B66" s="4">
         <v>4451</v>
       </c>
-      <c r="C64" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="D64" s="6">
+      <c r="C66" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="D66" s="6">
+        <v>35323915.030000001</v>
+      </c>
+      <c r="E66" s="6">
+        <v>16775518.720000001</v>
+      </c>
+      <c r="F66" s="6">
         <v>15712214.16</v>
       </c>
-      <c r="E64" s="6">
+      <c r="G66" s="6">
         <v>1711.42</v>
       </c>
-      <c r="F64" s="6">
+      <c r="H66" s="6">
         <v>370032.98</v>
       </c>
-      <c r="G64" s="7">
+      <c r="I66" s="7">
         <v>371744.4</v>
       </c>
     </row>
-    <row r="65" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="4">
-        <v>2023</v>
-      </c>
-      <c r="B65" s="4">
+    <row r="67" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A67" s="4">
+        <v>2023</v>
+      </c>
+      <c r="B67" s="4">
         <v>4491</v>
       </c>
-      <c r="C65" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="D65" s="6">
+      <c r="C67" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="D67" s="6">
+        <v>3940069.61</v>
+      </c>
+      <c r="E67" s="6">
+        <v>3940069.61</v>
+      </c>
+      <c r="F67" s="6">
         <v>3184573.65</v>
       </c>
-      <c r="E65" s="6">
+      <c r="G67" s="6">
         <v>390021.88</v>
       </c>
-      <c r="F65" s="6">
+      <c r="H67" s="6">
         <v>0</v>
       </c>
-      <c r="G65" s="7">
+      <c r="I67" s="7">
         <v>390021.88</v>
       </c>
     </row>
-    <row r="66" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="4">
-        <v>2023</v>
-      </c>
-      <c r="B66" s="4">
+    <row r="68" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A68" s="4">
+        <v>2023</v>
+      </c>
+      <c r="B68" s="4">
         <v>4541</v>
       </c>
-      <c r="C66" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="D66" s="6">
+      <c r="C68" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="D68" s="6">
+        <v>362500</v>
+      </c>
+      <c r="E68" s="6">
+        <v>327310.98</v>
+      </c>
+      <c r="F68" s="6">
         <v>320259.33</v>
       </c>
-      <c r="E66" s="6">
+      <c r="G68" s="6">
         <v>0</v>
       </c>
-      <c r="F66" s="6">
+      <c r="H68" s="6">
         <v>0</v>
       </c>
-      <c r="G66" s="7">
+      <c r="I68" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="4">
-        <v>2023</v>
-      </c>
-      <c r="B67" s="4">
+    <row r="69" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A69" s="4">
+        <v>2023</v>
+      </c>
+      <c r="B69" s="4">
         <v>4551</v>
       </c>
-      <c r="C67" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="D67" s="6">
+      <c r="C69" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D69" s="6">
+        <v>72736739.480000004</v>
+      </c>
+      <c r="E69" s="6">
+        <v>71196549.090000004</v>
+      </c>
+      <c r="F69" s="6">
         <v>71168742.390000001</v>
       </c>
-      <c r="E67" s="6">
+      <c r="G69" s="6">
         <v>6853309.7699999996</v>
       </c>
-      <c r="F67" s="6">
+      <c r="H69" s="6">
         <v>0</v>
       </c>
-      <c r="G67" s="7">
+      <c r="I69" s="7">
         <v>6853309.7699999996</v>
       </c>
     </row>
-    <row r="68" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="4">
-        <v>2023</v>
-      </c>
-      <c r="B68" s="4">
+    <row r="70" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A70" s="4">
+        <v>2023</v>
+      </c>
+      <c r="B70" s="4">
         <v>4601</v>
       </c>
-      <c r="C68" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="D68" s="6">
+      <c r="C70" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="D70" s="6">
+        <v>2887433.54</v>
+      </c>
+      <c r="E70" s="6">
+        <v>2887433.54</v>
+      </c>
+      <c r="F70" s="6">
         <v>0</v>
       </c>
-      <c r="E68" s="6">
+      <c r="G70" s="6">
         <v>180000</v>
       </c>
-      <c r="F68" s="6">
+      <c r="H70" s="6">
         <v>45000</v>
       </c>
-      <c r="G68" s="7">
+      <c r="I70" s="7">
         <v>225000</v>
       </c>
     </row>
-    <row r="69" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="4">
-        <v>2023</v>
-      </c>
-      <c r="B69" s="4">
-        <v>4631</v>
-      </c>
-      <c r="C69" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="D69" s="6">
-        <v>282507517.43000001</v>
-      </c>
-      <c r="E69" s="6">
-        <v>344621.26</v>
-      </c>
-      <c r="F69" s="6">
-        <v>28865269.27</v>
-      </c>
-      <c r="G69" s="7">
-        <v>29209890.530000001</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="4">
-        <v>2023</v>
-      </c>
-      <c r="B70" s="4">
+    <row r="71" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A71" s="4">
+        <v>2023</v>
+      </c>
+      <c r="B71" s="4">
         <v>4691</v>
       </c>
-      <c r="C70" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="D70" s="6">
+      <c r="C71" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="D71" s="6">
+        <v>56928753.649999999</v>
+      </c>
+      <c r="E71" s="6">
+        <v>13274144.699999999</v>
+      </c>
+      <c r="F71" s="6">
         <v>11948730.27</v>
       </c>
-      <c r="E70" s="6">
+      <c r="G71" s="6">
         <v>2022500.23</v>
       </c>
-      <c r="F70" s="6">
+      <c r="H71" s="6">
         <v>11009074.779999999</v>
       </c>
-      <c r="G70" s="7">
+      <c r="I71" s="7">
         <v>13031575.01</v>
       </c>
     </row>
-    <row r="71" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="4">
-        <v>2023</v>
-      </c>
-      <c r="B71" s="4">
+    <row r="72" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A72" s="4">
+        <v>2023</v>
+      </c>
+      <c r="B72" s="4">
         <v>4701</v>
       </c>
-      <c r="C71" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="D71" s="6">
+      <c r="C72" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="D72" s="6">
+        <v>481821.71</v>
+      </c>
+      <c r="E72" s="6">
+        <v>79007.12</v>
+      </c>
+      <c r="F72" s="6">
         <v>75725.759999999995</v>
       </c>
-      <c r="E71" s="6">
+      <c r="G72" s="6">
         <v>4212.6899999999996</v>
       </c>
-      <c r="F71" s="6">
+      <c r="H72" s="6">
         <v>950789.36</v>
       </c>
-      <c r="G71" s="7">
+      <c r="I72" s="7">
         <v>955002.05</v>
       </c>
     </row>
-    <row r="72" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="4">
-        <v>2023</v>
-      </c>
-      <c r="B72" s="4">
+    <row r="73" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A73" s="4">
+        <v>2023</v>
+      </c>
+      <c r="B73" s="4">
         <v>4711</v>
       </c>
-      <c r="C72" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="D72" s="6">
+      <c r="C73" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="D73" s="6">
+        <v>16707308683.780001</v>
+      </c>
+      <c r="E73" s="6">
+        <v>16706043073.459999</v>
+      </c>
+      <c r="F73" s="6">
         <v>16714373495.870001</v>
       </c>
-      <c r="E72" s="6">
+      <c r="G73" s="6">
         <v>3616.02</v>
       </c>
-      <c r="F72" s="6">
+      <c r="H73" s="6">
         <v>637267.26</v>
       </c>
-      <c r="G72" s="7">
+      <c r="I73" s="7">
         <v>640883.28</v>
       </c>
     </row>
-    <row r="73" spans="1:7" s="1" customFormat="1" ht="28.7" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="74" spans="1:9" s="1" customFormat="1" ht="28.7" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/upload/orgao2023.xlsx
+++ b/upload/orgao2023.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="8430"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15270" windowHeight="8355"/>
   </bookViews>
   <sheets>
     <sheet name="orgao" sheetId="1" r:id="rId1"/>

--- a/upload/orgao2023.xlsx
+++ b/upload/orgao2023.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m11483500\Documents\transparencia-mg\portal_despesa_empenho\upload\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m11483500\Documents\html_portal\portal_despesa_empenho\upload\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="15270" windowHeight="8355"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="8430"/>
   </bookViews>
   <sheets>
     <sheet name="orgao" sheetId="1" r:id="rId1"/>

--- a/upload/orgao2023.xlsx
+++ b/upload/orgao2023.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="8430"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="8400"/>
   </bookViews>
   <sheets>
     <sheet name="orgao" sheetId="1" r:id="rId1"/>

--- a/upload/orgao2023.xlsx
+++ b/upload/orgao2023.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m11483500\Documents\html_portal\portal_despesa_empenho\upload\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kbomf\OneDrive\Documents\html\portal_despesa_empenho\upload\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DB13AB72-6BB9-4CD0-B315-617836F5303B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="8400"/>
+    <workbookView xWindow="19200" yWindow="0" windowWidth="19200" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="orgao" sheetId="1" r:id="rId1"/>
@@ -19,15 +20,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="153">
   <si>
     <t>Ano de Exercício</t>
   </si>
   <si>
-    <t>Unidade Orçamentária - Código</t>
-  </si>
-  <si>
-    <t>Unidade Orçamentária - Nome</t>
+    <t>Unidade Orçamentária - Código/Nome</t>
+  </si>
+  <si>
+    <t>Unidade Orçamentária - Sigla</t>
   </si>
   <si>
     <t>Valor Despesa Empenhada</t>
@@ -48,226 +49,442 @@
     <t>Valor Pago RP</t>
   </si>
   <si>
-    <t>GABINETE MILITAR DO GOVERNADOR DO ESTADO DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>ADVOCACIA GERAL DO ESTADO</t>
-  </si>
-  <si>
-    <t>OUVIDORIA-GERAL DO ESTADO DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>SECRETARIA DE ESTADO DE FAZENDA</t>
-  </si>
-  <si>
-    <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONOMICO</t>
-  </si>
-  <si>
-    <t>SECRETARIA DE ESTADO DE AGRICULTURA, PECUARIA E ABASTECIMENTO - SEAPA</t>
-  </si>
-  <si>
-    <t>POLICIA MILITAR DO ESTADO DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>SECRETARIA DE ESTADO DE EDUCACAO</t>
-  </si>
-  <si>
-    <t>SECRETARIA DE ESTADO DE CULTURA E TURISMO</t>
-  </si>
-  <si>
-    <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIAS</t>
-  </si>
-  <si>
-    <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTAVEL</t>
-  </si>
-  <si>
-    <t>CORPO DE BOMBEIROS MILITAR DO ESTADO DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>SECRETARIA DE ESTADO DE JUSTICA E SEGURANCA PUBLICA</t>
-  </si>
-  <si>
-    <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL</t>
-  </si>
-  <si>
-    <t>SECRETARIA DE ESTADO DE GOVERNO</t>
-  </si>
-  <si>
-    <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTAO</t>
-  </si>
-  <si>
-    <t>POLICIA CIVIL DO ESTADO DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>CONTROLADORIA-GERAL DO ESTADO</t>
-  </si>
-  <si>
-    <t>ESCOLA DE SAUDE PUBLICA DO ESTADO DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>SECRETARIA-GERAL</t>
-  </si>
-  <si>
-    <t>SECRETARIA DE ESTADO DE COMUNICACAO SOCIAL</t>
-  </si>
-  <si>
-    <t>SECRETARIA DE ESTADO DA CASA CIVIL</t>
-  </si>
-  <si>
-    <t>EGE SEC.FAZENDA-ENCARGOS DIVERSOS</t>
-  </si>
-  <si>
-    <t>PARTICIPACAO NO AUMENTO DO CAPITAL SOCIAL DE EMPRESAS</t>
-  </si>
-  <si>
-    <t>GESTAO DA DIVIDA PUBLICA ESTADUAL</t>
-  </si>
-  <si>
-    <t>EGE-SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTAO</t>
-  </si>
-  <si>
-    <t>INSTITUTO DE PREVIDENCIA DOS SERVIDORES DO ESTADO DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>LOTERIA DO ESTADO DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>FUNDACAO JOAO PINHEIRO</t>
-  </si>
-  <si>
-    <t>FUNDACAO DE AMPARO A PESQUISA DO ESTADO DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>FUNDACAO ESTADUAL DO MEIO AMBIENTE</t>
-  </si>
-  <si>
-    <t>INSTITUTO ESTADUAL DE FLORESTAS</t>
-  </si>
-  <si>
-    <t>INSTITUTO DE PREVIDENCIA DOS SERVIDORES MILITARES DO ESTADO DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>FUNDACAO HELENA ANTIPOFF</t>
-  </si>
-  <si>
-    <t>FUNDACAO EDUCACIONAL CAIO MARTINS</t>
-  </si>
-  <si>
-    <t>FUNDACAO DE ARTE DE OURO PRETO</t>
-  </si>
-  <si>
-    <t>FUNDACAO CLOVIS SALGADO</t>
-  </si>
-  <si>
-    <t>INSTITUTO ESTADUAL DO PATRIMONIO HISTORICO E ARTISTICO DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>FUNDACAO TV MINAS CULTURAL E EDUCATIVA</t>
-  </si>
-  <si>
-    <t>INSTITUTO MINEIRO DE GESTAO DAS AGUAS</t>
-  </si>
-  <si>
-    <t>JUNTA COMERCIAL DO ESTADO DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>FUNDACAO EZEQUIEL DIAS</t>
-  </si>
-  <si>
-    <t>FUNDACAO HOSPITALAR DO ESTADO DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>FUNDACAO DE EDUCACAO PARA O TRABALHO DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>DEPARTAMENTO DE EDIFICACOES E ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>UNIVERSIDADE ESTADUAL DE MONTES CLAROS</t>
-  </si>
-  <si>
-    <t>FUNDACAO CENTRO DE HEMATOLOGIA E HEMOTERAPIA DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>INSTITUTO DE METROLOGIA E QUALIDADE DO ESTADO DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>UNIVERSIDADE DO ESTADO DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>INSTITUTO MINEIRO DE AGROPECUARIA</t>
-  </si>
-  <si>
-    <t>INSTITUTO DE DESENVOLVIMENTO DO NORTE E NORDESTE DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>AGENCIA DE DESENVOLVIMENTO DA REGIAO METROPOLITANA DE BELO HORIZONTE</t>
-  </si>
-  <si>
-    <t>AGENCIA REGULADORA DE SERVICOS DE ABASTECIMENTO DE AGUA E DE ESGOTAMENTO SANITARIO DO ESTADO DE MINA</t>
-  </si>
-  <si>
-    <t>AGENCIA DE DESENVOLVIMENTO DA REGIAO METROPOLITANA DO VALE DO ACO</t>
-  </si>
-  <si>
-    <t>EMPRESA DE ASSISTENCIA TECNICA E EXTENSAO RURAL DO ESTADO DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>EMPRESA DE PESQUISA AGROPECUARIA DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>FUNDO PARA A INFANCIA E A ADOLESCENCIA</t>
-  </si>
-  <si>
-    <t>FUNDO ESTADUAL DE HABITACAO</t>
-  </si>
-  <si>
-    <t>FUNDO PENITENCIARIO ESTADUAL</t>
-  </si>
-  <si>
-    <t>FUNDO ESTADUAL DE ASSISTENCIA SOCIAL</t>
-  </si>
-  <si>
-    <t>FUNDO ESTADUAL DE SAUDE</t>
-  </si>
-  <si>
-    <t>FUNDO DE DESENVOLVIMENTO METROPOLITANO</t>
-  </si>
-  <si>
-    <t>FUNDO DE RECUPERACAO, PROTECAO E DESENVOLVIMENTO SUSTENTAVEL DAS BACIAS HIDROGRAFICAS DO ESTADO DE M</t>
-  </si>
-  <si>
-    <t>FUNDO ESTADUAL DE DESENVOLVIMENTO DE TRANSPORTES</t>
-  </si>
-  <si>
-    <t>FUNDO ESTADUAL DE PROTECAO E DEFESA DO CONSUMIDOR</t>
-  </si>
-  <si>
-    <t>FUNDO ESTADUAL DE CULTURA</t>
-  </si>
-  <si>
-    <t>FUNDO DE APOIO HABITACIONAL AOS MILITARES DO ESTADO DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>FUNDO DE ASSISTENCIA AO PECULIO DOS SERVIDORES DO ESTADO DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>FUNDO ESTADUAL DOS DIREITOS DO IDOSO</t>
-  </si>
-  <si>
-    <t>FUNDO ESTADUAL DE SEGURANCA PUBLICA DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>FUNDO ESTADUAL DO TRABALHO DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>FUNDO FINANCEIRO DE PREVIDENCIA DO ESTADO DE MINAS GERAIS</t>
+    <t>1071 - GABINETE MILITAR DO GOVERNADOR DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>GABINETE MILITAR</t>
+  </si>
+  <si>
+    <t>1081 - ADVOCACIA GERAL DO ESTADO</t>
+  </si>
+  <si>
+    <t>AGE</t>
+  </si>
+  <si>
+    <t>1101 - OUVIDORIA-GERAL DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>OGE</t>
+  </si>
+  <si>
+    <t>1191 - SECRETARIA DE ESTADO DE FAZENDA</t>
+  </si>
+  <si>
+    <t>SEF</t>
+  </si>
+  <si>
+    <t>1221 - SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONOMICO</t>
+  </si>
+  <si>
+    <t>SEDE</t>
+  </si>
+  <si>
+    <t>1231 - SECRETARIA DE ESTADO DE AGRICULTURA, PECUARIA E ABASTECIMENTO - SEAPA</t>
+  </si>
+  <si>
+    <t>SEAPA</t>
+  </si>
+  <si>
+    <t>1251 - POLICIA MILITAR DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>PMMG</t>
+  </si>
+  <si>
+    <t>1261 - SECRETARIA DE ESTADO DE EDUCACAO</t>
+  </si>
+  <si>
+    <t>SEE</t>
+  </si>
+  <si>
+    <t>1271 - SECRETARIA DE ESTADO DE CULTURA E TURISMO</t>
+  </si>
+  <si>
+    <t>SECULT</t>
+  </si>
+  <si>
+    <t>1301 - SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIAS</t>
+  </si>
+  <si>
+    <t>SEINFRA</t>
+  </si>
+  <si>
+    <t>1371 - SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTAVEL</t>
+  </si>
+  <si>
+    <t>SEMAD</t>
+  </si>
+  <si>
+    <t>1401 - CORPO DE BOMBEIROS MILITAR DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>CBMMG</t>
+  </si>
+  <si>
+    <t>1451 - SECRETARIA DE ESTADO DE JUSTICA E SEGURANCA PUBLICA</t>
+  </si>
+  <si>
+    <t>SEJUSP</t>
+  </si>
+  <si>
+    <t>1481 - SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL</t>
+  </si>
+  <si>
+    <t>SEDESE</t>
+  </si>
+  <si>
+    <t>1491 - SECRETARIA DE ESTADO DE GOVERNO</t>
+  </si>
+  <si>
+    <t>SEGOV</t>
+  </si>
+  <si>
+    <t>1501 - SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTAO</t>
+  </si>
+  <si>
+    <t>SEPLAG</t>
+  </si>
+  <si>
+    <t>1511 - POLICIA CIVIL DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>PCMG</t>
+  </si>
+  <si>
+    <t>1521 - CONTROLADORIA-GERAL DO ESTADO</t>
+  </si>
+  <si>
+    <t>CGE</t>
+  </si>
+  <si>
+    <t>1541 - ESCOLA DE SAUDE PUBLICA DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>ESP MG</t>
+  </si>
+  <si>
+    <t>1631 - SECRETARIA-GERAL</t>
+  </si>
+  <si>
+    <t>SEC. GERAL</t>
+  </si>
+  <si>
+    <t>1711 - SECRETARIA DE ESTADO DE COMUNICACAO SOCIAL</t>
+  </si>
+  <si>
+    <t>SECOM</t>
+  </si>
+  <si>
+    <t>1721 - SECRETARIA DE ESTADO DA CASA CIVIL</t>
+  </si>
+  <si>
+    <t>SCC</t>
+  </si>
+  <si>
+    <t>1911 - EGE SEC.FAZENDA-ENCARGOS DIVERSOS</t>
+  </si>
+  <si>
+    <t>EGE - SEF</t>
+  </si>
+  <si>
+    <t>1915 - PARTICIPACAO NO AUMENTO DO CAPITAL SOCIAL DE EMPRESAS</t>
+  </si>
+  <si>
+    <t>PARTICIPAÇÃO EMPRESAS</t>
+  </si>
+  <si>
+    <t>1916 - GESTAO DA DIVIDA PUBLICA ESTADUAL</t>
+  </si>
+  <si>
+    <t>GDPE - SEF</t>
+  </si>
+  <si>
+    <t>1941 - EGE-SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTAO</t>
+  </si>
+  <si>
+    <t>EGE-SEPLAG</t>
+  </si>
+  <si>
+    <t>2011 - INSTITUTO DE PREVIDENCIA DOS SERVIDORES DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>IPSEMG</t>
+  </si>
+  <si>
+    <t>2041 - LOTERIA DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>LEMG</t>
+  </si>
+  <si>
+    <t>2061 - FUNDACAO JOAO PINHEIRO</t>
+  </si>
+  <si>
+    <t>FJP</t>
+  </si>
+  <si>
+    <t>2071 - FUNDACAO DE AMPARO A PESQUISA DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>FAPEMIG</t>
+  </si>
+  <si>
+    <t>2091 - FUNDACAO ESTADUAL DO MEIO AMBIENTE</t>
+  </si>
+  <si>
+    <t>FEAM</t>
+  </si>
+  <si>
+    <t>2101 - INSTITUTO ESTADUAL DE FLORESTAS</t>
+  </si>
+  <si>
+    <t>IEF</t>
+  </si>
+  <si>
+    <t>2121 - INSTITUTO DE PREVIDENCIA DOS SERVIDORES MILITARES DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>IPSM</t>
+  </si>
+  <si>
+    <t>2151 - FUNDACAO HELENA ANTIPOFF</t>
+  </si>
+  <si>
+    <t>FHA</t>
+  </si>
+  <si>
+    <t>2161 - FUNDACAO EDUCACIONAL CAIO MARTINS</t>
+  </si>
+  <si>
+    <t>FUCAM</t>
+  </si>
+  <si>
+    <t>2171 - FUNDACAO DE ARTE DE OURO PRETO</t>
+  </si>
+  <si>
+    <t>FAOP</t>
+  </si>
+  <si>
+    <t>2181 - FUNDACAO CLOVIS SALGADO</t>
+  </si>
+  <si>
+    <t>FCS</t>
+  </si>
+  <si>
+    <t>2201 - INSTITUTO ESTADUAL DO PATRIMONIO HISTORICO E ARTISTICO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>IEPHA</t>
+  </si>
+  <si>
+    <t>2211 - FUNDACAO TV MINAS CULTURAL E EDUCATIVA</t>
+  </si>
+  <si>
+    <t>TV MINAS</t>
+  </si>
+  <si>
+    <t>2241 - INSTITUTO MINEIRO DE GESTAO DAS AGUAS</t>
+  </si>
+  <si>
+    <t>IGAM</t>
+  </si>
+  <si>
+    <t>2251 - JUNTA COMERCIAL DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>JUCEMG</t>
+  </si>
+  <si>
+    <t>2261 - FUNDACAO EZEQUIEL DIAS</t>
+  </si>
+  <si>
+    <t>FUNED</t>
+  </si>
+  <si>
+    <t>2271 - FUNDACAO HOSPITALAR DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>FHEMIG</t>
+  </si>
+  <si>
+    <t>2281 - FUNDACAO DE EDUCACAO PARA O TRABALHO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>UTRAMIG</t>
+  </si>
+  <si>
+    <t>2301 - DEPARTAMENTO DE EDIFICACOES E ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>DER-MG</t>
+  </si>
+  <si>
+    <t>2311 - UNIVERSIDADE ESTADUAL DE MONTES CLAROS</t>
+  </si>
+  <si>
+    <t>UNIMONTES</t>
+  </si>
+  <si>
+    <t>2321 - FUNDACAO CENTRO DE HEMATOLOGIA E HEMOTERAPIA DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>HEMOMINAS</t>
+  </si>
+  <si>
+    <t>2331 - INSTITUTO DE METROLOGIA E QUALIDADE DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>IPEMMG</t>
+  </si>
+  <si>
+    <t>2351 - UNIVERSIDADE DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>UEMG</t>
+  </si>
+  <si>
+    <t>2371 - INSTITUTO MINEIRO DE AGROPECUARIA</t>
+  </si>
+  <si>
+    <t>IMA</t>
+  </si>
+  <si>
+    <t>2421 - INSTITUTO DE DESENVOLVIMENTO DO NORTE E NORDESTE DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>IDENE</t>
+  </si>
+  <si>
+    <t>2431 - AGENCIA DE DESENVOLVIMENTO DA REGIAO METROPOLITANA DE BELO HORIZONTE</t>
+  </si>
+  <si>
+    <t>AGÊNCIA RMBH</t>
+  </si>
+  <si>
+    <t>2441 - AGENCIA REGULADORA DE SERVICOS DE ABASTECIMENTO DE AGUA E DE ESGOTAMENTO SANITARIO DO ESTADO DE MINA</t>
+  </si>
+  <si>
+    <t>ARSAE -MG</t>
+  </si>
+  <si>
+    <t>2461 - AGENCIA DE DESENVOLVIMENTO DA REGIAO METROPOLITANA DO VALE DO ACO</t>
+  </si>
+  <si>
+    <t>ARMVA</t>
+  </si>
+  <si>
+    <t>3041 - EMPRESA DE ASSISTENCIA TECNICA E EXTENSAO RURAL DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>EMATER</t>
+  </si>
+  <si>
+    <t>3051 - EMPRESA DE PESQUISA AGROPECUARIA DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>EPAMIG</t>
+  </si>
+  <si>
+    <t>4091 - FUNDO PARA A INFANCIA E A ADOLESCENCIA</t>
+  </si>
+  <si>
+    <t>FIA</t>
+  </si>
+  <si>
+    <t>4101 - FUNDO ESTADUAL DE HABITACAO</t>
+  </si>
+  <si>
+    <t>FEH</t>
+  </si>
+  <si>
+    <t>4141 - FUNDO PENITENCIARIO ESTADUAL</t>
+  </si>
+  <si>
+    <t>FPE</t>
+  </si>
+  <si>
+    <t>4251 - FUNDO ESTADUAL DE ASSISTENCIA SOCIAL</t>
+  </si>
+  <si>
+    <t>FEAS</t>
+  </si>
+  <si>
+    <t>4291 - FUNDO ESTADUAL DE SAUDE</t>
+  </si>
+  <si>
+    <t>FES</t>
+  </si>
+  <si>
+    <t>4331 - FUNDO DE DESENVOLVIMENTO METROPOLITANO</t>
+  </si>
+  <si>
+    <t>FDM</t>
+  </si>
+  <si>
+    <t>4341 - FUNDO DE RECUPERACAO, PROTECAO E DESENVOLVIMENTO SUSTENTAVEL DAS BACIAS HIDROGRAFICAS DO ESTADO DE M</t>
+  </si>
+  <si>
+    <t>FHIDRO</t>
+  </si>
+  <si>
+    <t>4381 - FUNDO ESTADUAL DE DESENVOLVIMENTO DE TRANSPORTES</t>
+  </si>
+  <si>
+    <t>FUNTRANS</t>
+  </si>
+  <si>
+    <t>4451 - FUNDO ESTADUAL DE PROTECAO E DEFESA DO CONSUMIDOR</t>
+  </si>
+  <si>
+    <t>FEPDC</t>
+  </si>
+  <si>
+    <t>4491 - FUNDO ESTADUAL DE CULTURA</t>
+  </si>
+  <si>
+    <t>FEC</t>
+  </si>
+  <si>
+    <t>4541 - FUNDO DE APOIO HABITACIONAL AOS MILITARES DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>FAHMEMG</t>
+  </si>
+  <si>
+    <t>4551 - FUNDO DE ASSISTENCIA AO PECULIO DOS SERVIDORES DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>FUNAPEC</t>
+  </si>
+  <si>
+    <t>4601 - FUNDO ESTADUAL DOS DIREITOS DO IDOSO</t>
+  </si>
+  <si>
+    <t>FEI</t>
+  </si>
+  <si>
+    <t>4691 - FUNDO ESTADUAL DE SEGURANCA PUBLICA DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>FESP-MG</t>
+  </si>
+  <si>
+    <t>4701 - FUNDO ESTADUAL DO TRABALHO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>FET-MG</t>
+  </si>
+  <si>
+    <t>4711 - FUNDO FINANCEIRO DE PREVIDENCIA DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>FFP - MG</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,###,###,###,##0.00"/>
   </numFmts>
@@ -381,39 +598,39 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="0E2841"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="E8E8E8"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="156082"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="E97132"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="196B24"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="0F9ED5"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="A02B93"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="4EA72E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="467886"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="96607D"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -446,9 +663,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -481,6 +715,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -542,13 +793,6 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
@@ -557,6 +801,13 @@
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -621,24 +872,44 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I74"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
-    <col min="2" max="2" width="13.28515625" customWidth="1"/>
-    <col min="3" max="3" width="33.7109375" customWidth="1"/>
+    <col min="2" max="2" width="119.28515625" customWidth="1"/>
+    <col min="3" max="3" width="26.28515625" customWidth="1"/>
     <col min="4" max="6" width="17.28515625" customWidth="1"/>
     <col min="7" max="7" width="21.28515625" customWidth="1"/>
     <col min="8" max="8" width="25.140625" customWidth="1"/>
@@ -646,14 +917,14 @@
     <col min="10" max="10" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="1" customFormat="1" ht="45.4" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" s="1" customFormat="1" ht="34.700000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
@@ -679,11 +950,11 @@
       <c r="A2" s="4">
         <v>2023</v>
       </c>
-      <c r="B2" s="4">
-        <v>1071</v>
+      <c r="B2" s="5" t="s">
+        <v>9</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" s="6">
         <v>46143197.210000001</v>
@@ -708,11 +979,11 @@
       <c r="A3" s="4">
         <v>2023</v>
       </c>
-      <c r="B3" s="4">
-        <v>1081</v>
+      <c r="B3" s="5" t="s">
+        <v>11</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D3" s="6">
         <v>1163303001.26</v>
@@ -737,11 +1008,11 @@
       <c r="A4" s="4">
         <v>2023</v>
       </c>
-      <c r="B4" s="4">
-        <v>1101</v>
+      <c r="B4" s="5" t="s">
+        <v>13</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D4" s="6">
         <v>14788301.67</v>
@@ -766,11 +1037,11 @@
       <c r="A5" s="4">
         <v>2023</v>
       </c>
-      <c r="B5" s="4">
-        <v>1191</v>
+      <c r="B5" s="5" t="s">
+        <v>15</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D5" s="6">
         <v>1549832807.1400001</v>
@@ -795,11 +1066,11 @@
       <c r="A6" s="4">
         <v>2023</v>
       </c>
-      <c r="B6" s="4">
-        <v>1221</v>
+      <c r="B6" s="5" t="s">
+        <v>17</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D6" s="6">
         <v>71019848</v>
@@ -824,11 +1095,11 @@
       <c r="A7" s="4">
         <v>2023</v>
       </c>
-      <c r="B7" s="4">
-        <v>1231</v>
+      <c r="B7" s="5" t="s">
+        <v>19</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D7" s="6">
         <v>157335344.34</v>
@@ -853,11 +1124,11 @@
       <c r="A8" s="4">
         <v>2023</v>
       </c>
-      <c r="B8" s="4">
-        <v>1251</v>
+      <c r="B8" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="D8" s="6">
         <v>13028366670.83</v>
@@ -882,11 +1153,11 @@
       <c r="A9" s="4">
         <v>2023</v>
       </c>
-      <c r="B9" s="4">
-        <v>1261</v>
+      <c r="B9" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D9" s="6">
         <v>17449007243.25</v>
@@ -911,11 +1182,11 @@
       <c r="A10" s="4">
         <v>2023</v>
       </c>
-      <c r="B10" s="4">
-        <v>1271</v>
+      <c r="B10" s="5" t="s">
+        <v>25</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="D10" s="6">
         <v>89313458.840000004</v>
@@ -940,11 +1211,11 @@
       <c r="A11" s="4">
         <v>2023</v>
       </c>
-      <c r="B11" s="4">
-        <v>1301</v>
+      <c r="B11" s="5" t="s">
+        <v>27</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="D11" s="6">
         <v>1210413287.27</v>
@@ -969,11 +1240,11 @@
       <c r="A12" s="4">
         <v>2023</v>
       </c>
-      <c r="B12" s="4">
-        <v>1371</v>
+      <c r="B12" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="D12" s="6">
         <v>208856328.28</v>
@@ -998,11 +1269,11 @@
       <c r="A13" s="4">
         <v>2023</v>
       </c>
-      <c r="B13" s="4">
-        <v>1401</v>
+      <c r="B13" s="5" t="s">
+        <v>31</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="D13" s="6">
         <v>1564505806.6600001</v>
@@ -1027,11 +1298,11 @@
       <c r="A14" s="4">
         <v>2023</v>
       </c>
-      <c r="B14" s="4">
-        <v>1451</v>
+      <c r="B14" s="5" t="s">
+        <v>33</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="D14" s="6">
         <v>3781312622.1199999</v>
@@ -1056,11 +1327,11 @@
       <c r="A15" s="4">
         <v>2023</v>
       </c>
-      <c r="B15" s="4">
-        <v>1481</v>
+      <c r="B15" s="5" t="s">
+        <v>35</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="D15" s="6">
         <v>278200685.86000001</v>
@@ -1085,11 +1356,11 @@
       <c r="A16" s="4">
         <v>2023</v>
       </c>
-      <c r="B16" s="4">
-        <v>1491</v>
+      <c r="B16" s="5" t="s">
+        <v>37</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="D16" s="6">
         <v>614122774.96000004</v>
@@ -1114,11 +1385,11 @@
       <c r="A17" s="4">
         <v>2023</v>
       </c>
-      <c r="B17" s="4">
-        <v>1501</v>
+      <c r="B17" s="5" t="s">
+        <v>39</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="D17" s="6">
         <v>558633697.67999995</v>
@@ -1143,11 +1414,11 @@
       <c r="A18" s="4">
         <v>2023</v>
       </c>
-      <c r="B18" s="4">
-        <v>1511</v>
+      <c r="B18" s="5" t="s">
+        <v>41</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="D18" s="6">
         <v>3065566676.29</v>
@@ -1172,11 +1443,11 @@
       <c r="A19" s="4">
         <v>2023</v>
       </c>
-      <c r="B19" s="4">
-        <v>1521</v>
+      <c r="B19" s="5" t="s">
+        <v>43</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="D19" s="6">
         <v>60102963.539999999</v>
@@ -1201,11 +1472,11 @@
       <c r="A20" s="4">
         <v>2023</v>
       </c>
-      <c r="B20" s="4">
-        <v>1541</v>
+      <c r="B20" s="5" t="s">
+        <v>45</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="D20" s="6">
         <v>19938984.920000002</v>
@@ -1230,11 +1501,11 @@
       <c r="A21" s="4">
         <v>2023</v>
       </c>
-      <c r="B21" s="4">
-        <v>1631</v>
+      <c r="B21" s="5" t="s">
+        <v>47</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="D21" s="6">
         <v>64901564.210000001</v>
@@ -1259,11 +1530,11 @@
       <c r="A22" s="4">
         <v>2023</v>
       </c>
-      <c r="B22" s="4">
-        <v>1711</v>
+      <c r="B22" s="5" t="s">
+        <v>49</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="D22" s="6">
         <v>85247066.049999997</v>
@@ -1282,11 +1553,11 @@
       <c r="A23" s="4">
         <v>2023</v>
       </c>
-      <c r="B23" s="4">
-        <v>1721</v>
+      <c r="B23" s="5" t="s">
+        <v>51</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="D23" s="6">
         <v>5572590.71</v>
@@ -1305,11 +1576,11 @@
       <c r="A24" s="4">
         <v>2023</v>
       </c>
-      <c r="B24" s="4">
-        <v>1911</v>
+      <c r="B24" s="5" t="s">
+        <v>53</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="D24" s="6">
         <v>854860168.33000004</v>
@@ -1334,11 +1605,11 @@
       <c r="A25" s="4">
         <v>2023</v>
       </c>
-      <c r="B25" s="4">
-        <v>1915</v>
+      <c r="B25" s="5" t="s">
+        <v>55</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="D25" s="6">
         <v>508647503.19999999</v>
@@ -1363,11 +1634,11 @@
       <c r="A26" s="4">
         <v>2023</v>
       </c>
-      <c r="B26" s="4">
-        <v>1916</v>
+      <c r="B26" s="5" t="s">
+        <v>57</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="D26" s="6">
         <v>4151422885</v>
@@ -1392,11 +1663,11 @@
       <c r="A27" s="4">
         <v>2023</v>
       </c>
-      <c r="B27" s="4">
-        <v>1941</v>
+      <c r="B27" s="5" t="s">
+        <v>59</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="D27" s="6">
         <v>196770413.59</v>
@@ -1421,11 +1692,11 @@
       <c r="A28" s="4">
         <v>2023</v>
       </c>
-      <c r="B28" s="4">
-        <v>2011</v>
+      <c r="B28" s="5" t="s">
+        <v>61</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="D28" s="6">
         <v>1616992072.96</v>
@@ -1450,11 +1721,11 @@
       <c r="A29" s="4">
         <v>2023</v>
       </c>
-      <c r="B29" s="4">
-        <v>2041</v>
+      <c r="B29" s="5" t="s">
+        <v>63</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>36</v>
+        <v>64</v>
       </c>
       <c r="D29" s="6">
         <v>3423162.82</v>
@@ -1479,11 +1750,11 @@
       <c r="A30" s="4">
         <v>2023</v>
       </c>
-      <c r="B30" s="4">
-        <v>2061</v>
+      <c r="B30" s="5" t="s">
+        <v>65</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>37</v>
+        <v>66</v>
       </c>
       <c r="D30" s="6">
         <v>65473442.710000001</v>
@@ -1508,11 +1779,11 @@
       <c r="A31" s="4">
         <v>2023</v>
       </c>
-      <c r="B31" s="4">
-        <v>2071</v>
+      <c r="B31" s="5" t="s">
+        <v>67</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="D31" s="6">
         <v>475574938.69</v>
@@ -1537,11 +1808,11 @@
       <c r="A32" s="4">
         <v>2023</v>
       </c>
-      <c r="B32" s="4">
-        <v>2091</v>
+      <c r="B32" s="5" t="s">
+        <v>69</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="D32" s="6">
         <v>43259418.770000003</v>
@@ -1566,11 +1837,11 @@
       <c r="A33" s="4">
         <v>2023</v>
       </c>
-      <c r="B33" s="4">
-        <v>2101</v>
+      <c r="B33" s="5" t="s">
+        <v>71</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="D33" s="6">
         <v>206253448.78999999</v>
@@ -1595,11 +1866,11 @@
       <c r="A34" s="4">
         <v>2023</v>
       </c>
-      <c r="B34" s="4">
-        <v>2121</v>
+      <c r="B34" s="5" t="s">
+        <v>73</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>41</v>
+        <v>74</v>
       </c>
       <c r="D34" s="6">
         <v>2900878606.77</v>
@@ -1624,11 +1895,11 @@
       <c r="A35" s="4">
         <v>2023</v>
       </c>
-      <c r="B35" s="4">
-        <v>2151</v>
+      <c r="B35" s="5" t="s">
+        <v>75</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>42</v>
+        <v>76</v>
       </c>
       <c r="D35" s="6">
         <v>64938007.380000003</v>
@@ -1653,11 +1924,11 @@
       <c r="A36" s="4">
         <v>2023</v>
       </c>
-      <c r="B36" s="4">
-        <v>2161</v>
+      <c r="B36" s="5" t="s">
+        <v>77</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>43</v>
+        <v>78</v>
       </c>
       <c r="D36" s="6">
         <v>10901641.689999999</v>
@@ -1682,11 +1953,11 @@
       <c r="A37" s="4">
         <v>2023</v>
       </c>
-      <c r="B37" s="4">
-        <v>2171</v>
+      <c r="B37" s="5" t="s">
+        <v>79</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="D37" s="6">
         <v>4750004.05</v>
@@ -1711,11 +1982,11 @@
       <c r="A38" s="4">
         <v>2023</v>
       </c>
-      <c r="B38" s="4">
-        <v>2181</v>
+      <c r="B38" s="5" t="s">
+        <v>81</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>45</v>
+        <v>82</v>
       </c>
       <c r="D38" s="6">
         <v>49628398.030000001</v>
@@ -1740,11 +2011,11 @@
       <c r="A39" s="4">
         <v>2023</v>
       </c>
-      <c r="B39" s="4">
-        <v>2201</v>
+      <c r="B39" s="5" t="s">
+        <v>83</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>46</v>
+        <v>84</v>
       </c>
       <c r="D39" s="6">
         <v>20854647.149999999</v>
@@ -1769,11 +2040,11 @@
       <c r="A40" s="4">
         <v>2023</v>
       </c>
-      <c r="B40" s="4">
-        <v>2211</v>
+      <c r="B40" s="5" t="s">
+        <v>85</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>47</v>
+        <v>86</v>
       </c>
       <c r="D40" s="6">
         <v>16156823.34</v>
@@ -1798,11 +2069,11 @@
       <c r="A41" s="4">
         <v>2023</v>
       </c>
-      <c r="B41" s="4">
-        <v>2241</v>
+      <c r="B41" s="5" t="s">
+        <v>87</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>48</v>
+        <v>88</v>
       </c>
       <c r="D41" s="6">
         <v>106797429.43000001</v>
@@ -1827,11 +2098,11 @@
       <c r="A42" s="4">
         <v>2023</v>
       </c>
-      <c r="B42" s="4">
-        <v>2251</v>
+      <c r="B42" s="5" t="s">
+        <v>89</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="D42" s="6">
         <v>30826852.399999999</v>
@@ -1856,11 +2127,11 @@
       <c r="A43" s="4">
         <v>2023</v>
       </c>
-      <c r="B43" s="4">
-        <v>2261</v>
+      <c r="B43" s="5" t="s">
+        <v>91</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>50</v>
+        <v>92</v>
       </c>
       <c r="D43" s="6">
         <v>368684570.20999998</v>
@@ -1885,11 +2156,11 @@
       <c r="A44" s="4">
         <v>2023</v>
       </c>
-      <c r="B44" s="4">
-        <v>2271</v>
+      <c r="B44" s="5" t="s">
+        <v>93</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>51</v>
+        <v>94</v>
       </c>
       <c r="D44" s="6">
         <v>2164150549.4200001</v>
@@ -1914,11 +2185,11 @@
       <c r="A45" s="4">
         <v>2023</v>
       </c>
-      <c r="B45" s="4">
-        <v>2281</v>
+      <c r="B45" s="5" t="s">
+        <v>95</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>52</v>
+        <v>96</v>
       </c>
       <c r="D45" s="6">
         <v>6125588.9400000004</v>
@@ -1943,11 +2214,11 @@
       <c r="A46" s="4">
         <v>2023</v>
       </c>
-      <c r="B46" s="4">
-        <v>2301</v>
+      <c r="B46" s="5" t="s">
+        <v>97</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>53</v>
+        <v>98</v>
       </c>
       <c r="D46" s="6">
         <v>1914847566.8499999</v>
@@ -1972,11 +2243,11 @@
       <c r="A47" s="4">
         <v>2023</v>
       </c>
-      <c r="B47" s="4">
-        <v>2311</v>
+      <c r="B47" s="5" t="s">
+        <v>99</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>54</v>
+        <v>100</v>
       </c>
       <c r="D47" s="6">
         <v>469927618.13</v>
@@ -2001,11 +2272,11 @@
       <c r="A48" s="4">
         <v>2023</v>
       </c>
-      <c r="B48" s="4">
-        <v>2321</v>
+      <c r="B48" s="5" t="s">
+        <v>101</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>55</v>
+        <v>102</v>
       </c>
       <c r="D48" s="6">
         <v>355203535.23000002</v>
@@ -2030,11 +2301,11 @@
       <c r="A49" s="4">
         <v>2023</v>
       </c>
-      <c r="B49" s="4">
-        <v>2331</v>
+      <c r="B49" s="5" t="s">
+        <v>103</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>56</v>
+        <v>104</v>
       </c>
       <c r="D49" s="6">
         <v>30989568.550000001</v>
@@ -2059,11 +2330,11 @@
       <c r="A50" s="4">
         <v>2023</v>
       </c>
-      <c r="B50" s="4">
-        <v>2351</v>
+      <c r="B50" s="5" t="s">
+        <v>105</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>57</v>
+        <v>106</v>
       </c>
       <c r="D50" s="6">
         <v>404521667.47000003</v>
@@ -2088,11 +2359,11 @@
       <c r="A51" s="4">
         <v>2023</v>
       </c>
-      <c r="B51" s="4">
-        <v>2371</v>
+      <c r="B51" s="5" t="s">
+        <v>107</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>58</v>
+        <v>108</v>
       </c>
       <c r="D51" s="6">
         <v>247119982.84</v>
@@ -2117,11 +2388,11 @@
       <c r="A52" s="4">
         <v>2023</v>
       </c>
-      <c r="B52" s="4">
-        <v>2421</v>
+      <c r="B52" s="5" t="s">
+        <v>109</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>59</v>
+        <v>110</v>
       </c>
       <c r="D52" s="6">
         <v>100992421.23999999</v>
@@ -2146,11 +2417,11 @@
       <c r="A53" s="4">
         <v>2023</v>
       </c>
-      <c r="B53" s="4">
-        <v>2431</v>
+      <c r="B53" s="5" t="s">
+        <v>111</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>60</v>
+        <v>112</v>
       </c>
       <c r="D53" s="6">
         <v>6692249.8799999999</v>
@@ -2175,11 +2446,11 @@
       <c r="A54" s="4">
         <v>2023</v>
       </c>
-      <c r="B54" s="4">
-        <v>2441</v>
+      <c r="B54" s="5" t="s">
+        <v>113</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>61</v>
+        <v>114</v>
       </c>
       <c r="D54" s="6">
         <v>17351140.010000002</v>
@@ -2204,11 +2475,11 @@
       <c r="A55" s="4">
         <v>2023</v>
       </c>
-      <c r="B55" s="4">
-        <v>2461</v>
+      <c r="B55" s="5" t="s">
+        <v>115</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>62</v>
+        <v>116</v>
       </c>
       <c r="D55" s="6">
         <v>3919274.27</v>
@@ -2233,11 +2504,11 @@
       <c r="A56" s="4">
         <v>2023</v>
       </c>
-      <c r="B56" s="4">
-        <v>3041</v>
+      <c r="B56" s="5" t="s">
+        <v>117</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>63</v>
+        <v>118</v>
       </c>
       <c r="D56" s="6">
         <v>360362919.20999998</v>
@@ -2256,11 +2527,11 @@
       <c r="A57" s="4">
         <v>2023</v>
       </c>
-      <c r="B57" s="4">
-        <v>3051</v>
+      <c r="B57" s="5" t="s">
+        <v>119</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>64</v>
+        <v>120</v>
       </c>
       <c r="D57" s="6">
         <v>129507075.06</v>
@@ -2279,11 +2550,11 @@
       <c r="A58" s="4">
         <v>2023</v>
       </c>
-      <c r="B58" s="4">
-        <v>4091</v>
+      <c r="B58" s="5" t="s">
+        <v>121</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>65</v>
+        <v>122</v>
       </c>
       <c r="D58" s="6">
         <v>7031581.25</v>
@@ -2308,11 +2579,11 @@
       <c r="A59" s="4">
         <v>2023</v>
       </c>
-      <c r="B59" s="4">
-        <v>4101</v>
+      <c r="B59" s="5" t="s">
+        <v>123</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>66</v>
+        <v>124</v>
       </c>
       <c r="D59" s="6">
         <v>16882559.960000001</v>
@@ -2337,11 +2608,11 @@
       <c r="A60" s="4">
         <v>2023</v>
       </c>
-      <c r="B60" s="4">
-        <v>4141</v>
+      <c r="B60" s="5" t="s">
+        <v>125</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>67</v>
+        <v>126</v>
       </c>
       <c r="D60" s="6">
         <v>40613382.549999997</v>
@@ -2366,11 +2637,11 @@
       <c r="A61" s="4">
         <v>2023</v>
       </c>
-      <c r="B61" s="4">
-        <v>4251</v>
+      <c r="B61" s="5" t="s">
+        <v>127</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>68</v>
+        <v>128</v>
       </c>
       <c r="D61" s="6">
         <v>110854339.84999999</v>
@@ -2395,11 +2666,11 @@
       <c r="A62" s="4">
         <v>2023</v>
       </c>
-      <c r="B62" s="4">
-        <v>4291</v>
+      <c r="B62" s="5" t="s">
+        <v>129</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>69</v>
+        <v>130</v>
       </c>
       <c r="D62" s="6">
         <v>11302215537.530001</v>
@@ -2424,11 +2695,11 @@
       <c r="A63" s="4">
         <v>2023</v>
       </c>
-      <c r="B63" s="4">
-        <v>4331</v>
+      <c r="B63" s="5" t="s">
+        <v>131</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>70</v>
+        <v>132</v>
       </c>
       <c r="D63" s="6">
         <v>652279.16</v>
@@ -2447,11 +2718,11 @@
       <c r="A64" s="4">
         <v>2023</v>
       </c>
-      <c r="B64" s="4">
-        <v>4341</v>
+      <c r="B64" s="5" t="s">
+        <v>133</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>71</v>
+        <v>134</v>
       </c>
       <c r="D64" s="6">
         <v>3424799.42</v>
@@ -2476,11 +2747,11 @@
       <c r="A65" s="4">
         <v>2023</v>
       </c>
-      <c r="B65" s="4">
-        <v>4381</v>
+      <c r="B65" s="5" t="s">
+        <v>135</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>72</v>
+        <v>136</v>
       </c>
       <c r="D65" s="6">
         <v>93182744.760000005</v>
@@ -2505,11 +2776,11 @@
       <c r="A66" s="4">
         <v>2023</v>
       </c>
-      <c r="B66" s="4">
-        <v>4451</v>
+      <c r="B66" s="5" t="s">
+        <v>137</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>73</v>
+        <v>138</v>
       </c>
       <c r="D66" s="6">
         <v>35323915.030000001</v>
@@ -2534,11 +2805,11 @@
       <c r="A67" s="4">
         <v>2023</v>
       </c>
-      <c r="B67" s="4">
-        <v>4491</v>
+      <c r="B67" s="5" t="s">
+        <v>139</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>74</v>
+        <v>140</v>
       </c>
       <c r="D67" s="6">
         <v>3940069.61</v>
@@ -2563,11 +2834,11 @@
       <c r="A68" s="4">
         <v>2023</v>
       </c>
-      <c r="B68" s="4">
-        <v>4541</v>
+      <c r="B68" s="5" t="s">
+        <v>141</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>75</v>
+        <v>142</v>
       </c>
       <c r="D68" s="6">
         <v>362500</v>
@@ -2592,11 +2863,11 @@
       <c r="A69" s="4">
         <v>2023</v>
       </c>
-      <c r="B69" s="4">
-        <v>4551</v>
+      <c r="B69" s="5" t="s">
+        <v>143</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>76</v>
+        <v>144</v>
       </c>
       <c r="D69" s="6">
         <v>72736739.480000004</v>
@@ -2621,11 +2892,11 @@
       <c r="A70" s="4">
         <v>2023</v>
       </c>
-      <c r="B70" s="4">
-        <v>4601</v>
+      <c r="B70" s="5" t="s">
+        <v>145</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>77</v>
+        <v>146</v>
       </c>
       <c r="D70" s="6">
         <v>2887433.54</v>
@@ -2650,11 +2921,11 @@
       <c r="A71" s="4">
         <v>2023</v>
       </c>
-      <c r="B71" s="4">
-        <v>4691</v>
+      <c r="B71" s="5" t="s">
+        <v>147</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>78</v>
+        <v>148</v>
       </c>
       <c r="D71" s="6">
         <v>56928753.649999999</v>
@@ -2679,11 +2950,11 @@
       <c r="A72" s="4">
         <v>2023</v>
       </c>
-      <c r="B72" s="4">
-        <v>4701</v>
+      <c r="B72" s="5" t="s">
+        <v>149</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>79</v>
+        <v>150</v>
       </c>
       <c r="D72" s="6">
         <v>481821.71</v>
@@ -2708,11 +2979,11 @@
       <c r="A73" s="4">
         <v>2023</v>
       </c>
-      <c r="B73" s="4">
-        <v>4711</v>
+      <c r="B73" s="5" t="s">
+        <v>151</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>80</v>
+        <v>152</v>
       </c>
       <c r="D73" s="6">
         <v>16707308683.780001</v>

--- a/upload/orgao2023.xlsx
+++ b/upload/orgao2023.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/upload/orgao2023.xlsx
+++ b/upload/orgao2023.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J73"/>
+  <dimension ref="A1:J74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -840,25 +840,25 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>EPAMIG</t>
+          <t>EMC</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3051</v>
+        <v>3151</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>EMPRESA DE PESQUISA AGROPECUARIA DE MINAS GERAIS</t>
+          <t>EMPRESA MINEIRA DE COMUNICACAO</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>129507075.06</v>
+        <v>21506861.17</v>
       </c>
       <c r="F12" t="n">
-        <v>129507075.06</v>
+        <v>21506861.17</v>
       </c>
       <c r="G12" t="n">
-        <v>129507075.06</v>
+        <v>21506861.17</v>
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
@@ -870,35 +870,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ESP MG</t>
+          <t>EPAMIG</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1541</v>
+        <v>3051</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>ESCOLA DE SAUDE PUBLICA DO ESTADO DE MINAS GERAIS</t>
+          <t>EMPRESA DE PESQUISA AGROPECUARIA DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>19938984.92</v>
+        <v>129507075.06</v>
       </c>
       <c r="F13" t="n">
-        <v>19458800.92</v>
+        <v>129507075.06</v>
       </c>
       <c r="G13" t="n">
-        <v>19168057.7</v>
-      </c>
-      <c r="H13" t="n">
-        <v>8211.5</v>
-      </c>
-      <c r="I13" t="n">
-        <v>116097.68</v>
-      </c>
-      <c r="J13" t="n">
-        <v>124309.18</v>
-      </c>
+        <v>129507075.06</v>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -906,34 +900,34 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>FAHMEMG</t>
+          <t>ESP MG</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>4541</v>
+        <v>1541</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>FUNDO DE APOIO HABITACIONAL AOS MILITARES DO ESTADO DE MINAS GERAIS</t>
+          <t>ESCOLA DE SAUDE PUBLICA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>362500</v>
+        <v>19938984.92</v>
       </c>
       <c r="F14" t="n">
-        <v>327310.98</v>
+        <v>19458800.92</v>
       </c>
       <c r="G14" t="n">
-        <v>320259.33</v>
+        <v>19168057.7</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>8211.5</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>116097.68</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>124309.18</v>
       </c>
     </row>
     <row r="15">
@@ -942,34 +936,34 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>FAOP</t>
+          <t>FAHMEMG</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2171</v>
+        <v>4541</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>FUNDACAO DE ARTE DE OURO PRETO</t>
+          <t>FUNDO DE APOIO HABITACIONAL AOS MILITARES DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4750004.05</v>
+        <v>362500</v>
       </c>
       <c r="F15" t="n">
-        <v>4345485.27</v>
+        <v>327310.98</v>
       </c>
       <c r="G15" t="n">
-        <v>4163957.5</v>
+        <v>320259.33</v>
       </c>
       <c r="H15" t="n">
-        <v>27405.6</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>295215.94</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>322621.54</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -978,34 +972,34 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>FAPEMIG</t>
+          <t>FAOP</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2071</v>
+        <v>2171</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>FUNDACAO DE AMPARO A PESQUISA DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDACAO DE ARTE DE OURO PRETO</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>475574938.69</v>
+        <v>4750004.05</v>
       </c>
       <c r="F16" t="n">
-        <v>469867300.36</v>
+        <v>4345485.27</v>
       </c>
       <c r="G16" t="n">
-        <v>420221524.1</v>
+        <v>4163957.5</v>
       </c>
       <c r="H16" t="n">
-        <v>12738999.81</v>
+        <v>27405.6</v>
       </c>
       <c r="I16" t="n">
-        <v>7274018.25</v>
+        <v>295215.94</v>
       </c>
       <c r="J16" t="n">
-        <v>20013018.06</v>
+        <v>322621.54</v>
       </c>
     </row>
     <row r="17">
@@ -1014,34 +1008,34 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>FCS</t>
+          <t>FAPEMIG</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2181</v>
+        <v>2071</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>FUNDACAO CLOVIS SALGADO</t>
+          <t>FUNDACAO DE AMPARO A PESQUISA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>49628398.03</v>
+        <v>475574938.69</v>
       </c>
       <c r="F17" t="n">
-        <v>47405823.66</v>
+        <v>469867300.36</v>
       </c>
       <c r="G17" t="n">
-        <v>46275247.85</v>
+        <v>420221524.1</v>
       </c>
       <c r="H17" t="n">
-        <v>253.4</v>
+        <v>12738999.81</v>
       </c>
       <c r="I17" t="n">
-        <v>878433.0699999999</v>
+        <v>7274018.25</v>
       </c>
       <c r="J17" t="n">
-        <v>878686.47</v>
+        <v>20013018.06</v>
       </c>
     </row>
     <row r="18">
@@ -1050,29 +1044,35 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>FDM</t>
+          <t>FCS</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>4331</v>
+        <v>2181</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>FUNDO DE DESENVOLVIMENTO METROPOLITANO</t>
+          <t>FUNDACAO CLOVIS SALGADO</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>652279.16</v>
+        <v>49628398.03</v>
       </c>
       <c r="F18" t="n">
-        <v>254203.16</v>
+        <v>47405823.66</v>
       </c>
       <c r="G18" t="n">
-        <v>245243.42</v>
-      </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+        <v>46275247.85</v>
+      </c>
+      <c r="H18" t="n">
+        <v>253.4</v>
+      </c>
+      <c r="I18" t="n">
+        <v>878433.0699999999</v>
+      </c>
+      <c r="J18" t="n">
+        <v>878686.47</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1080,35 +1080,29 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>FEAM</t>
+          <t>FDM</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2091</v>
+        <v>4331</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>FUNDACAO ESTADUAL DO MEIO AMBIENTE</t>
+          <t>FUNDO DE DESENVOLVIMENTO METROPOLITANO</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>43259418.77</v>
+        <v>652279.16</v>
       </c>
       <c r="F19" t="n">
-        <v>38126464.75</v>
+        <v>254203.16</v>
       </c>
       <c r="G19" t="n">
-        <v>37435935.06</v>
-      </c>
-      <c r="H19" t="n">
-        <v>95.91</v>
-      </c>
-      <c r="I19" t="n">
-        <v>37153.49</v>
-      </c>
-      <c r="J19" t="n">
-        <v>37249.4</v>
-      </c>
+        <v>245243.42</v>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1116,34 +1110,34 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>FEAS</t>
+          <t>FEAM</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4251</v>
+        <v>2091</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE ASSISTENCIA SOCIAL</t>
+          <t>FUNDACAO ESTADUAL DO MEIO AMBIENTE</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>110854339.85</v>
+        <v>43259418.77</v>
       </c>
       <c r="F20" t="n">
-        <v>106583471.83</v>
+        <v>38126464.75</v>
       </c>
       <c r="G20" t="n">
-        <v>105151900.42</v>
+        <v>37435935.06</v>
       </c>
       <c r="H20" t="n">
-        <v>12672808.3</v>
+        <v>95.91</v>
       </c>
       <c r="I20" t="n">
-        <v>17248454.85</v>
+        <v>37153.49</v>
       </c>
       <c r="J20" t="n">
-        <v>29921263.15</v>
+        <v>37249.4</v>
       </c>
     </row>
     <row r="21">
@@ -1152,34 +1146,34 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>FEC</t>
+          <t>FEAS</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>4491</v>
+        <v>4251</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE CULTURA</t>
+          <t>FUNDO ESTADUAL DE ASSISTENCIA SOCIAL</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3940069.61</v>
+        <v>110854339.85</v>
       </c>
       <c r="F21" t="n">
-        <v>3940069.61</v>
+        <v>106583471.83</v>
       </c>
       <c r="G21" t="n">
-        <v>3184573.65</v>
+        <v>105151900.42</v>
       </c>
       <c r="H21" t="n">
-        <v>390021.88</v>
+        <v>12672808.3</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>17248454.85</v>
       </c>
       <c r="J21" t="n">
-        <v>390021.88</v>
+        <v>29921263.15</v>
       </c>
     </row>
     <row r="22">
@@ -1188,34 +1182,34 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>FEH</t>
+          <t>FEC</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>4101</v>
+        <v>4491</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE HABITACAO</t>
+          <t>FUNDO ESTADUAL DE CULTURA</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>16882559.96</v>
+        <v>3940069.61</v>
       </c>
       <c r="F22" t="n">
-        <v>15883952.89</v>
+        <v>3940069.61</v>
       </c>
       <c r="G22" t="n">
-        <v>15883952.89</v>
+        <v>3184573.65</v>
       </c>
       <c r="H22" t="n">
+        <v>390021.88</v>
+      </c>
+      <c r="I22" t="n">
         <v>0</v>
       </c>
-      <c r="I22" t="n">
-        <v>707987.39</v>
-      </c>
       <c r="J22" t="n">
-        <v>707987.39</v>
+        <v>390021.88</v>
       </c>
     </row>
     <row r="23">
@@ -1224,34 +1218,34 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>FEI</t>
+          <t>FEH</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>4601</v>
+        <v>4101</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DOS DIREITOS DO IDOSO</t>
+          <t>FUNDO ESTADUAL DE HABITACAO</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2887433.54</v>
+        <v>16882559.96</v>
       </c>
       <c r="F23" t="n">
-        <v>2887433.54</v>
+        <v>15883952.89</v>
       </c>
       <c r="G23" t="n">
+        <v>15883952.89</v>
+      </c>
+      <c r="H23" t="n">
         <v>0</v>
       </c>
-      <c r="H23" t="n">
-        <v>180000</v>
-      </c>
       <c r="I23" t="n">
-        <v>45000</v>
+        <v>707987.39</v>
       </c>
       <c r="J23" t="n">
-        <v>225000</v>
+        <v>707987.39</v>
       </c>
     </row>
     <row r="24">
@@ -1260,34 +1254,34 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>FEPDC</t>
+          <t>FEI</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>4451</v>
+        <v>4601</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE PROTECAO E DEFESA DO CONSUMIDOR</t>
+          <t>FUNDO ESTADUAL DOS DIREITOS DO IDOSO</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>35323915.03</v>
+        <v>2887433.54</v>
       </c>
       <c r="F24" t="n">
-        <v>16775518.72</v>
+        <v>2887433.54</v>
       </c>
       <c r="G24" t="n">
-        <v>15712214.16</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1711.42</v>
+        <v>180000</v>
       </c>
       <c r="I24" t="n">
-        <v>370032.98</v>
+        <v>45000</v>
       </c>
       <c r="J24" t="n">
-        <v>371744.4</v>
+        <v>225000</v>
       </c>
     </row>
     <row r="25">
@@ -1656,34 +1650,34 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>FUCAM</t>
+          <t>FPP - MG</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>2161</v>
+        <v>4631</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>FUNDACAO EDUCACIONAL CAIO MARTINS</t>
+          <t>FUNDO DE PAGAMENTO DE PARCERIAS PUBLICO - PRIVADAS DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>10901641.69</v>
+        <v>860717853.34</v>
       </c>
       <c r="F35" t="n">
-        <v>10318773.13</v>
+        <v>307011647.13</v>
       </c>
       <c r="G35" t="n">
-        <v>8998548.609999999</v>
+        <v>282507517.43</v>
       </c>
       <c r="H35" t="n">
-        <v>121569.88</v>
+        <v>344621.26</v>
       </c>
       <c r="I35" t="n">
-        <v>1346214.75</v>
+        <v>28865269.27</v>
       </c>
       <c r="J35" t="n">
-        <v>1467784.63</v>
+        <v>29209890.53</v>
       </c>
     </row>
     <row r="36">
@@ -1692,34 +1686,34 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>FUNAPEC</t>
+          <t>FUCAM</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>4551</v>
+        <v>2161</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>FUNDO DE ASSISTENCIA AO PECULIO DOS SERVIDORES DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDACAO EDUCACIONAL CAIO MARTINS</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>72736739.48</v>
+        <v>10901641.69</v>
       </c>
       <c r="F36" t="n">
-        <v>71196549.09</v>
+        <v>10318773.13</v>
       </c>
       <c r="G36" t="n">
-        <v>71168742.39</v>
+        <v>8998548.609999999</v>
       </c>
       <c r="H36" t="n">
-        <v>6853309.77</v>
+        <v>121569.88</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>1346214.75</v>
       </c>
       <c r="J36" t="n">
-        <v>6853309.77</v>
+        <v>1467784.63</v>
       </c>
     </row>
     <row r="37">
@@ -1728,34 +1722,34 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>FUNED</t>
+          <t>FUNAPEC</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>2261</v>
+        <v>4551</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>FUNDACAO EZEQUIEL DIAS</t>
+          <t>FUNDO DE ASSISTENCIA AO PECULIO DOS SERVIDORES DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>368684570.21</v>
+        <v>72736739.48</v>
       </c>
       <c r="F37" t="n">
-        <v>273219748.02</v>
+        <v>71196549.09</v>
       </c>
       <c r="G37" t="n">
-        <v>269618135.07</v>
+        <v>71168742.39</v>
       </c>
       <c r="H37" t="n">
-        <v>8154203.6</v>
+        <v>6853309.77</v>
       </c>
       <c r="I37" t="n">
-        <v>41399163.16</v>
+        <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>49553366.76</v>
+        <v>6853309.77</v>
       </c>
     </row>
     <row r="38">
@@ -1764,34 +1758,34 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>FUNTRANS</t>
+          <t>FUNED</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>4381</v>
+        <v>2261</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE DESENVOLVIMENTO DE TRANSPORTES</t>
+          <t>FUNDACAO EZEQUIEL DIAS</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>93182744.76000001</v>
+        <v>368684570.21</v>
       </c>
       <c r="F38" t="n">
-        <v>73453457.05</v>
+        <v>273219748.02</v>
       </c>
       <c r="G38" t="n">
-        <v>71188066.92</v>
+        <v>269618135.07</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>8154203.6</v>
       </c>
       <c r="I38" t="n">
-        <v>8330157.76</v>
+        <v>41399163.16</v>
       </c>
       <c r="J38" t="n">
-        <v>8330157.76</v>
+        <v>49553366.76</v>
       </c>
     </row>
     <row r="39">
@@ -1800,34 +1794,34 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>GABINETE MILITAR</t>
+          <t>FUNTRANS</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1071</v>
+        <v>4381</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>GABINETE MILITAR DO GOVERNADOR DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDO ESTADUAL DE DESENVOLVIMENTO DE TRANSPORTES</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>46143197.21</v>
+        <v>93182744.76000001</v>
       </c>
       <c r="F39" t="n">
-        <v>35398463.11</v>
+        <v>73453457.05</v>
       </c>
       <c r="G39" t="n">
-        <v>34050957.79</v>
+        <v>71188066.92</v>
       </c>
       <c r="H39" t="n">
-        <v>211337.1</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>3943260.33</v>
+        <v>8330157.76</v>
       </c>
       <c r="J39" t="n">
-        <v>4154597.43</v>
+        <v>8330157.76</v>
       </c>
     </row>
     <row r="40">
@@ -1836,34 +1830,34 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>GDPE - SEF</t>
+          <t>GABINETE MILITAR</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1916</v>
+        <v>1071</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>GESTAO DA DIVIDA PUBLICA ESTADUAL</t>
+          <t>GABINETE MILITAR DO GOVERNADOR DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4151422885</v>
+        <v>46143197.21</v>
       </c>
       <c r="F40" t="n">
-        <v>4151422885</v>
+        <v>35398463.11</v>
       </c>
       <c r="G40" t="n">
-        <v>3992987258.55</v>
+        <v>34050957.79</v>
       </c>
       <c r="H40" t="n">
-        <v>316225142.59</v>
+        <v>211337.1</v>
       </c>
       <c r="I40" t="n">
-        <v>123029711.28</v>
+        <v>3943260.33</v>
       </c>
       <c r="J40" t="n">
-        <v>439254853.87</v>
+        <v>4154597.43</v>
       </c>
     </row>
     <row r="41">
@@ -1872,34 +1866,34 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>HEMOMINAS</t>
+          <t>GDPE - SEF</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>2321</v>
+        <v>1916</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>FUNDACAO CENTRO DE HEMATOLOGIA E HEMOTERAPIA DE MINAS GERAIS</t>
+          <t>GESTAO DA DIVIDA PUBLICA ESTADUAL</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>355203535.23</v>
+        <v>4151422885</v>
       </c>
       <c r="F41" t="n">
-        <v>320246686.79</v>
+        <v>4151422885</v>
       </c>
       <c r="G41" t="n">
-        <v>311999002.94</v>
+        <v>3992987258.55</v>
       </c>
       <c r="H41" t="n">
-        <v>1679096.03</v>
+        <v>316225142.59</v>
       </c>
       <c r="I41" t="n">
-        <v>28146659.99</v>
+        <v>123029711.28</v>
       </c>
       <c r="J41" t="n">
-        <v>29825756.02</v>
+        <v>439254853.87</v>
       </c>
     </row>
     <row r="42">
@@ -1908,34 +1902,34 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>IDENE</t>
+          <t>HEMOMINAS</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>2421</v>
+        <v>2321</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>INSTITUTO DE DESENVOLVIMENTO DO NORTE E NORDESTE DE MINAS GERAIS</t>
+          <t>FUNDACAO CENTRO DE HEMATOLOGIA E HEMOTERAPIA DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100992421.24</v>
+        <v>355203535.23</v>
       </c>
       <c r="F42" t="n">
-        <v>76969361.8</v>
+        <v>320246686.79</v>
       </c>
       <c r="G42" t="n">
-        <v>75625489.05</v>
+        <v>311999002.94</v>
       </c>
       <c r="H42" t="n">
-        <v>163906.27</v>
+        <v>1679096.03</v>
       </c>
       <c r="I42" t="n">
-        <v>6105648.21</v>
+        <v>28146659.99</v>
       </c>
       <c r="J42" t="n">
-        <v>6269554.48</v>
+        <v>29825756.02</v>
       </c>
     </row>
     <row r="43">
@@ -1944,34 +1938,34 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>IEF</t>
+          <t>IDENE</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>2101</v>
+        <v>2421</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>INSTITUTO ESTADUAL DE FLORESTAS</t>
+          <t>INSTITUTO DE DESENVOLVIMENTO DO NORTE E NORDESTE DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>206253448.79</v>
+        <v>100992421.24</v>
       </c>
       <c r="F43" t="n">
-        <v>201049210.28</v>
+        <v>76969361.8</v>
       </c>
       <c r="G43" t="n">
-        <v>193758815.18</v>
+        <v>75625489.05</v>
       </c>
       <c r="H43" t="n">
-        <v>2044943.53</v>
+        <v>163906.27</v>
       </c>
       <c r="I43" t="n">
-        <v>3790350.53</v>
+        <v>6105648.21</v>
       </c>
       <c r="J43" t="n">
-        <v>5835294.06</v>
+        <v>6269554.48</v>
       </c>
     </row>
     <row r="44">
@@ -1980,34 +1974,34 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>IEPHA</t>
+          <t>IEF</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>2201</v>
+        <v>2101</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>INSTITUTO ESTADUAL DO PATRIMONIO HISTORICO E ARTISTICO DE MINAS GERAIS</t>
+          <t>INSTITUTO ESTADUAL DE FLORESTAS</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>20854647.15</v>
+        <v>206253448.79</v>
       </c>
       <c r="F44" t="n">
-        <v>19794515.12</v>
+        <v>201049210.28</v>
       </c>
       <c r="G44" t="n">
-        <v>18916412.23</v>
+        <v>193758815.18</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>2044943.53</v>
       </c>
       <c r="I44" t="n">
-        <v>2810067.14</v>
+        <v>3790350.53</v>
       </c>
       <c r="J44" t="n">
-        <v>2810067.14</v>
+        <v>5835294.06</v>
       </c>
     </row>
     <row r="45">
@@ -2016,34 +2010,34 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>IGAM</t>
+          <t>IEPHA</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>2241</v>
+        <v>2201</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>INSTITUTO MINEIRO DE GESTAO DAS AGUAS</t>
+          <t>INSTITUTO ESTADUAL DO PATRIMONIO HISTORICO E ARTISTICO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>106797429.43</v>
+        <v>20854647.15</v>
       </c>
       <c r="F45" t="n">
-        <v>101404974.15</v>
+        <v>19794515.12</v>
       </c>
       <c r="G45" t="n">
-        <v>100479945.84</v>
+        <v>18916412.23</v>
       </c>
       <c r="H45" t="n">
-        <v>10446834.76</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>3875281.47</v>
+        <v>2810067.14</v>
       </c>
       <c r="J45" t="n">
-        <v>14322116.23</v>
+        <v>2810067.14</v>
       </c>
     </row>
     <row r="46">
@@ -2052,34 +2046,34 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>IMA</t>
+          <t>IGAM</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>2371</v>
+        <v>2241</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>INSTITUTO MINEIRO DE AGROPECUARIA</t>
+          <t>INSTITUTO MINEIRO DE GESTAO DAS AGUAS</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>247119982.84</v>
+        <v>106797429.43</v>
       </c>
       <c r="F46" t="n">
-        <v>242894139.49</v>
+        <v>101404974.15</v>
       </c>
       <c r="G46" t="n">
-        <v>242543975.53</v>
+        <v>100479945.84</v>
       </c>
       <c r="H46" t="n">
-        <v>378714.11</v>
+        <v>10446834.76</v>
       </c>
       <c r="I46" t="n">
-        <v>3948517.78</v>
+        <v>3875281.47</v>
       </c>
       <c r="J46" t="n">
-        <v>4327231.89</v>
+        <v>14322116.23</v>
       </c>
     </row>
     <row r="47">
@@ -2088,34 +2082,34 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>IPEMMG</t>
+          <t>IMA</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>2331</v>
+        <v>2371</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>INSTITUTO DE METROLOGIA E QUALIDADE DO ESTADO DE MINAS GERAIS</t>
+          <t>INSTITUTO MINEIRO DE AGROPECUARIA</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>30989568.55</v>
+        <v>247119982.84</v>
       </c>
       <c r="F47" t="n">
-        <v>30394216.46</v>
+        <v>242894139.49</v>
       </c>
       <c r="G47" t="n">
-        <v>28953199.86</v>
+        <v>242543975.53</v>
       </c>
       <c r="H47" t="n">
-        <v>78441.50999999999</v>
+        <v>378714.11</v>
       </c>
       <c r="I47" t="n">
-        <v>108549.11</v>
+        <v>3948517.78</v>
       </c>
       <c r="J47" t="n">
-        <v>186990.62</v>
+        <v>4327231.89</v>
       </c>
     </row>
     <row r="48">
@@ -2124,34 +2118,34 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>IPSEMG</t>
+          <t>IPEMMG</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>2011</v>
+        <v>2331</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>INSTITUTO DE PREVIDENCIA DOS SERVIDORES DO ESTADO DE MINAS GERAIS</t>
+          <t>INSTITUTO DE METROLOGIA E QUALIDADE DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1616992072.96</v>
+        <v>30989568.55</v>
       </c>
       <c r="F48" t="n">
-        <v>1414919735.8</v>
+        <v>30394216.46</v>
       </c>
       <c r="G48" t="n">
-        <v>1379497007.69</v>
+        <v>28953199.86</v>
       </c>
       <c r="H48" t="n">
-        <v>2730465.24</v>
+        <v>78441.50999999999</v>
       </c>
       <c r="I48" t="n">
-        <v>139505498.51</v>
+        <v>108549.11</v>
       </c>
       <c r="J48" t="n">
-        <v>142235963.75</v>
+        <v>186990.62</v>
       </c>
     </row>
     <row r="49">
@@ -2160,34 +2154,34 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>IPSM</t>
+          <t>IPSEMG</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>2121</v>
+        <v>2011</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>INSTITUTO DE PREVIDENCIA DOS SERVIDORES MILITARES DO ESTADO DE MINAS GERAIS</t>
+          <t>INSTITUTO DE PREVIDENCIA DOS SERVIDORES DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2900878606.77</v>
+        <v>1616992072.96</v>
       </c>
       <c r="F49" t="n">
-        <v>2876463795.17</v>
+        <v>1414919735.8</v>
       </c>
       <c r="G49" t="n">
-        <v>2327341436.54</v>
+        <v>1379497007.69</v>
       </c>
       <c r="H49" t="n">
-        <v>102308456.42</v>
+        <v>2730465.24</v>
       </c>
       <c r="I49" t="n">
-        <v>33347552.64</v>
+        <v>139505498.51</v>
       </c>
       <c r="J49" t="n">
-        <v>135656009.06</v>
+        <v>142235963.75</v>
       </c>
     </row>
     <row r="50">
@@ -2196,34 +2190,34 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>JUCEMG</t>
+          <t>IPSM</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>2251</v>
+        <v>2121</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>JUNTA COMERCIAL DO ESTADO DE MINAS GERAIS</t>
+          <t>INSTITUTO DE PREVIDENCIA DOS SERVIDORES MILITARES DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>30826852.4</v>
+        <v>2900878606.77</v>
       </c>
       <c r="F50" t="n">
-        <v>29563968.03</v>
+        <v>2876463795.17</v>
       </c>
       <c r="G50" t="n">
-        <v>29011549.3</v>
+        <v>2327341436.54</v>
       </c>
       <c r="H50" t="n">
-        <v>565.47</v>
+        <v>102308456.42</v>
       </c>
       <c r="I50" t="n">
-        <v>746119.0600000001</v>
+        <v>33347552.64</v>
       </c>
       <c r="J50" t="n">
-        <v>746684.53</v>
+        <v>135656009.06</v>
       </c>
     </row>
     <row r="51">
@@ -2232,34 +2226,34 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>LEMG</t>
+          <t>JUCEMG</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>2041</v>
+        <v>2251</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LOTERIA DO ESTADO DE MINAS GERAIS</t>
+          <t>JUNTA COMERCIAL DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>3423162.82</v>
+        <v>30826852.4</v>
       </c>
       <c r="F51" t="n">
-        <v>3283189.87</v>
+        <v>29563968.03</v>
       </c>
       <c r="G51" t="n">
-        <v>3280441.52</v>
+        <v>29011549.3</v>
       </c>
       <c r="H51" t="n">
-        <v>0</v>
+        <v>565.47</v>
       </c>
       <c r="I51" t="n">
-        <v>6507</v>
+        <v>746119.0600000001</v>
       </c>
       <c r="J51" t="n">
-        <v>6507</v>
+        <v>746684.53</v>
       </c>
     </row>
     <row r="52">
@@ -2268,34 +2262,34 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>OGE</t>
+          <t>LEMG</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1101</v>
+        <v>2041</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>OUVIDORIA-GERAL DO ESTADO DE MINAS GERAIS</t>
+          <t>LOTERIA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>14788301.67</v>
+        <v>3423162.82</v>
       </c>
       <c r="F52" t="n">
-        <v>14630579.61</v>
+        <v>3283189.87</v>
       </c>
       <c r="G52" t="n">
-        <v>14490566</v>
+        <v>3280441.52</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>94372.77</v>
+        <v>6507</v>
       </c>
       <c r="J52" t="n">
-        <v>94372.77</v>
+        <v>6507</v>
       </c>
     </row>
     <row r="53">
@@ -2304,34 +2298,34 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>PARTICIPAÇÃO EMPRESAS</t>
+          <t>OGE</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1915</v>
+        <v>1101</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>PARTICIPACAO NO AUMENTO DO CAPITAL SOCIAL DE EMPRESAS</t>
+          <t>OUVIDORIA-GERAL DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>508647503.2</v>
+        <v>14788301.67</v>
       </c>
       <c r="F53" t="n">
-        <v>3647503.2</v>
+        <v>14630579.61</v>
       </c>
       <c r="G53" t="n">
-        <v>3647503.2</v>
+        <v>14490566</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
       </c>
       <c r="I53" t="n">
-        <v>75202844.75</v>
+        <v>94372.77</v>
       </c>
       <c r="J53" t="n">
-        <v>75202844.75</v>
+        <v>94372.77</v>
       </c>
     </row>
     <row r="54">
@@ -2340,34 +2334,34 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>PCMG</t>
+          <t>PARTICIPAÇÃO EMPRESAS</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1511</v>
+        <v>1915</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>POLICIA CIVIL DO ESTADO DE MINAS GERAIS</t>
+          <t>PARTICIPACAO NO AUMENTO DO CAPITAL SOCIAL DE EMPRESAS</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>3065566676.29</v>
+        <v>508647503.2</v>
       </c>
       <c r="F54" t="n">
-        <v>2994754625.68</v>
+        <v>3647503.2</v>
       </c>
       <c r="G54" t="n">
-        <v>2978077582.97</v>
+        <v>3647503.2</v>
       </c>
       <c r="H54" t="n">
-        <v>12864618.77</v>
+        <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>79194935.12</v>
+        <v>75202844.75</v>
       </c>
       <c r="J54" t="n">
-        <v>92059553.89</v>
+        <v>75202844.75</v>
       </c>
     </row>
     <row r="55">
@@ -2376,34 +2370,34 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>PMMG</t>
+          <t>PCMG</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1251</v>
+        <v>1511</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>POLICIA MILITAR DO ESTADO DE MINAS GERAIS</t>
+          <t>POLICIA CIVIL DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>13028366670.83</v>
+        <v>3065566676.29</v>
       </c>
       <c r="F55" t="n">
-        <v>12841769394.38</v>
+        <v>2994754625.68</v>
       </c>
       <c r="G55" t="n">
-        <v>12810307610.08</v>
+        <v>2978077582.97</v>
       </c>
       <c r="H55" t="n">
-        <v>36489178.11</v>
+        <v>12864618.77</v>
       </c>
       <c r="I55" t="n">
-        <v>226080162.79</v>
+        <v>79194935.12</v>
       </c>
       <c r="J55" t="n">
-        <v>262569340.9</v>
+        <v>92059553.89</v>
       </c>
     </row>
     <row r="56">
@@ -2412,29 +2406,35 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>SCC</t>
+          <t>PMMG</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1721</v>
+        <v>1251</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DA CASA CIVIL</t>
+          <t>POLICIA MILITAR DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5572590.71</v>
+        <v>13028366670.83</v>
       </c>
       <c r="F56" t="n">
-        <v>5270468.4</v>
+        <v>12841769394.38</v>
       </c>
       <c r="G56" t="n">
-        <v>4983565.3</v>
-      </c>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
+        <v>12810307610.08</v>
+      </c>
+      <c r="H56" t="n">
+        <v>36489178.11</v>
+      </c>
+      <c r="I56" t="n">
+        <v>226080162.79</v>
+      </c>
+      <c r="J56" t="n">
+        <v>262569340.9</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -2442,35 +2442,29 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>SEAPA</t>
+          <t>SCC</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1231</v>
+        <v>1721</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE AGRICULTURA, PECUARIA E ABASTECIMENTO - SEAPA</t>
+          <t>SECRETARIA DE ESTADO DA CASA CIVIL</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>157335344.34</v>
+        <v>5572590.71</v>
       </c>
       <c r="F57" t="n">
-        <v>140995120.89</v>
+        <v>5270468.4</v>
       </c>
       <c r="G57" t="n">
-        <v>122957383.2</v>
-      </c>
-      <c r="H57" t="n">
-        <v>7823519.95</v>
-      </c>
-      <c r="I57" t="n">
-        <v>3775929.39</v>
-      </c>
-      <c r="J57" t="n">
-        <v>11599449.34</v>
-      </c>
+        <v>4983565.3</v>
+      </c>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -2478,34 +2472,34 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>SEC. GERAL</t>
+          <t>SEAPA</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1631</v>
+        <v>1231</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>SECRETARIA-GERAL</t>
+          <t>SECRETARIA DE ESTADO DE AGRICULTURA, PECUARIA E ABASTECIMENTO - SEAPA</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>64901564.21</v>
+        <v>157335344.34</v>
       </c>
       <c r="F58" t="n">
-        <v>59419458.57</v>
+        <v>140995120.89</v>
       </c>
       <c r="G58" t="n">
-        <v>57509982.39</v>
+        <v>122957383.2</v>
       </c>
       <c r="H58" t="n">
-        <v>777.25</v>
+        <v>7823519.95</v>
       </c>
       <c r="I58" t="n">
-        <v>22162487.86</v>
+        <v>3775929.39</v>
       </c>
       <c r="J58" t="n">
-        <v>22163265.11</v>
+        <v>11599449.34</v>
       </c>
     </row>
     <row r="59">
@@ -2514,29 +2508,35 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>SECOM</t>
+          <t>SEC. GERAL</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1711</v>
+        <v>1631</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE COMUNICACAO SOCIAL</t>
+          <t>SECRETARIA-GERAL</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>85247066.05</v>
+        <v>64901564.21</v>
       </c>
       <c r="F59" t="n">
-        <v>32467458.6</v>
+        <v>59419458.57</v>
       </c>
       <c r="G59" t="n">
-        <v>31192326.84</v>
-      </c>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
+        <v>57509982.39</v>
+      </c>
+      <c r="H59" t="n">
+        <v>777.25</v>
+      </c>
+      <c r="I59" t="n">
+        <v>22162487.86</v>
+      </c>
+      <c r="J59" t="n">
+        <v>22163265.11</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -2544,35 +2544,29 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>SECULT</t>
+          <t>SECOM</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1271</v>
+        <v>1711</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE CULTURA E TURISMO</t>
+          <t>SECRETARIA DE ESTADO DE COMUNICACAO SOCIAL</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>89313458.84</v>
+        <v>85247066.05</v>
       </c>
       <c r="F60" t="n">
-        <v>86513089.77</v>
+        <v>32467458.6</v>
       </c>
       <c r="G60" t="n">
-        <v>82380637.92</v>
-      </c>
-      <c r="H60" t="n">
-        <v>1333330.75</v>
-      </c>
-      <c r="I60" t="n">
-        <v>896505.38</v>
-      </c>
-      <c r="J60" t="n">
-        <v>2229836.13</v>
-      </c>
+        <v>31192326.84</v>
+      </c>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -2580,34 +2574,34 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>SEDE</t>
+          <t>SECULT</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1221</v>
+        <v>1271</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONOMICO</t>
+          <t>SECRETARIA DE ESTADO DE CULTURA E TURISMO</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>71019848</v>
+        <v>89313458.84</v>
       </c>
       <c r="F61" t="n">
-        <v>49587285.62</v>
+        <v>86513089.77</v>
       </c>
       <c r="G61" t="n">
-        <v>28903226.95</v>
+        <v>82380637.92</v>
       </c>
       <c r="H61" t="n">
-        <v>468159.26</v>
+        <v>1333330.75</v>
       </c>
       <c r="I61" t="n">
-        <v>8730755.23</v>
+        <v>896505.38</v>
       </c>
       <c r="J61" t="n">
-        <v>9198914.49</v>
+        <v>2229836.13</v>
       </c>
     </row>
     <row r="62">
@@ -2616,34 +2610,34 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>SEDESE</t>
+          <t>SEDE</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1481</v>
+        <v>1221</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONOMICO</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>278200685.86</v>
+        <v>71019848</v>
       </c>
       <c r="F62" t="n">
-        <v>258721057.71</v>
+        <v>49587285.62</v>
       </c>
       <c r="G62" t="n">
-        <v>187380767.61</v>
+        <v>28903226.95</v>
       </c>
       <c r="H62" t="n">
-        <v>13128483.79</v>
+        <v>468159.26</v>
       </c>
       <c r="I62" t="n">
-        <v>14858520.74</v>
+        <v>8730755.23</v>
       </c>
       <c r="J62" t="n">
-        <v>27987004.53</v>
+        <v>9198914.49</v>
       </c>
     </row>
     <row r="63">
@@ -2652,34 +2646,34 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>SEE</t>
+          <t>SEDESE</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>1261</v>
+        <v>1481</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE EDUCACAO</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>17449007243.25</v>
+        <v>278200685.86</v>
       </c>
       <c r="F63" t="n">
-        <v>16913371691.71</v>
+        <v>258721057.71</v>
       </c>
       <c r="G63" t="n">
-        <v>16658293209.57</v>
+        <v>187380767.61</v>
       </c>
       <c r="H63" t="n">
-        <v>258732199.34</v>
+        <v>13128483.79</v>
       </c>
       <c r="I63" t="n">
-        <v>420280749.51</v>
+        <v>14858520.74</v>
       </c>
       <c r="J63" t="n">
-        <v>679012948.85</v>
+        <v>27987004.53</v>
       </c>
     </row>
     <row r="64">
@@ -2688,34 +2682,34 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>SEF</t>
+          <t>SEE</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1191</v>
+        <v>1261</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE FAZENDA</t>
+          <t>SECRETARIA DE ESTADO DE EDUCACAO</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1549832807.14</v>
+        <v>17449007243.25</v>
       </c>
       <c r="F64" t="n">
-        <v>1487682339.64</v>
+        <v>16913371691.71</v>
       </c>
       <c r="G64" t="n">
-        <v>1468478278.25</v>
+        <v>16658293209.57</v>
       </c>
       <c r="H64" t="n">
-        <v>5469083</v>
+        <v>258732199.34</v>
       </c>
       <c r="I64" t="n">
-        <v>34680028.15</v>
+        <v>420280749.51</v>
       </c>
       <c r="J64" t="n">
-        <v>40149111.15</v>
+        <v>679012948.85</v>
       </c>
     </row>
     <row r="65">
@@ -2724,34 +2718,34 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>SEGOV</t>
+          <t>SEF</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1491</v>
+        <v>1191</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE GOVERNO</t>
+          <t>SECRETARIA DE ESTADO DE FAZENDA</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>614122774.96</v>
+        <v>1549832807.14</v>
       </c>
       <c r="F65" t="n">
-        <v>581433110.22</v>
+        <v>1487682339.64</v>
       </c>
       <c r="G65" t="n">
-        <v>577033471.5</v>
+        <v>1468478278.25</v>
       </c>
       <c r="H65" t="n">
-        <v>8649196.529999999</v>
+        <v>5469083</v>
       </c>
       <c r="I65" t="n">
-        <v>27927671.89</v>
+        <v>34680028.15</v>
       </c>
       <c r="J65" t="n">
-        <v>36576868.42</v>
+        <v>40149111.15</v>
       </c>
     </row>
     <row r="66">
@@ -2760,34 +2754,34 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>SEINFRA</t>
+          <t>SEGOV</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1301</v>
+        <v>1491</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIAS</t>
+          <t>SECRETARIA DE ESTADO DE GOVERNO</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1210413287.27</v>
+        <v>614122774.96</v>
       </c>
       <c r="F66" t="n">
-        <v>948715257.75</v>
+        <v>581433110.22</v>
       </c>
       <c r="G66" t="n">
-        <v>820248138.33</v>
+        <v>577033471.5</v>
       </c>
       <c r="H66" t="n">
-        <v>79551005.90000001</v>
+        <v>8649196.529999999</v>
       </c>
       <c r="I66" t="n">
-        <v>47275927.88</v>
+        <v>27927671.89</v>
       </c>
       <c r="J66" t="n">
-        <v>126826933.78</v>
+        <v>36576868.42</v>
       </c>
     </row>
     <row r="67">
@@ -2796,34 +2790,34 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>SEJUSP</t>
+          <t>SEINFRA</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1451</v>
+        <v>1301</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE JUSTICA E SEGURANCA PUBLICA</t>
+          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIAS</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>3781312622.12</v>
+        <v>1210413287.27</v>
       </c>
       <c r="F67" t="n">
-        <v>3625298484.23</v>
+        <v>948715257.75</v>
       </c>
       <c r="G67" t="n">
-        <v>3596218710.39</v>
+        <v>820248138.33</v>
       </c>
       <c r="H67" t="n">
-        <v>19811807.26</v>
+        <v>79551005.90000001</v>
       </c>
       <c r="I67" t="n">
-        <v>100572066.62</v>
+        <v>47275927.88</v>
       </c>
       <c r="J67" t="n">
-        <v>120383873.88</v>
+        <v>126826933.78</v>
       </c>
     </row>
     <row r="68">
@@ -2832,34 +2826,34 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>SEMAD</t>
+          <t>SEJUSP</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1371</v>
+        <v>1451</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTAVEL</t>
+          <t>SECRETARIA DE ESTADO DE JUSTICA E SEGURANCA PUBLICA</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>208856328.28</v>
+        <v>3781312622.12</v>
       </c>
       <c r="F68" t="n">
-        <v>202130317.06</v>
+        <v>3625298484.23</v>
       </c>
       <c r="G68" t="n">
-        <v>183745409.62</v>
+        <v>3596218710.39</v>
       </c>
       <c r="H68" t="n">
-        <v>3452019.16</v>
+        <v>19811807.26</v>
       </c>
       <c r="I68" t="n">
-        <v>2453491.44</v>
+        <v>100572066.62</v>
       </c>
       <c r="J68" t="n">
-        <v>5905510.6</v>
+        <v>120383873.88</v>
       </c>
     </row>
     <row r="69">
@@ -2868,34 +2862,34 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>SEPLAG</t>
+          <t>SEMAD</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1501</v>
+        <v>1371</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTAO</t>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTAVEL</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>558633697.6799999</v>
+        <v>208856328.28</v>
       </c>
       <c r="F69" t="n">
-        <v>499616023.57</v>
+        <v>202130317.06</v>
       </c>
       <c r="G69" t="n">
-        <v>469179324</v>
+        <v>183745409.62</v>
       </c>
       <c r="H69" t="n">
-        <v>3809874.58</v>
+        <v>3452019.16</v>
       </c>
       <c r="I69" t="n">
-        <v>18299317.45</v>
+        <v>2453491.44</v>
       </c>
       <c r="J69" t="n">
-        <v>22109192.03</v>
+        <v>5905510.6</v>
       </c>
     </row>
     <row r="70">
@@ -2904,34 +2898,34 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>TV MINAS</t>
+          <t>SEPLAG</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>2211</v>
+        <v>1501</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>FUNDACAO TV MINAS CULTURAL E EDUCATIVA</t>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTAO</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>16156823.34</v>
+        <v>558633697.6799999</v>
       </c>
       <c r="F70" t="n">
-        <v>15396119.26</v>
+        <v>499616023.57</v>
       </c>
       <c r="G70" t="n">
-        <v>14519942.39</v>
+        <v>469179324</v>
       </c>
       <c r="H70" t="n">
-        <v>113058.43</v>
+        <v>3809874.58</v>
       </c>
       <c r="I70" t="n">
-        <v>599716.37</v>
+        <v>18299317.45</v>
       </c>
       <c r="J70" t="n">
-        <v>712774.8</v>
+        <v>22109192.03</v>
       </c>
     </row>
     <row r="71">
@@ -2940,34 +2934,34 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>UEMG</t>
+          <t>TV MINAS</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>2351</v>
+        <v>2211</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>UNIVERSIDADE DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDACAO TV MINAS CULTURAL E EDUCATIVA</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>404521667.47</v>
+        <v>16156823.34</v>
       </c>
       <c r="F71" t="n">
-        <v>384928295.57</v>
+        <v>15396119.26</v>
       </c>
       <c r="G71" t="n">
-        <v>374712336.29</v>
+        <v>14519942.39</v>
       </c>
       <c r="H71" t="n">
-        <v>6005270.76</v>
+        <v>113058.43</v>
       </c>
       <c r="I71" t="n">
-        <v>21210103.71</v>
+        <v>599716.37</v>
       </c>
       <c r="J71" t="n">
-        <v>27215374.47</v>
+        <v>712774.8</v>
       </c>
     </row>
     <row r="72">
@@ -2976,34 +2970,34 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>UNIMONTES</t>
+          <t>UEMG</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>2311</v>
+        <v>2351</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>UNIVERSIDADE ESTADUAL DE MONTES CLAROS</t>
+          <t>UNIVERSIDADE DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>469927618.13</v>
+        <v>404521667.47</v>
       </c>
       <c r="F72" t="n">
-        <v>414313756.03</v>
+        <v>384928295.57</v>
       </c>
       <c r="G72" t="n">
-        <v>405713436.11</v>
+        <v>374712336.29</v>
       </c>
       <c r="H72" t="n">
-        <v>1205407.47</v>
+        <v>6005270.76</v>
       </c>
       <c r="I72" t="n">
-        <v>16962260.8</v>
+        <v>21210103.71</v>
       </c>
       <c r="J72" t="n">
-        <v>18167668.27</v>
+        <v>27215374.47</v>
       </c>
     </row>
     <row r="73">
@@ -3012,33 +3006,69 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
+          <t>UNIMONTES</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>2311</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>UNIVERSIDADE ESTADUAL DE MONTES CLAROS</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>469927618.13</v>
+      </c>
+      <c r="F73" t="n">
+        <v>414313756.03</v>
+      </c>
+      <c r="G73" t="n">
+        <v>405713436.11</v>
+      </c>
+      <c r="H73" t="n">
+        <v>1205407.47</v>
+      </c>
+      <c r="I73" t="n">
+        <v>16962260.8</v>
+      </c>
+      <c r="J73" t="n">
+        <v>18167668.27</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
           <t>UTRAMIG</t>
         </is>
       </c>
-      <c r="C73" t="n">
+      <c r="C74" t="n">
         <v>2281</v>
       </c>
-      <c r="D73" t="inlineStr">
+      <c r="D74" t="inlineStr">
         <is>
           <t>FUNDACAO DE EDUCACAO PARA O TRABALHO DE MINAS GERAIS</t>
         </is>
       </c>
-      <c r="E73" t="n">
+      <c r="E74" t="n">
         <v>6125588.94</v>
       </c>
-      <c r="F73" t="n">
+      <c r="F74" t="n">
         <v>5821567.34</v>
       </c>
-      <c r="G73" t="n">
+      <c r="G74" t="n">
         <v>5483571.33</v>
       </c>
-      <c r="H73" t="n">
+      <c r="H74" t="n">
         <v>24344.67</v>
       </c>
-      <c r="I73" t="n">
+      <c r="I74" t="n">
         <v>193381.66</v>
       </c>
-      <c r="J73" t="n">
+      <c r="J74" t="n">
         <v>217726.33</v>
       </c>
     </row>

--- a/upload/orgao2023.xlsx
+++ b/upload/orgao2023.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/upload/orgao2023.xlsx
+++ b/upload/orgao2023.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J74"/>
+  <dimension ref="A1:J85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -558,34 +558,34 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ARMVA</t>
+          <t>ALMG</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2461</v>
+        <v>1011</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>AGENCIA DE DESENVOLVIMENTO DA REGIAO METROPOLITANA DO VALE DO ACO</t>
+          <t>ASSEMBLEIA LEGISLATIVA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3919274.27</v>
+        <v>1903297527.8</v>
       </c>
       <c r="F4" t="n">
-        <v>3274957.97</v>
+        <v>1874294477.86</v>
       </c>
       <c r="G4" t="n">
-        <v>2995203.29</v>
+        <v>1861899226.21</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>3920.75</v>
       </c>
       <c r="I4" t="n">
-        <v>526357.61</v>
+        <v>117462912.92</v>
       </c>
       <c r="J4" t="n">
-        <v>526357.61</v>
+        <v>117466833.67</v>
       </c>
     </row>
     <row r="5">
@@ -594,34 +594,34 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ARSAE -MG</t>
+          <t>ARMVA</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2441</v>
+        <v>2461</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>AGENCIA REGULADORA DE SERVICOS DE ABASTECIMENTO DE AGUA E DE ESGOTAMENTO SANITARIO DO ESTADO DE MINA</t>
+          <t>AGENCIA DE DESENVOLVIMENTO DA REGIAO METROPOLITANA DO VALE DO ACO</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>17351140.01</v>
+        <v>3919274.27</v>
       </c>
       <c r="F5" t="n">
-        <v>16698417.52</v>
+        <v>3274957.97</v>
       </c>
       <c r="G5" t="n">
-        <v>16573785.26</v>
+        <v>2995203.29</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>611025.34</v>
+        <v>526357.61</v>
       </c>
       <c r="J5" t="n">
-        <v>611025.34</v>
+        <v>526357.61</v>
       </c>
     </row>
     <row r="6">
@@ -630,34 +630,34 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CBMMG</t>
+          <t>ARSAE -MG</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1401</v>
+        <v>2441</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CORPO DE BOMBEIROS MILITAR DO ESTADO DE MINAS GERAIS</t>
+          <t>AGENCIA REGULADORA DE SERVICOS DE ABASTECIMENTO DE AGUA E DE ESGOTAMENTO SANITARIO DO ESTADO DE MINA</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1564505806.66</v>
+        <v>17351140.01</v>
       </c>
       <c r="F6" t="n">
-        <v>1472603650.09</v>
+        <v>16698417.52</v>
       </c>
       <c r="G6" t="n">
-        <v>1466343606.91</v>
+        <v>16573785.26</v>
       </c>
       <c r="H6" t="n">
-        <v>7744878.53</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>30546600.96</v>
+        <v>611025.34</v>
       </c>
       <c r="J6" t="n">
-        <v>38291479.49</v>
+        <v>611025.34</v>
       </c>
     </row>
     <row r="7">
@@ -666,34 +666,34 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CGE</t>
+          <t>CBMMG</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1521</v>
+        <v>1401</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CONTROLADORIA-GERAL DO ESTADO</t>
+          <t>CORPO DE BOMBEIROS MILITAR DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>60102963.54</v>
+        <v>1564505806.66</v>
       </c>
       <c r="F7" t="n">
-        <v>59580613.9</v>
+        <v>1472603650.09</v>
       </c>
       <c r="G7" t="n">
-        <v>59323104.46</v>
+        <v>1466343606.91</v>
       </c>
       <c r="H7" t="n">
-        <v>77665.00999999999</v>
+        <v>7744878.53</v>
       </c>
       <c r="I7" t="n">
-        <v>197493.6</v>
+        <v>30546600.96</v>
       </c>
       <c r="J7" t="n">
-        <v>275158.61</v>
+        <v>38291479.49</v>
       </c>
     </row>
     <row r="8">
@@ -702,34 +702,34 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>DER-MG</t>
+          <t>CGE</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2301</v>
+        <v>1521</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO DE EDIFICACOES E ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
+          <t>CONTROLADORIA-GERAL DO ESTADO</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1914847566.85</v>
+        <v>60102963.54</v>
       </c>
       <c r="F8" t="n">
-        <v>1044533400.24</v>
+        <v>59580613.9</v>
       </c>
       <c r="G8" t="n">
-        <v>966297540.79</v>
+        <v>59323104.46</v>
       </c>
       <c r="H8" t="n">
-        <v>16445711.3</v>
+        <v>77665.00999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>318972727.76</v>
+        <v>197493.6</v>
       </c>
       <c r="J8" t="n">
-        <v>335418439.06</v>
+        <v>275158.61</v>
       </c>
     </row>
     <row r="9">
@@ -738,34 +738,34 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>EGE - SEF</t>
+          <t>DEF PUB</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1911</v>
+        <v>1441</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>EGE SEC.FAZENDA-ENCARGOS DIVERSOS</t>
+          <t>DEFENSORIA PUBLICA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>854860168.33</v>
+        <v>853902750.97</v>
       </c>
       <c r="F9" t="n">
-        <v>765439410.1</v>
+        <v>823500196.72</v>
       </c>
       <c r="G9" t="n">
-        <v>765416129.62</v>
+        <v>816971152.8200001</v>
       </c>
       <c r="H9" t="n">
-        <v>25335200.02</v>
+        <v>2699.3</v>
       </c>
       <c r="I9" t="n">
-        <v>609616599.35</v>
+        <v>13731269.67</v>
       </c>
       <c r="J9" t="n">
-        <v>634951799.37</v>
+        <v>13733968.97</v>
       </c>
     </row>
     <row r="10">
@@ -774,34 +774,34 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>EGE-SEPLAG</t>
+          <t>DER-MG</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1941</v>
+        <v>2301</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>EGE-SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTAO</t>
+          <t>DEPARTAMENTO DE EDIFICACOES E ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>196770413.59</v>
+        <v>1914847566.85</v>
       </c>
       <c r="F10" t="n">
-        <v>196243687.54</v>
+        <v>1044533400.24</v>
       </c>
       <c r="G10" t="n">
-        <v>196240526.92</v>
+        <v>966297540.79</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>16445711.3</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>318972727.76</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>335418439.06</v>
       </c>
     </row>
     <row r="11">
@@ -810,29 +810,35 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>EMATER</t>
+          <t>EGE - SEF</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3041</v>
+        <v>1911</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>EMPRESA DE ASSISTENCIA TECNICA E EXTENSAO RURAL DO ESTADO DE MINAS GERAIS</t>
+          <t>EGE SEC.FAZENDA-ENCARGOS DIVERSOS</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>360362919.21</v>
+        <v>854860168.33</v>
       </c>
       <c r="F11" t="n">
-        <v>360362919.21</v>
+        <v>765439410.1</v>
       </c>
       <c r="G11" t="n">
-        <v>360362919.21</v>
-      </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+        <v>765416129.62</v>
+      </c>
+      <c r="H11" t="n">
+        <v>25335200.02</v>
+      </c>
+      <c r="I11" t="n">
+        <v>609616599.35</v>
+      </c>
+      <c r="J11" t="n">
+        <v>634951799.37</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -840,29 +846,35 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>EMC</t>
+          <t>EGE-SEPLAG</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3151</v>
+        <v>1941</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>EMPRESA MINEIRA DE COMUNICACAO</t>
+          <t>EGE-SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTAO</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>21506861.17</v>
+        <v>196770413.59</v>
       </c>
       <c r="F12" t="n">
-        <v>21506861.17</v>
+        <v>196243687.54</v>
       </c>
       <c r="G12" t="n">
-        <v>21506861.17</v>
-      </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+        <v>196240526.92</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -870,25 +882,25 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EPAMIG</t>
+          <t>EMATER</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3051</v>
+        <v>3041</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>EMPRESA DE PESQUISA AGROPECUARIA DE MINAS GERAIS</t>
+          <t>EMPRESA DE ASSISTENCIA TECNICA E EXTENSAO RURAL DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>129507075.06</v>
+        <v>360362919.21</v>
       </c>
       <c r="F13" t="n">
-        <v>129507075.06</v>
+        <v>360362919.21</v>
       </c>
       <c r="G13" t="n">
-        <v>129507075.06</v>
+        <v>360362919.21</v>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
@@ -900,35 +912,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ESP MG</t>
+          <t>EMC</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1541</v>
+        <v>3151</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>ESCOLA DE SAUDE PUBLICA DO ESTADO DE MINAS GERAIS</t>
+          <t>EMPRESA MINEIRA DE COMUNICACAO</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>19938984.92</v>
+        <v>21506861.17</v>
       </c>
       <c r="F14" t="n">
-        <v>19458800.92</v>
+        <v>21506861.17</v>
       </c>
       <c r="G14" t="n">
-        <v>19168057.7</v>
-      </c>
-      <c r="H14" t="n">
-        <v>8211.5</v>
-      </c>
-      <c r="I14" t="n">
-        <v>116097.68</v>
-      </c>
-      <c r="J14" t="n">
-        <v>124309.18</v>
-      </c>
+        <v>21506861.17</v>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -936,35 +942,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>FAHMEMG</t>
+          <t>EPAMIG</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>4541</v>
+        <v>3051</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>FUNDO DE APOIO HABITACIONAL AOS MILITARES DO ESTADO DE MINAS GERAIS</t>
+          <t>EMPRESA DE PESQUISA AGROPECUARIA DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>362500</v>
+        <v>129507075.06</v>
       </c>
       <c r="F15" t="n">
-        <v>327310.98</v>
+        <v>129507075.06</v>
       </c>
       <c r="G15" t="n">
-        <v>320259.33</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
+        <v>129507075.06</v>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -972,34 +972,34 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>FAOP</t>
+          <t>ESP MG</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2171</v>
+        <v>1541</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>FUNDACAO DE ARTE DE OURO PRETO</t>
+          <t>ESCOLA DE SAUDE PUBLICA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4750004.05</v>
+        <v>19938984.92</v>
       </c>
       <c r="F16" t="n">
-        <v>4345485.27</v>
+        <v>19458800.92</v>
       </c>
       <c r="G16" t="n">
-        <v>4163957.5</v>
+        <v>19168057.7</v>
       </c>
       <c r="H16" t="n">
-        <v>27405.6</v>
+        <v>8211.5</v>
       </c>
       <c r="I16" t="n">
-        <v>295215.94</v>
+        <v>116097.68</v>
       </c>
       <c r="J16" t="n">
-        <v>322621.54</v>
+        <v>124309.18</v>
       </c>
     </row>
     <row r="17">
@@ -1008,34 +1008,34 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>FAPEMIG</t>
+          <t>FAHMEMG</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2071</v>
+        <v>4541</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>FUNDACAO DE AMPARO A PESQUISA DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDO DE APOIO HABITACIONAL AOS MILITARES DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>475574938.69</v>
+        <v>362500</v>
       </c>
       <c r="F17" t="n">
-        <v>469867300.36</v>
+        <v>327310.98</v>
       </c>
       <c r="G17" t="n">
-        <v>420221524.1</v>
+        <v>320259.33</v>
       </c>
       <c r="H17" t="n">
-        <v>12738999.81</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>7274018.25</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>20013018.06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1044,34 +1044,34 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>FCS</t>
+          <t>FAOP</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2181</v>
+        <v>2171</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>FUNDACAO CLOVIS SALGADO</t>
+          <t>FUNDACAO DE ARTE DE OURO PRETO</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>49628398.03</v>
+        <v>4750004.05</v>
       </c>
       <c r="F18" t="n">
-        <v>47405823.66</v>
+        <v>4345485.27</v>
       </c>
       <c r="G18" t="n">
-        <v>46275247.85</v>
+        <v>4163957.5</v>
       </c>
       <c r="H18" t="n">
-        <v>253.4</v>
+        <v>27405.6</v>
       </c>
       <c r="I18" t="n">
-        <v>878433.0699999999</v>
+        <v>295215.94</v>
       </c>
       <c r="J18" t="n">
-        <v>878686.47</v>
+        <v>322621.54</v>
       </c>
     </row>
     <row r="19">
@@ -1080,29 +1080,35 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>FDM</t>
+          <t>FAPEMIG</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>4331</v>
+        <v>2071</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>FUNDO DE DESENVOLVIMENTO METROPOLITANO</t>
+          <t>FUNDACAO DE AMPARO A PESQUISA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>652279.16</v>
+        <v>475574938.69</v>
       </c>
       <c r="F19" t="n">
-        <v>254203.16</v>
+        <v>469867300.36</v>
       </c>
       <c r="G19" t="n">
-        <v>245243.42</v>
-      </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+        <v>420221524.1</v>
+      </c>
+      <c r="H19" t="n">
+        <v>12738999.81</v>
+      </c>
+      <c r="I19" t="n">
+        <v>7274018.25</v>
+      </c>
+      <c r="J19" t="n">
+        <v>20013018.06</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1110,34 +1116,34 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>FEAM</t>
+          <t>FCS</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2091</v>
+        <v>2181</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>FUNDACAO ESTADUAL DO MEIO AMBIENTE</t>
+          <t>FUNDACAO CLOVIS SALGADO</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>43259418.77</v>
+        <v>49628398.03</v>
       </c>
       <c r="F20" t="n">
-        <v>38126464.75</v>
+        <v>47405823.66</v>
       </c>
       <c r="G20" t="n">
-        <v>37435935.06</v>
+        <v>46275247.85</v>
       </c>
       <c r="H20" t="n">
-        <v>95.91</v>
+        <v>253.4</v>
       </c>
       <c r="I20" t="n">
-        <v>37153.49</v>
+        <v>878433.0699999999</v>
       </c>
       <c r="J20" t="n">
-        <v>37249.4</v>
+        <v>878686.47</v>
       </c>
     </row>
     <row r="21">
@@ -1146,35 +1152,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>FEAS</t>
+          <t>FDM</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>4251</v>
+        <v>4331</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE ASSISTENCIA SOCIAL</t>
+          <t>FUNDO DE DESENVOLVIMENTO METROPOLITANO</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>110854339.85</v>
+        <v>652279.16</v>
       </c>
       <c r="F21" t="n">
-        <v>106583471.83</v>
+        <v>254203.16</v>
       </c>
       <c r="G21" t="n">
-        <v>105151900.42</v>
-      </c>
-      <c r="H21" t="n">
-        <v>12672808.3</v>
-      </c>
-      <c r="I21" t="n">
-        <v>17248454.85</v>
-      </c>
-      <c r="J21" t="n">
-        <v>29921263.15</v>
-      </c>
+        <v>245243.42</v>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1182,34 +1182,34 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>FEC</t>
+          <t>FEAM</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>4491</v>
+        <v>2091</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE CULTURA</t>
+          <t>FUNDACAO ESTADUAL DO MEIO AMBIENTE</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3940069.61</v>
+        <v>43259418.77</v>
       </c>
       <c r="F22" t="n">
-        <v>3940069.61</v>
+        <v>38126464.75</v>
       </c>
       <c r="G22" t="n">
-        <v>3184573.65</v>
+        <v>37435935.06</v>
       </c>
       <c r="H22" t="n">
-        <v>390021.88</v>
+        <v>95.91</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>37153.49</v>
       </c>
       <c r="J22" t="n">
-        <v>390021.88</v>
+        <v>37249.4</v>
       </c>
     </row>
     <row r="23">
@@ -1218,34 +1218,34 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>FEH</t>
+          <t>FEAS</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>4101</v>
+        <v>4251</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE HABITACAO</t>
+          <t>FUNDO ESTADUAL DE ASSISTENCIA SOCIAL</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>16882559.96</v>
+        <v>110854339.85</v>
       </c>
       <c r="F23" t="n">
-        <v>15883952.89</v>
+        <v>106583471.83</v>
       </c>
       <c r="G23" t="n">
-        <v>15883952.89</v>
+        <v>105151900.42</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>12672808.3</v>
       </c>
       <c r="I23" t="n">
-        <v>707987.39</v>
+        <v>17248454.85</v>
       </c>
       <c r="J23" t="n">
-        <v>707987.39</v>
+        <v>29921263.15</v>
       </c>
     </row>
     <row r="24">
@@ -1254,34 +1254,34 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>FEI</t>
+          <t>FEC</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>4601</v>
+        <v>4491</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DOS DIREITOS DO IDOSO</t>
+          <t>FUNDO ESTADUAL DE CULTURA</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2887433.54</v>
+        <v>3940069.61</v>
       </c>
       <c r="F24" t="n">
-        <v>2887433.54</v>
+        <v>3940069.61</v>
       </c>
       <c r="G24" t="n">
+        <v>3184573.65</v>
+      </c>
+      <c r="H24" t="n">
+        <v>390021.88</v>
+      </c>
+      <c r="I24" t="n">
         <v>0</v>
       </c>
-      <c r="H24" t="n">
-        <v>180000</v>
-      </c>
-      <c r="I24" t="n">
-        <v>45000</v>
-      </c>
       <c r="J24" t="n">
-        <v>225000</v>
+        <v>390021.88</v>
       </c>
     </row>
     <row r="25">
@@ -1290,34 +1290,34 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>FES</t>
+          <t>FEH</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>4291</v>
+        <v>4101</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE SAUDE</t>
+          <t>FUNDO ESTADUAL DE HABITACAO</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>11302215537.53</v>
+        <v>16882559.96</v>
       </c>
       <c r="F25" t="n">
-        <v>10567487751.92</v>
+        <v>15883952.89</v>
       </c>
       <c r="G25" t="n">
-        <v>10368587376.49</v>
+        <v>15883952.89</v>
       </c>
       <c r="H25" t="n">
-        <v>876192598.35</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>462749484.48</v>
+        <v>707987.39</v>
       </c>
       <c r="J25" t="n">
-        <v>1338942082.83</v>
+        <v>707987.39</v>
       </c>
     </row>
     <row r="26">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>FESP-MG</t>
+          <t>FEI</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>4691</v>
+        <v>4601</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE SEGURANCA PUBLICA DE MINAS GERAIS</t>
+          <t>FUNDO ESTADUAL DOS DIREITOS DO IDOSO</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>56928753.65</v>
+        <v>2887433.54</v>
       </c>
       <c r="F26" t="n">
-        <v>13274144.7</v>
+        <v>2887433.54</v>
       </c>
       <c r="G26" t="n">
-        <v>11948730.27</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>2022500.23</v>
+        <v>180000</v>
       </c>
       <c r="I26" t="n">
-        <v>11009074.78</v>
+        <v>45000</v>
       </c>
       <c r="J26" t="n">
-        <v>13031575.01</v>
+        <v>225000</v>
       </c>
     </row>
     <row r="27">
@@ -1362,34 +1362,34 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>FET-MG</t>
+          <t>FEPDC</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>4701</v>
+        <v>4451</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DO TRABALHO DE MINAS GERAIS</t>
+          <t>FUNDO ESTADUAL DE PROTECAO E DEFESA DO CONSUMIDOR</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>481821.71</v>
+        <v>35323915.03</v>
       </c>
       <c r="F27" t="n">
-        <v>79007.12</v>
+        <v>16775518.72</v>
       </c>
       <c r="G27" t="n">
-        <v>75725.75999999999</v>
+        <v>15712214.16</v>
       </c>
       <c r="H27" t="n">
-        <v>4212.69</v>
+        <v>1711.42</v>
       </c>
       <c r="I27" t="n">
-        <v>950789.36</v>
+        <v>370032.98</v>
       </c>
       <c r="J27" t="n">
-        <v>955002.05</v>
+        <v>371744.4</v>
       </c>
     </row>
     <row r="28">
@@ -1398,34 +1398,34 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>FFP - MG</t>
+          <t>FEPJ</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>4711</v>
+        <v>4031</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>FUNDO FINANCEIRO DE PREVIDENCIA DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDO ESPECIAL DO PODER JUDICIARIO DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>16707308683.78</v>
+        <v>2021294271.44</v>
       </c>
       <c r="F28" t="n">
-        <v>16706043073.46</v>
+        <v>1695364467.38</v>
       </c>
       <c r="G28" t="n">
-        <v>16714373495.87</v>
+        <v>1541166557.69</v>
       </c>
       <c r="H28" t="n">
-        <v>3616.02</v>
+        <v>1469990.01</v>
       </c>
       <c r="I28" t="n">
-        <v>637267.26</v>
+        <v>148541174.34</v>
       </c>
       <c r="J28" t="n">
-        <v>640883.28</v>
+        <v>150011164.35</v>
       </c>
     </row>
     <row r="29">
@@ -1434,34 +1434,34 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>FHA</t>
+          <t>FES</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2151</v>
+        <v>4291</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>FUNDACAO HELENA ANTIPOFF</t>
+          <t>FUNDO ESTADUAL DE SAUDE</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>64938007.38</v>
+        <v>11302215537.53</v>
       </c>
       <c r="F29" t="n">
-        <v>62329642.07</v>
+        <v>10567487751.92</v>
       </c>
       <c r="G29" t="n">
-        <v>61232129.22</v>
+        <v>10368587376.49</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>876192598.35</v>
       </c>
       <c r="I29" t="n">
-        <v>2676209.5</v>
+        <v>462749484.48</v>
       </c>
       <c r="J29" t="n">
-        <v>2676209.5</v>
+        <v>1338942082.83</v>
       </c>
     </row>
     <row r="30">
@@ -1470,34 +1470,34 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>FHEMIG</t>
+          <t>FESP-MG</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>2271</v>
+        <v>4691</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>FUNDACAO HOSPITALAR DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDO ESTADUAL DE SEGURANCA PUBLICA DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2164150549.42</v>
+        <v>56928753.65</v>
       </c>
       <c r="F30" t="n">
-        <v>2059482648.7</v>
+        <v>13274144.7</v>
       </c>
       <c r="G30" t="n">
-        <v>2019538042.37</v>
+        <v>11948730.27</v>
       </c>
       <c r="H30" t="n">
-        <v>3347619.96</v>
+        <v>2022500.23</v>
       </c>
       <c r="I30" t="n">
-        <v>95082172.20999999</v>
+        <v>11009074.78</v>
       </c>
       <c r="J30" t="n">
-        <v>98429792.17</v>
+        <v>13031575.01</v>
       </c>
     </row>
     <row r="31">
@@ -1506,34 +1506,34 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>FHIDRO</t>
+          <t>FET-MG</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>4341</v>
+        <v>4701</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>FUNDO DE RECUPERACAO, PROTECAO E DESENVOLVIMENTO SUSTENTAVEL DAS BACIAS HIDROGRAFICAS DO ESTADO DE M</t>
+          <t>FUNDO ESTADUAL DO TRABALHO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>3424799.42</v>
+        <v>481821.71</v>
       </c>
       <c r="F31" t="n">
-        <v>2738104.88</v>
+        <v>79007.12</v>
       </c>
       <c r="G31" t="n">
-        <v>2250014.71</v>
+        <v>75725.75999999999</v>
       </c>
       <c r="H31" t="n">
-        <v>68971.2</v>
+        <v>4212.69</v>
       </c>
       <c r="I31" t="n">
-        <v>75798.71000000001</v>
+        <v>950789.36</v>
       </c>
       <c r="J31" t="n">
-        <v>144769.91</v>
+        <v>955002.05</v>
       </c>
     </row>
     <row r="32">
@@ -1542,34 +1542,34 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>FIA</t>
+          <t>FFP - MG</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>4091</v>
+        <v>4711</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>FUNDO PARA A INFANCIA E A ADOLESCENCIA</t>
+          <t>FUNDO FINANCEIRO DE PREVIDENCIA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>7031581.25</v>
+        <v>16707308683.78</v>
       </c>
       <c r="F32" t="n">
-        <v>5241364.07</v>
+        <v>16706043073.46</v>
       </c>
       <c r="G32" t="n">
-        <v>3380577.21</v>
+        <v>16714373495.87</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>3616.02</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>637267.26</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>640883.28</v>
       </c>
     </row>
     <row r="33">
@@ -1578,34 +1578,34 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>FJP</t>
+          <t>FHA</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>2061</v>
+        <v>2151</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>FUNDACAO JOAO PINHEIRO</t>
+          <t>FUNDACAO HELENA ANTIPOFF</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>65473442.71</v>
+        <v>64938007.38</v>
       </c>
       <c r="F33" t="n">
-        <v>62245323.49</v>
+        <v>62329642.07</v>
       </c>
       <c r="G33" t="n">
-        <v>61139568.08</v>
+        <v>61232129.22</v>
       </c>
       <c r="H33" t="n">
-        <v>658090.65</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>5690027.08</v>
+        <v>2676209.5</v>
       </c>
       <c r="J33" t="n">
-        <v>6348117.73</v>
+        <v>2676209.5</v>
       </c>
     </row>
     <row r="34">
@@ -1614,34 +1614,34 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>FPE</t>
+          <t>FHEMIG</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>4141</v>
+        <v>2271</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>FUNDO PENITENCIARIO ESTADUAL</t>
+          <t>FUNDACAO HOSPITALAR DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>40613382.55</v>
+        <v>2164150549.42</v>
       </c>
       <c r="F34" t="n">
-        <v>23565562.32</v>
+        <v>2059482648.7</v>
       </c>
       <c r="G34" t="n">
-        <v>22676692.22</v>
+        <v>2019538042.37</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>3347619.96</v>
       </c>
       <c r="I34" t="n">
-        <v>11408560.88</v>
+        <v>95082172.20999999</v>
       </c>
       <c r="J34" t="n">
-        <v>11408560.88</v>
+        <v>98429792.17</v>
       </c>
     </row>
     <row r="35">
@@ -1650,34 +1650,34 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>FPP - MG</t>
+          <t>FHIDRO</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>4631</v>
+        <v>4341</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>FUNDO DE PAGAMENTO DE PARCERIAS PUBLICO - PRIVADAS DE MINAS GERAIS</t>
+          <t>FUNDO DE RECUPERACAO, PROTECAO E DESENVOLVIMENTO SUSTENTAVEL DAS BACIAS HIDROGRAFICAS DO ESTADO DE M</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>860717853.34</v>
+        <v>3424799.42</v>
       </c>
       <c r="F35" t="n">
-        <v>307011647.13</v>
+        <v>2738104.88</v>
       </c>
       <c r="G35" t="n">
-        <v>282507517.43</v>
+        <v>2250014.71</v>
       </c>
       <c r="H35" t="n">
-        <v>344621.26</v>
+        <v>68971.2</v>
       </c>
       <c r="I35" t="n">
-        <v>28865269.27</v>
+        <v>75798.71000000001</v>
       </c>
       <c r="J35" t="n">
-        <v>29209890.53</v>
+        <v>144769.91</v>
       </c>
     </row>
     <row r="36">
@@ -1686,34 +1686,34 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>FUCAM</t>
+          <t>FIA</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>2161</v>
+        <v>4091</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>FUNDACAO EDUCACIONAL CAIO MARTINS</t>
+          <t>FUNDO PARA A INFANCIA E A ADOLESCENCIA</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>10901641.69</v>
+        <v>7031581.25</v>
       </c>
       <c r="F36" t="n">
-        <v>10318773.13</v>
+        <v>5241364.07</v>
       </c>
       <c r="G36" t="n">
-        <v>8998548.609999999</v>
+        <v>3380577.21</v>
       </c>
       <c r="H36" t="n">
-        <v>121569.88</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>1346214.75</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>1467784.63</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -1722,34 +1722,34 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>FUNAPEC</t>
+          <t>FJP</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>4551</v>
+        <v>2061</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>FUNDO DE ASSISTENCIA AO PECULIO DOS SERVIDORES DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDACAO JOAO PINHEIRO</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>72736739.48</v>
+        <v>65473442.71</v>
       </c>
       <c r="F37" t="n">
-        <v>71196549.09</v>
+        <v>62245323.49</v>
       </c>
       <c r="G37" t="n">
-        <v>71168742.39</v>
+        <v>61139568.08</v>
       </c>
       <c r="H37" t="n">
-        <v>6853309.77</v>
+        <v>658090.65</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>5690027.08</v>
       </c>
       <c r="J37" t="n">
-        <v>6853309.77</v>
+        <v>6348117.73</v>
       </c>
     </row>
     <row r="38">
@@ -1758,34 +1758,34 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>FUNED</t>
+          <t>FPE</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>2261</v>
+        <v>4141</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>FUNDACAO EZEQUIEL DIAS</t>
+          <t>FUNDO PENITENCIARIO ESTADUAL</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>368684570.21</v>
+        <v>40613382.55</v>
       </c>
       <c r="F38" t="n">
-        <v>273219748.02</v>
+        <v>23565562.32</v>
       </c>
       <c r="G38" t="n">
-        <v>269618135.07</v>
+        <v>22676692.22</v>
       </c>
       <c r="H38" t="n">
-        <v>8154203.6</v>
+        <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>41399163.16</v>
+        <v>11408560.88</v>
       </c>
       <c r="J38" t="n">
-        <v>49553366.76</v>
+        <v>11408560.88</v>
       </c>
     </row>
     <row r="39">
@@ -1794,34 +1794,34 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>FUNTRANS</t>
+          <t>FPP - MG</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>4381</v>
+        <v>4631</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE DESENVOLVIMENTO DE TRANSPORTES</t>
+          <t>FUNDO DE PAGAMENTO DE PARCERIAS PUBLICO - PRIVADAS DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>93182744.76000001</v>
+        <v>860717853.34</v>
       </c>
       <c r="F39" t="n">
-        <v>73453457.05</v>
+        <v>307011647.13</v>
       </c>
       <c r="G39" t="n">
-        <v>71188066.92</v>
+        <v>282507517.43</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>344621.26</v>
       </c>
       <c r="I39" t="n">
-        <v>8330157.76</v>
+        <v>28865269.27</v>
       </c>
       <c r="J39" t="n">
-        <v>8330157.76</v>
+        <v>29209890.53</v>
       </c>
     </row>
     <row r="40">
@@ -1830,34 +1830,34 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>GABINETE MILITAR</t>
+          <t>FUCAM</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1071</v>
+        <v>2161</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>GABINETE MILITAR DO GOVERNADOR DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDACAO EDUCACIONAL CAIO MARTINS</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>46143197.21</v>
+        <v>10901641.69</v>
       </c>
       <c r="F40" t="n">
-        <v>35398463.11</v>
+        <v>10318773.13</v>
       </c>
       <c r="G40" t="n">
-        <v>34050957.79</v>
+        <v>8998548.609999999</v>
       </c>
       <c r="H40" t="n">
-        <v>211337.1</v>
+        <v>121569.88</v>
       </c>
       <c r="I40" t="n">
-        <v>3943260.33</v>
+        <v>1346214.75</v>
       </c>
       <c r="J40" t="n">
-        <v>4154597.43</v>
+        <v>1467784.63</v>
       </c>
     </row>
     <row r="41">
@@ -1866,34 +1866,34 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>GDPE - SEF</t>
+          <t>FUNAPEC</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1916</v>
+        <v>4551</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>GESTAO DA DIVIDA PUBLICA ESTADUAL</t>
+          <t>FUNDO DE ASSISTENCIA AO PECULIO DOS SERVIDORES DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4151422885</v>
+        <v>72736739.48</v>
       </c>
       <c r="F41" t="n">
-        <v>4151422885</v>
+        <v>71196549.09</v>
       </c>
       <c r="G41" t="n">
-        <v>3992987258.55</v>
+        <v>71168742.39</v>
       </c>
       <c r="H41" t="n">
-        <v>316225142.59</v>
+        <v>6853309.77</v>
       </c>
       <c r="I41" t="n">
-        <v>123029711.28</v>
+        <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>439254853.87</v>
+        <v>6853309.77</v>
       </c>
     </row>
     <row r="42">
@@ -1902,34 +1902,34 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>HEMOMINAS</t>
+          <t>FUNDHAB</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>2321</v>
+        <v>4121</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>FUNDACAO CENTRO DE HEMATOLOGIA E HEMOTERAPIA DE MINAS GERAIS</t>
+          <t>FUNDO DE APOIO HABITACIONAL DA ASSEMBLEIA LEGISLATIVA DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>355203535.23</v>
+        <v>9679354.34</v>
       </c>
       <c r="F42" t="n">
-        <v>320246686.79</v>
+        <v>8669954.34</v>
       </c>
       <c r="G42" t="n">
-        <v>311999002.94</v>
+        <v>7633039.44</v>
       </c>
       <c r="H42" t="n">
-        <v>1679096.03</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>28146659.99</v>
+        <v>644000</v>
       </c>
       <c r="J42" t="n">
-        <v>29825756.02</v>
+        <v>644000</v>
       </c>
     </row>
     <row r="43">
@@ -1938,34 +1938,34 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>IDENE</t>
+          <t>FUNED</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>2421</v>
+        <v>2261</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>INSTITUTO DE DESENVOLVIMENTO DO NORTE E NORDESTE DE MINAS GERAIS</t>
+          <t>FUNDACAO EZEQUIEL DIAS</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100992421.24</v>
+        <v>368684570.21</v>
       </c>
       <c r="F43" t="n">
-        <v>76969361.8</v>
+        <v>273219748.02</v>
       </c>
       <c r="G43" t="n">
-        <v>75625489.05</v>
+        <v>269618135.07</v>
       </c>
       <c r="H43" t="n">
-        <v>163906.27</v>
+        <v>8154203.6</v>
       </c>
       <c r="I43" t="n">
-        <v>6105648.21</v>
+        <v>41399163.16</v>
       </c>
       <c r="J43" t="n">
-        <v>6269554.48</v>
+        <v>49553366.76</v>
       </c>
     </row>
     <row r="44">
@@ -1974,34 +1974,34 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>IEF</t>
+          <t>FUNEMP</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>2101</v>
+        <v>4441</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>INSTITUTO ESTADUAL DE FLORESTAS</t>
+          <t>FUNDO ESPECIAL DO MINISTERIO PUBLICO DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>206253448.79</v>
+        <v>41979113.94</v>
       </c>
       <c r="F44" t="n">
-        <v>201049210.28</v>
+        <v>18233630.68</v>
       </c>
       <c r="G44" t="n">
-        <v>193758815.18</v>
+        <v>17916399.77</v>
       </c>
       <c r="H44" t="n">
-        <v>2044943.53</v>
+        <v>19771.3</v>
       </c>
       <c r="I44" t="n">
-        <v>3790350.53</v>
+        <v>9428804.08</v>
       </c>
       <c r="J44" t="n">
-        <v>5835294.06</v>
+        <v>9448575.380000001</v>
       </c>
     </row>
     <row r="45">
@@ -2010,34 +2010,34 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>IEPHA</t>
+          <t>FUNTRANS</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>2201</v>
+        <v>4381</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>INSTITUTO ESTADUAL DO PATRIMONIO HISTORICO E ARTISTICO DE MINAS GERAIS</t>
+          <t>FUNDO ESTADUAL DE DESENVOLVIMENTO DE TRANSPORTES</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>20854647.15</v>
+        <v>93182744.76000001</v>
       </c>
       <c r="F45" t="n">
-        <v>19794515.12</v>
+        <v>73453457.05</v>
       </c>
       <c r="G45" t="n">
-        <v>18916412.23</v>
+        <v>71188066.92</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>2810067.14</v>
+        <v>8330157.76</v>
       </c>
       <c r="J45" t="n">
-        <v>2810067.14</v>
+        <v>8330157.76</v>
       </c>
     </row>
     <row r="46">
@@ -2046,34 +2046,34 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>IGAM</t>
+          <t>GABINETE MILITAR</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>2241</v>
+        <v>1071</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>INSTITUTO MINEIRO DE GESTAO DAS AGUAS</t>
+          <t>GABINETE MILITAR DO GOVERNADOR DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>106797429.43</v>
+        <v>46143197.21</v>
       </c>
       <c r="F46" t="n">
-        <v>101404974.15</v>
+        <v>35398463.11</v>
       </c>
       <c r="G46" t="n">
-        <v>100479945.84</v>
+        <v>34050957.79</v>
       </c>
       <c r="H46" t="n">
-        <v>10446834.76</v>
+        <v>211337.1</v>
       </c>
       <c r="I46" t="n">
-        <v>3875281.47</v>
+        <v>3943260.33</v>
       </c>
       <c r="J46" t="n">
-        <v>14322116.23</v>
+        <v>4154597.43</v>
       </c>
     </row>
     <row r="47">
@@ -2082,34 +2082,34 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>IMA</t>
+          <t>GDPE - SEF</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>2371</v>
+        <v>1916</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>INSTITUTO MINEIRO DE AGROPECUARIA</t>
+          <t>GESTAO DA DIVIDA PUBLICA ESTADUAL</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>247119982.84</v>
+        <v>4151422885</v>
       </c>
       <c r="F47" t="n">
-        <v>242894139.49</v>
+        <v>4151422885</v>
       </c>
       <c r="G47" t="n">
-        <v>242543975.53</v>
+        <v>3992987258.55</v>
       </c>
       <c r="H47" t="n">
-        <v>378714.11</v>
+        <v>316225142.59</v>
       </c>
       <c r="I47" t="n">
-        <v>3948517.78</v>
+        <v>123029711.28</v>
       </c>
       <c r="J47" t="n">
-        <v>4327231.89</v>
+        <v>439254853.87</v>
       </c>
     </row>
     <row r="48">
@@ -2118,34 +2118,34 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>IPEMMG</t>
+          <t>HEMOMINAS</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>2331</v>
+        <v>2321</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>INSTITUTO DE METROLOGIA E QUALIDADE DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDACAO CENTRO DE HEMATOLOGIA E HEMOTERAPIA DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>30989568.55</v>
+        <v>355203535.23</v>
       </c>
       <c r="F48" t="n">
-        <v>30394216.46</v>
+        <v>320246686.79</v>
       </c>
       <c r="G48" t="n">
-        <v>28953199.86</v>
+        <v>311999002.94</v>
       </c>
       <c r="H48" t="n">
-        <v>78441.50999999999</v>
+        <v>1679096.03</v>
       </c>
       <c r="I48" t="n">
-        <v>108549.11</v>
+        <v>28146659.99</v>
       </c>
       <c r="J48" t="n">
-        <v>186990.62</v>
+        <v>29825756.02</v>
       </c>
     </row>
     <row r="49">
@@ -2154,34 +2154,34 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>IPSEMG</t>
+          <t>IDENE</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>2011</v>
+        <v>2421</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>INSTITUTO DE PREVIDENCIA DOS SERVIDORES DO ESTADO DE MINAS GERAIS</t>
+          <t>INSTITUTO DE DESENVOLVIMENTO DO NORTE E NORDESTE DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1616992072.96</v>
+        <v>100992421.24</v>
       </c>
       <c r="F49" t="n">
-        <v>1414919735.8</v>
+        <v>76969361.8</v>
       </c>
       <c r="G49" t="n">
-        <v>1379497007.69</v>
+        <v>75625489.05</v>
       </c>
       <c r="H49" t="n">
-        <v>2730465.24</v>
+        <v>163906.27</v>
       </c>
       <c r="I49" t="n">
-        <v>139505498.51</v>
+        <v>6105648.21</v>
       </c>
       <c r="J49" t="n">
-        <v>142235963.75</v>
+        <v>6269554.48</v>
       </c>
     </row>
     <row r="50">
@@ -2190,34 +2190,34 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>IPSM</t>
+          <t>IEF</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>2121</v>
+        <v>2101</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>INSTITUTO DE PREVIDENCIA DOS SERVIDORES MILITARES DO ESTADO DE MINAS GERAIS</t>
+          <t>INSTITUTO ESTADUAL DE FLORESTAS</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2900878606.77</v>
+        <v>206253448.79</v>
       </c>
       <c r="F50" t="n">
-        <v>2876463795.17</v>
+        <v>201049210.28</v>
       </c>
       <c r="G50" t="n">
-        <v>2327341436.54</v>
+        <v>193758815.18</v>
       </c>
       <c r="H50" t="n">
-        <v>102308456.42</v>
+        <v>2044943.53</v>
       </c>
       <c r="I50" t="n">
-        <v>33347552.64</v>
+        <v>3790350.53</v>
       </c>
       <c r="J50" t="n">
-        <v>135656009.06</v>
+        <v>5835294.06</v>
       </c>
     </row>
     <row r="51">
@@ -2226,34 +2226,34 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>JUCEMG</t>
+          <t>IEPHA</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>2251</v>
+        <v>2201</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>JUNTA COMERCIAL DO ESTADO DE MINAS GERAIS</t>
+          <t>INSTITUTO ESTADUAL DO PATRIMONIO HISTORICO E ARTISTICO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>30826852.4</v>
+        <v>20854647.15</v>
       </c>
       <c r="F51" t="n">
-        <v>29563968.03</v>
+        <v>19794515.12</v>
       </c>
       <c r="G51" t="n">
-        <v>29011549.3</v>
+        <v>18916412.23</v>
       </c>
       <c r="H51" t="n">
-        <v>565.47</v>
+        <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>746119.0600000001</v>
+        <v>2810067.14</v>
       </c>
       <c r="J51" t="n">
-        <v>746684.53</v>
+        <v>2810067.14</v>
       </c>
     </row>
     <row r="52">
@@ -2262,34 +2262,34 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>LEMG</t>
+          <t>IGAM</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>2041</v>
+        <v>2241</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LOTERIA DO ESTADO DE MINAS GERAIS</t>
+          <t>INSTITUTO MINEIRO DE GESTAO DAS AGUAS</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>3423162.82</v>
+        <v>106797429.43</v>
       </c>
       <c r="F52" t="n">
-        <v>3283189.87</v>
+        <v>101404974.15</v>
       </c>
       <c r="G52" t="n">
-        <v>3280441.52</v>
+        <v>100479945.84</v>
       </c>
       <c r="H52" t="n">
-        <v>0</v>
+        <v>10446834.76</v>
       </c>
       <c r="I52" t="n">
-        <v>6507</v>
+        <v>3875281.47</v>
       </c>
       <c r="J52" t="n">
-        <v>6507</v>
+        <v>14322116.23</v>
       </c>
     </row>
     <row r="53">
@@ -2298,34 +2298,34 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>OGE</t>
+          <t>IMA</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1101</v>
+        <v>2371</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>OUVIDORIA-GERAL DO ESTADO DE MINAS GERAIS</t>
+          <t>INSTITUTO MINEIRO DE AGROPECUARIA</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>14788301.67</v>
+        <v>247119982.84</v>
       </c>
       <c r="F53" t="n">
-        <v>14630579.61</v>
+        <v>242894139.49</v>
       </c>
       <c r="G53" t="n">
-        <v>14490566</v>
+        <v>242543975.53</v>
       </c>
       <c r="H53" t="n">
-        <v>0</v>
+        <v>378714.11</v>
       </c>
       <c r="I53" t="n">
-        <v>94372.77</v>
+        <v>3948517.78</v>
       </c>
       <c r="J53" t="n">
-        <v>94372.77</v>
+        <v>4327231.89</v>
       </c>
     </row>
     <row r="54">
@@ -2334,34 +2334,34 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>PARTICIPAÇÃO EMPRESAS</t>
+          <t>IPEMMG</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1915</v>
+        <v>2331</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>PARTICIPACAO NO AUMENTO DO CAPITAL SOCIAL DE EMPRESAS</t>
+          <t>INSTITUTO DE METROLOGIA E QUALIDADE DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>508647503.2</v>
+        <v>30989568.55</v>
       </c>
       <c r="F54" t="n">
-        <v>3647503.2</v>
+        <v>30394216.46</v>
       </c>
       <c r="G54" t="n">
-        <v>3647503.2</v>
+        <v>28953199.86</v>
       </c>
       <c r="H54" t="n">
-        <v>0</v>
+        <v>78441.50999999999</v>
       </c>
       <c r="I54" t="n">
-        <v>75202844.75</v>
+        <v>108549.11</v>
       </c>
       <c r="J54" t="n">
-        <v>75202844.75</v>
+        <v>186990.62</v>
       </c>
     </row>
     <row r="55">
@@ -2370,35 +2370,29 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>PCMG</t>
+          <t>IPLEMG</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1511</v>
+        <v>2361</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>POLICIA CIVIL DO ESTADO DE MINAS GERAIS</t>
+          <t>INSTITUTO DE PREVIDENCIA DO LEGISLATIVO DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>3065566676.29</v>
+        <v>60477343.11</v>
       </c>
       <c r="F55" t="n">
-        <v>2994754625.68</v>
+        <v>60477343.11</v>
       </c>
       <c r="G55" t="n">
-        <v>2978077582.97</v>
-      </c>
-      <c r="H55" t="n">
-        <v>12864618.77</v>
-      </c>
-      <c r="I55" t="n">
-        <v>79194935.12</v>
-      </c>
-      <c r="J55" t="n">
-        <v>92059553.89</v>
-      </c>
+        <v>60477343.11</v>
+      </c>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -2406,34 +2400,34 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>PMMG</t>
+          <t>IPSEMG</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1251</v>
+        <v>2011</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>POLICIA MILITAR DO ESTADO DE MINAS GERAIS</t>
+          <t>INSTITUTO DE PREVIDENCIA DOS SERVIDORES DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>13028366670.83</v>
+        <v>1616992072.96</v>
       </c>
       <c r="F56" t="n">
-        <v>12841769394.38</v>
+        <v>1414919735.8</v>
       </c>
       <c r="G56" t="n">
-        <v>12810307610.08</v>
+        <v>1379497007.69</v>
       </c>
       <c r="H56" t="n">
-        <v>36489178.11</v>
+        <v>2730465.24</v>
       </c>
       <c r="I56" t="n">
-        <v>226080162.79</v>
+        <v>139505498.51</v>
       </c>
       <c r="J56" t="n">
-        <v>262569340.9</v>
+        <v>142235963.75</v>
       </c>
     </row>
     <row r="57">
@@ -2442,29 +2436,35 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>SCC</t>
+          <t>IPSM</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1721</v>
+        <v>2121</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DA CASA CIVIL</t>
+          <t>INSTITUTO DE PREVIDENCIA DOS SERVIDORES MILITARES DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5572590.71</v>
+        <v>2900878606.77</v>
       </c>
       <c r="F57" t="n">
-        <v>5270468.4</v>
+        <v>2876463795.17</v>
       </c>
       <c r="G57" t="n">
-        <v>4983565.3</v>
-      </c>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
+        <v>2327341436.54</v>
+      </c>
+      <c r="H57" t="n">
+        <v>102308456.42</v>
+      </c>
+      <c r="I57" t="n">
+        <v>33347552.64</v>
+      </c>
+      <c r="J57" t="n">
+        <v>135656009.06</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -2472,34 +2472,34 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>SEAPA</t>
+          <t>JUCEMG</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1231</v>
+        <v>2251</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE AGRICULTURA, PECUARIA E ABASTECIMENTO - SEAPA</t>
+          <t>JUNTA COMERCIAL DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>157335344.34</v>
+        <v>30826852.4</v>
       </c>
       <c r="F58" t="n">
-        <v>140995120.89</v>
+        <v>29563968.03</v>
       </c>
       <c r="G58" t="n">
-        <v>122957383.2</v>
+        <v>29011549.3</v>
       </c>
       <c r="H58" t="n">
-        <v>7823519.95</v>
+        <v>565.47</v>
       </c>
       <c r="I58" t="n">
-        <v>3775929.39</v>
+        <v>746119.0600000001</v>
       </c>
       <c r="J58" t="n">
-        <v>11599449.34</v>
+        <v>746684.53</v>
       </c>
     </row>
     <row r="59">
@@ -2508,34 +2508,34 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>SEC. GERAL</t>
+          <t>LEMG</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1631</v>
+        <v>2041</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>SECRETARIA-GERAL</t>
+          <t>LOTERIA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>64901564.21</v>
+        <v>3423162.82</v>
       </c>
       <c r="F59" t="n">
-        <v>59419458.57</v>
+        <v>3283189.87</v>
       </c>
       <c r="G59" t="n">
-        <v>57509982.39</v>
+        <v>3280441.52</v>
       </c>
       <c r="H59" t="n">
-        <v>777.25</v>
+        <v>0</v>
       </c>
       <c r="I59" t="n">
-        <v>22162487.86</v>
+        <v>6507</v>
       </c>
       <c r="J59" t="n">
-        <v>22163265.11</v>
+        <v>6507</v>
       </c>
     </row>
     <row r="60">
@@ -2544,29 +2544,35 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>SECOM</t>
+          <t>OGE</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1711</v>
+        <v>1101</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE COMUNICACAO SOCIAL</t>
+          <t>OUVIDORIA-GERAL DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>85247066.05</v>
+        <v>14788301.67</v>
       </c>
       <c r="F60" t="n">
-        <v>32467458.6</v>
+        <v>14630579.61</v>
       </c>
       <c r="G60" t="n">
-        <v>31192326.84</v>
-      </c>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
+        <v>14490566</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" t="n">
+        <v>94372.77</v>
+      </c>
+      <c r="J60" t="n">
+        <v>94372.77</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -2574,34 +2580,34 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>SECULT</t>
+          <t>PARTICIPAÇÃO EMPRESAS</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1271</v>
+        <v>1915</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE CULTURA E TURISMO</t>
+          <t>PARTICIPACAO NO AUMENTO DO CAPITAL SOCIAL DE EMPRESAS</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>89313458.84</v>
+        <v>508647503.2</v>
       </c>
       <c r="F61" t="n">
-        <v>86513089.77</v>
+        <v>3647503.2</v>
       </c>
       <c r="G61" t="n">
-        <v>82380637.92</v>
+        <v>3647503.2</v>
       </c>
       <c r="H61" t="n">
-        <v>1333330.75</v>
+        <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>896505.38</v>
+        <v>75202844.75</v>
       </c>
       <c r="J61" t="n">
-        <v>2229836.13</v>
+        <v>75202844.75</v>
       </c>
     </row>
     <row r="62">
@@ -2610,34 +2616,34 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>SEDE</t>
+          <t>PCMG</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1221</v>
+        <v>1511</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONOMICO</t>
+          <t>POLICIA CIVIL DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>71019848</v>
+        <v>3065566676.29</v>
       </c>
       <c r="F62" t="n">
-        <v>49587285.62</v>
+        <v>2994754625.68</v>
       </c>
       <c r="G62" t="n">
-        <v>28903226.95</v>
+        <v>2978077582.97</v>
       </c>
       <c r="H62" t="n">
-        <v>468159.26</v>
+        <v>12864618.77</v>
       </c>
       <c r="I62" t="n">
-        <v>8730755.23</v>
+        <v>79194935.12</v>
       </c>
       <c r="J62" t="n">
-        <v>9198914.49</v>
+        <v>92059553.89</v>
       </c>
     </row>
     <row r="63">
@@ -2646,34 +2652,34 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>SEDESE</t>
+          <t>PGJ</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>1481</v>
+        <v>1091</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL</t>
+          <t>PROCURADORIA GERAL DE JUSTICA</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>278200685.86</v>
+        <v>3497134160</v>
       </c>
       <c r="F63" t="n">
-        <v>258721057.71</v>
+        <v>3397602683.81</v>
       </c>
       <c r="G63" t="n">
-        <v>187380767.61</v>
+        <v>3372626349.55</v>
       </c>
       <c r="H63" t="n">
-        <v>13128483.79</v>
+        <v>3341565.82</v>
       </c>
       <c r="I63" t="n">
-        <v>14858520.74</v>
+        <v>78964299.98999999</v>
       </c>
       <c r="J63" t="n">
-        <v>27987004.53</v>
+        <v>82305865.81</v>
       </c>
     </row>
     <row r="64">
@@ -2682,34 +2688,34 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>SEE</t>
+          <t>PMMG</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1261</v>
+        <v>1251</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE EDUCACAO</t>
+          <t>POLICIA MILITAR DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>17449007243.25</v>
+        <v>13028366670.83</v>
       </c>
       <c r="F64" t="n">
-        <v>16913371691.71</v>
+        <v>12841769394.38</v>
       </c>
       <c r="G64" t="n">
-        <v>16658293209.57</v>
+        <v>12810307610.08</v>
       </c>
       <c r="H64" t="n">
-        <v>258732199.34</v>
+        <v>36489178.11</v>
       </c>
       <c r="I64" t="n">
-        <v>420280749.51</v>
+        <v>226080162.79</v>
       </c>
       <c r="J64" t="n">
-        <v>679012948.85</v>
+        <v>262569340.9</v>
       </c>
     </row>
     <row r="65">
@@ -2718,35 +2724,29 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>SEF</t>
+          <t>SCC</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1191</v>
+        <v>1721</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE FAZENDA</t>
+          <t>SECRETARIA DE ESTADO DA CASA CIVIL</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1549832807.14</v>
+        <v>5572590.71</v>
       </c>
       <c r="F65" t="n">
-        <v>1487682339.64</v>
+        <v>5270468.4</v>
       </c>
       <c r="G65" t="n">
-        <v>1468478278.25</v>
-      </c>
-      <c r="H65" t="n">
-        <v>5469083</v>
-      </c>
-      <c r="I65" t="n">
-        <v>34680028.15</v>
-      </c>
-      <c r="J65" t="n">
-        <v>40149111.15</v>
-      </c>
+        <v>4983565.3</v>
+      </c>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -2754,34 +2754,34 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>SEGOV</t>
+          <t>SEAPA</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1491</v>
+        <v>1231</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE GOVERNO</t>
+          <t>SECRETARIA DE ESTADO DE AGRICULTURA, PECUARIA E ABASTECIMENTO - SEAPA</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>614122774.96</v>
+        <v>157335344.34</v>
       </c>
       <c r="F66" t="n">
-        <v>581433110.22</v>
+        <v>140995120.89</v>
       </c>
       <c r="G66" t="n">
-        <v>577033471.5</v>
+        <v>122957383.2</v>
       </c>
       <c r="H66" t="n">
-        <v>8649196.529999999</v>
+        <v>7823519.95</v>
       </c>
       <c r="I66" t="n">
-        <v>27927671.89</v>
+        <v>3775929.39</v>
       </c>
       <c r="J66" t="n">
-        <v>36576868.42</v>
+        <v>11599449.34</v>
       </c>
     </row>
     <row r="67">
@@ -2790,34 +2790,34 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>SEINFRA</t>
+          <t>SEC. GERAL</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1301</v>
+        <v>1631</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIAS</t>
+          <t>SECRETARIA-GERAL</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1210413287.27</v>
+        <v>64901564.21</v>
       </c>
       <c r="F67" t="n">
-        <v>948715257.75</v>
+        <v>59419458.57</v>
       </c>
       <c r="G67" t="n">
-        <v>820248138.33</v>
+        <v>57509982.39</v>
       </c>
       <c r="H67" t="n">
-        <v>79551005.90000001</v>
+        <v>777.25</v>
       </c>
       <c r="I67" t="n">
-        <v>47275927.88</v>
+        <v>22162487.86</v>
       </c>
       <c r="J67" t="n">
-        <v>126826933.78</v>
+        <v>22163265.11</v>
       </c>
     </row>
     <row r="68">
@@ -2826,35 +2826,29 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>SEJUSP</t>
+          <t>SECOM</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1451</v>
+        <v>1711</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE JUSTICA E SEGURANCA PUBLICA</t>
+          <t>SECRETARIA DE ESTADO DE COMUNICACAO SOCIAL</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>3781312622.12</v>
+        <v>85247066.05</v>
       </c>
       <c r="F68" t="n">
-        <v>3625298484.23</v>
+        <v>32467458.6</v>
       </c>
       <c r="G68" t="n">
-        <v>3596218710.39</v>
-      </c>
-      <c r="H68" t="n">
-        <v>19811807.26</v>
-      </c>
-      <c r="I68" t="n">
-        <v>100572066.62</v>
-      </c>
-      <c r="J68" t="n">
-        <v>120383873.88</v>
-      </c>
+        <v>31192326.84</v>
+      </c>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -2862,34 +2856,34 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>SEMAD</t>
+          <t>SECULT</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1371</v>
+        <v>1271</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTAVEL</t>
+          <t>SECRETARIA DE ESTADO DE CULTURA E TURISMO</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>208856328.28</v>
+        <v>89313458.84</v>
       </c>
       <c r="F69" t="n">
-        <v>202130317.06</v>
+        <v>86513089.77</v>
       </c>
       <c r="G69" t="n">
-        <v>183745409.62</v>
+        <v>82380637.92</v>
       </c>
       <c r="H69" t="n">
-        <v>3452019.16</v>
+        <v>1333330.75</v>
       </c>
       <c r="I69" t="n">
-        <v>2453491.44</v>
+        <v>896505.38</v>
       </c>
       <c r="J69" t="n">
-        <v>5905510.6</v>
+        <v>2229836.13</v>
       </c>
     </row>
     <row r="70">
@@ -2898,34 +2892,34 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>SEPLAG</t>
+          <t>SEDE</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1501</v>
+        <v>1221</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTAO</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONOMICO</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>558633697.6799999</v>
+        <v>71019848</v>
       </c>
       <c r="F70" t="n">
-        <v>499616023.57</v>
+        <v>49587285.62</v>
       </c>
       <c r="G70" t="n">
-        <v>469179324</v>
+        <v>28903226.95</v>
       </c>
       <c r="H70" t="n">
-        <v>3809874.58</v>
+        <v>468159.26</v>
       </c>
       <c r="I70" t="n">
-        <v>18299317.45</v>
+        <v>8730755.23</v>
       </c>
       <c r="J70" t="n">
-        <v>22109192.03</v>
+        <v>9198914.49</v>
       </c>
     </row>
     <row r="71">
@@ -2934,34 +2928,34 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>TV MINAS</t>
+          <t>SEDESE</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>2211</v>
+        <v>1481</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>FUNDACAO TV MINAS CULTURAL E EDUCATIVA</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>16156823.34</v>
+        <v>278200685.86</v>
       </c>
       <c r="F71" t="n">
-        <v>15396119.26</v>
+        <v>258721057.71</v>
       </c>
       <c r="G71" t="n">
-        <v>14519942.39</v>
+        <v>187380767.61</v>
       </c>
       <c r="H71" t="n">
-        <v>113058.43</v>
+        <v>13128483.79</v>
       </c>
       <c r="I71" t="n">
-        <v>599716.37</v>
+        <v>14858520.74</v>
       </c>
       <c r="J71" t="n">
-        <v>712774.8</v>
+        <v>27987004.53</v>
       </c>
     </row>
     <row r="72">
@@ -2970,34 +2964,34 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>UEMG</t>
+          <t>SEE</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>2351</v>
+        <v>1261</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>UNIVERSIDADE DO ESTADO DE MINAS GERAIS</t>
+          <t>SECRETARIA DE ESTADO DE EDUCACAO</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>404521667.47</v>
+        <v>17449007243.25</v>
       </c>
       <c r="F72" t="n">
-        <v>384928295.57</v>
+        <v>16913371691.71</v>
       </c>
       <c r="G72" t="n">
-        <v>374712336.29</v>
+        <v>16658293209.57</v>
       </c>
       <c r="H72" t="n">
-        <v>6005270.76</v>
+        <v>258732199.34</v>
       </c>
       <c r="I72" t="n">
-        <v>21210103.71</v>
+        <v>420280749.51</v>
       </c>
       <c r="J72" t="n">
-        <v>27215374.47</v>
+        <v>679012948.85</v>
       </c>
     </row>
     <row r="73">
@@ -3006,34 +3000,34 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>UNIMONTES</t>
+          <t>SEF</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>2311</v>
+        <v>1191</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>UNIVERSIDADE ESTADUAL DE MONTES CLAROS</t>
+          <t>SECRETARIA DE ESTADO DE FAZENDA</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>469927618.13</v>
+        <v>1549832807.14</v>
       </c>
       <c r="F73" t="n">
-        <v>414313756.03</v>
+        <v>1487682339.64</v>
       </c>
       <c r="G73" t="n">
-        <v>405713436.11</v>
+        <v>1468478278.25</v>
       </c>
       <c r="H73" t="n">
-        <v>1205407.47</v>
+        <v>5469083</v>
       </c>
       <c r="I73" t="n">
-        <v>16962260.8</v>
+        <v>34680028.15</v>
       </c>
       <c r="J73" t="n">
-        <v>18167668.27</v>
+        <v>40149111.15</v>
       </c>
     </row>
     <row r="74">
@@ -3042,33 +3036,423 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
+          <t>SEGOV</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>1491</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE GOVERNO</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>614122774.96</v>
+      </c>
+      <c r="F74" t="n">
+        <v>581433110.22</v>
+      </c>
+      <c r="G74" t="n">
+        <v>577033471.5</v>
+      </c>
+      <c r="H74" t="n">
+        <v>8649196.529999999</v>
+      </c>
+      <c r="I74" t="n">
+        <v>27927671.89</v>
+      </c>
+      <c r="J74" t="n">
+        <v>36576868.42</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>SEINFRA</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1301</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIAS</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>1210413287.27</v>
+      </c>
+      <c r="F75" t="n">
+        <v>948715257.75</v>
+      </c>
+      <c r="G75" t="n">
+        <v>820248138.33</v>
+      </c>
+      <c r="H75" t="n">
+        <v>79551005.90000001</v>
+      </c>
+      <c r="I75" t="n">
+        <v>47275927.88</v>
+      </c>
+      <c r="J75" t="n">
+        <v>126826933.78</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>SEJUSP</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>1451</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE JUSTICA E SEGURANCA PUBLICA</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>3781312622.12</v>
+      </c>
+      <c r="F76" t="n">
+        <v>3625298484.23</v>
+      </c>
+      <c r="G76" t="n">
+        <v>3596218710.39</v>
+      </c>
+      <c r="H76" t="n">
+        <v>19811807.26</v>
+      </c>
+      <c r="I76" t="n">
+        <v>100572066.62</v>
+      </c>
+      <c r="J76" t="n">
+        <v>120383873.88</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>SEMAD</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>1371</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTAVEL</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>208856328.28</v>
+      </c>
+      <c r="F77" t="n">
+        <v>202130317.06</v>
+      </c>
+      <c r="G77" t="n">
+        <v>183745409.62</v>
+      </c>
+      <c r="H77" t="n">
+        <v>3452019.16</v>
+      </c>
+      <c r="I77" t="n">
+        <v>2453491.44</v>
+      </c>
+      <c r="J77" t="n">
+        <v>5905510.6</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>SEPLAG</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>1501</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTAO</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>558633697.6799999</v>
+      </c>
+      <c r="F78" t="n">
+        <v>499616023.57</v>
+      </c>
+      <c r="G78" t="n">
+        <v>469179324</v>
+      </c>
+      <c r="H78" t="n">
+        <v>3809874.58</v>
+      </c>
+      <c r="I78" t="n">
+        <v>18299317.45</v>
+      </c>
+      <c r="J78" t="n">
+        <v>22109192.03</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>TCEMG</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>1021</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>TRIBUNAL DE CONTAS DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>1031554980.46</v>
+      </c>
+      <c r="F79" t="n">
+        <v>1011187631.34</v>
+      </c>
+      <c r="G79" t="n">
+        <v>1000081162.41</v>
+      </c>
+      <c r="H79" t="n">
+        <v>2349.38</v>
+      </c>
+      <c r="I79" t="n">
+        <v>13089699.04</v>
+      </c>
+      <c r="J79" t="n">
+        <v>13092048.42</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>TJMG</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>1031</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>TRIBUNAL DE JUSTICA DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>8552007441.49</v>
+      </c>
+      <c r="F80" t="n">
+        <v>8552007441.49</v>
+      </c>
+      <c r="G80" t="n">
+        <v>8552432135.36</v>
+      </c>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>TJMMG</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>1051</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>TRIBUNAL DE JUSTICA MILITAR DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>105322332.72</v>
+      </c>
+      <c r="F81" t="n">
+        <v>100216812.04</v>
+      </c>
+      <c r="G81" t="n">
+        <v>99085341.56999999</v>
+      </c>
+      <c r="H81" t="n">
+        <v>103192.45</v>
+      </c>
+      <c r="I81" t="n">
+        <v>3844435.05</v>
+      </c>
+      <c r="J81" t="n">
+        <v>3947627.5</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>TV MINAS</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>2211</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>FUNDACAO TV MINAS CULTURAL E EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>16156823.34</v>
+      </c>
+      <c r="F82" t="n">
+        <v>15396119.26</v>
+      </c>
+      <c r="G82" t="n">
+        <v>14519942.39</v>
+      </c>
+      <c r="H82" t="n">
+        <v>113058.43</v>
+      </c>
+      <c r="I82" t="n">
+        <v>599716.37</v>
+      </c>
+      <c r="J82" t="n">
+        <v>712774.8</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>UEMG</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>2351</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>UNIVERSIDADE DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>404521667.47</v>
+      </c>
+      <c r="F83" t="n">
+        <v>384928295.57</v>
+      </c>
+      <c r="G83" t="n">
+        <v>374712336.29</v>
+      </c>
+      <c r="H83" t="n">
+        <v>6005270.76</v>
+      </c>
+      <c r="I83" t="n">
+        <v>21210103.71</v>
+      </c>
+      <c r="J83" t="n">
+        <v>27215374.47</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>UNIMONTES</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>2311</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>UNIVERSIDADE ESTADUAL DE MONTES CLAROS</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>469927618.13</v>
+      </c>
+      <c r="F84" t="n">
+        <v>414313756.03</v>
+      </c>
+      <c r="G84" t="n">
+        <v>405713436.11</v>
+      </c>
+      <c r="H84" t="n">
+        <v>1205407.47</v>
+      </c>
+      <c r="I84" t="n">
+        <v>16962260.8</v>
+      </c>
+      <c r="J84" t="n">
+        <v>18167668.27</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
           <t>UTRAMIG</t>
         </is>
       </c>
-      <c r="C74" t="n">
+      <c r="C85" t="n">
         <v>2281</v>
       </c>
-      <c r="D74" t="inlineStr">
+      <c r="D85" t="inlineStr">
         <is>
           <t>FUNDACAO DE EDUCACAO PARA O TRABALHO DE MINAS GERAIS</t>
         </is>
       </c>
-      <c r="E74" t="n">
+      <c r="E85" t="n">
         <v>6125588.94</v>
       </c>
-      <c r="F74" t="n">
+      <c r="F85" t="n">
         <v>5821567.34</v>
       </c>
-      <c r="G74" t="n">
+      <c r="G85" t="n">
         <v>5483571.33</v>
       </c>
-      <c r="H74" t="n">
+      <c r="H85" t="n">
         <v>24344.67</v>
       </c>
-      <c r="I74" t="n">
+      <c r="I85" t="n">
         <v>193381.66</v>
       </c>
-      <c r="J74" t="n">
+      <c r="J85" t="n">
         <v>217726.33</v>
       </c>
     </row>

--- a/upload/orgao2023.xlsx
+++ b/upload/orgao2023.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J85"/>
+  <dimension ref="A1:I86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,15 +466,10 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Valor Pago Processado</t>
+          <t>Valor Liquidado RP</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Valor Pago Não Processado</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Valor Pago RP</t>
         </is>
@@ -498,21 +493,18 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1163303001.26</v>
+        <v>25517625.37</v>
       </c>
       <c r="F2" t="n">
-        <v>1160222383.64</v>
+        <v>23278329.8</v>
       </c>
       <c r="G2" t="n">
-        <v>1001681057.22</v>
+        <v>21310053.47</v>
       </c>
       <c r="H2" t="n">
-        <v>29087656.78</v>
+        <v>3071386.34</v>
       </c>
       <c r="I2" t="n">
-        <v>3000988.94</v>
-      </c>
-      <c r="J2" t="n">
         <v>32088645.72</v>
       </c>
     </row>
@@ -534,21 +526,18 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6692249.88</v>
+        <v>2231134.65</v>
       </c>
       <c r="F3" t="n">
-        <v>5732550.69</v>
+        <v>1316091.99</v>
       </c>
       <c r="G3" t="n">
-        <v>5640278.65</v>
+        <v>1223729.1</v>
       </c>
       <c r="H3" t="n">
-        <v>44191.45</v>
+        <v>9442.959999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>9439.76</v>
-      </c>
-      <c r="J3" t="n">
         <v>53631.21</v>
       </c>
     </row>
@@ -570,21 +559,18 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1903297527.8</v>
+        <v>149200147.28</v>
       </c>
       <c r="F4" t="n">
-        <v>1874294477.86</v>
+        <v>123661987.34</v>
       </c>
       <c r="G4" t="n">
-        <v>1861899226.21</v>
+        <v>114934763.03</v>
       </c>
       <c r="H4" t="n">
-        <v>3920.75</v>
+        <v>139561362</v>
       </c>
       <c r="I4" t="n">
-        <v>117462912.92</v>
-      </c>
-      <c r="J4" t="n">
         <v>117466833.67</v>
       </c>
     </row>
@@ -606,23 +592,20 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3919274.27</v>
+        <v>1886555.58</v>
       </c>
       <c r="F5" t="n">
-        <v>3274957.97</v>
+        <v>1253560.43</v>
       </c>
       <c r="G5" t="n">
-        <v>2995203.29</v>
+        <v>976873.5699999999</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>715433.6</v>
       </c>
       <c r="I5" t="n">
         <v>526357.61</v>
       </c>
-      <c r="J5" t="n">
-        <v>526357.61</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -642,23 +625,20 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>17351140.01</v>
+        <v>2248938.91</v>
       </c>
       <c r="F6" t="n">
-        <v>16698417.52</v>
+        <v>1653847.62</v>
       </c>
       <c r="G6" t="n">
-        <v>16573785.26</v>
+        <v>1527703.75</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>640038.33</v>
       </c>
       <c r="I6" t="n">
         <v>611025.34</v>
       </c>
-      <c r="J6" t="n">
-        <v>611025.34</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -678,21 +658,18 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1564505806.66</v>
+        <v>146395724.6</v>
       </c>
       <c r="F7" t="n">
-        <v>1472603650.09</v>
+        <v>54958228.46</v>
       </c>
       <c r="G7" t="n">
-        <v>1466343606.91</v>
+        <v>48820508.66</v>
       </c>
       <c r="H7" t="n">
-        <v>7744878.53</v>
+        <v>39061066.04</v>
       </c>
       <c r="I7" t="n">
-        <v>30546600.96</v>
-      </c>
-      <c r="J7" t="n">
         <v>38291479.49</v>
       </c>
     </row>
@@ -714,21 +691,18 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>60102963.54</v>
+        <v>2527896.01</v>
       </c>
       <c r="F8" t="n">
-        <v>59580613.9</v>
+        <v>2036996.43</v>
       </c>
       <c r="G8" t="n">
-        <v>59323104.46</v>
+        <v>1844302.12</v>
       </c>
       <c r="H8" t="n">
-        <v>77665.00999999999</v>
+        <v>199993.11</v>
       </c>
       <c r="I8" t="n">
-        <v>197493.6</v>
-      </c>
-      <c r="J8" t="n">
         <v>275158.61</v>
       </c>
     </row>
@@ -750,21 +724,18 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>853902750.97</v>
+        <v>107486336.52</v>
       </c>
       <c r="F9" t="n">
-        <v>823500196.72</v>
+        <v>79962153.77</v>
       </c>
       <c r="G9" t="n">
-        <v>816971152.8200001</v>
+        <v>73017715.38</v>
       </c>
       <c r="H9" t="n">
-        <v>2699.3</v>
+        <v>14185479.88</v>
       </c>
       <c r="I9" t="n">
-        <v>13731269.67</v>
-      </c>
-      <c r="J9" t="n">
         <v>13733968.97</v>
       </c>
     </row>
@@ -786,21 +757,18 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1914847566.85</v>
+        <v>1644491070.63</v>
       </c>
       <c r="F10" t="n">
-        <v>1044533400.24</v>
+        <v>798578802.99</v>
       </c>
       <c r="G10" t="n">
-        <v>966297540.79</v>
+        <v>779153132.4</v>
       </c>
       <c r="H10" t="n">
-        <v>16445711.3</v>
+        <v>321118810.84</v>
       </c>
       <c r="I10" t="n">
-        <v>318972727.76</v>
-      </c>
-      <c r="J10" t="n">
         <v>335418439.06</v>
       </c>
     </row>
@@ -821,22 +789,13 @@
           <t>EGE SEC.FAZENDA-ENCARGOS DIVERSOS</t>
         </is>
       </c>
-      <c r="E11" t="n">
-        <v>854860168.33</v>
-      </c>
-      <c r="F11" t="n">
-        <v>765439410.1</v>
-      </c>
-      <c r="G11" t="n">
-        <v>765416129.62</v>
-      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>25335200.02</v>
+        <v>609616599.35</v>
       </c>
       <c r="I11" t="n">
-        <v>609616599.35</v>
-      </c>
-      <c r="J11" t="n">
         <v>634951799.37</v>
       </c>
     </row>
@@ -858,13 +817,13 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>196770413.59</v>
+        <v>588259.27</v>
       </c>
       <c r="F12" t="n">
-        <v>196243687.54</v>
+        <v>61533.22</v>
       </c>
       <c r="G12" t="n">
-        <v>196240526.92</v>
+        <v>58372.6</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -872,9 +831,6 @@
       <c r="I12" t="n">
         <v>0</v>
       </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -904,7 +860,6 @@
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -934,7 +889,6 @@
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -942,29 +896,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EPAMIG</t>
+          <t>EMG - ADM. DIRETA</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3051</v>
+        <v>9999</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>EMPRESA DE PESQUISA AGROPECUARIA DE MINAS GERAIS</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>129507075.06</v>
-      </c>
-      <c r="F15" t="n">
-        <v>129507075.06</v>
-      </c>
-      <c r="G15" t="n">
-        <v>129507075.06</v>
-      </c>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -972,35 +919,28 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ESP MG</t>
+          <t>EPAMIG</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1541</v>
+        <v>3051</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>ESCOLA DE SAUDE PUBLICA DO ESTADO DE MINAS GERAIS</t>
+          <t>EMPRESA DE PESQUISA AGROPECUARIA DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>19938984.92</v>
+        <v>129507075.06</v>
       </c>
       <c r="F16" t="n">
-        <v>19458800.92</v>
+        <v>129507075.06</v>
       </c>
       <c r="G16" t="n">
-        <v>19168057.7</v>
-      </c>
-      <c r="H16" t="n">
-        <v>8211.5</v>
-      </c>
-      <c r="I16" t="n">
-        <v>116097.68</v>
-      </c>
-      <c r="J16" t="n">
-        <v>124309.18</v>
-      </c>
+        <v>129507075.06</v>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1008,34 +948,31 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>FAHMEMG</t>
+          <t>ESP MG</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>4541</v>
+        <v>1541</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>FUNDO DE APOIO HABITACIONAL AOS MILITARES DO ESTADO DE MINAS GERAIS</t>
+          <t>ESCOLA DE SAUDE PUBLICA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>362500</v>
+        <v>4126998.81</v>
       </c>
       <c r="F17" t="n">
-        <v>327310.98</v>
+        <v>3655143.63</v>
       </c>
       <c r="G17" t="n">
-        <v>320259.33</v>
+        <v>3363232.22</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>117578.81</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
+        <v>124309.18</v>
       </c>
     </row>
     <row r="18">
@@ -1044,34 +981,31 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>FAOP</t>
+          <t>FAHMEMG</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2171</v>
+        <v>4541</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>FUNDACAO DE ARTE DE OURO PRETO</t>
+          <t>FUNDO DE APOIO HABITACIONAL AOS MILITARES DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4750004.05</v>
+        <v>362500</v>
       </c>
       <c r="F18" t="n">
-        <v>4345485.27</v>
+        <v>327310.98</v>
       </c>
       <c r="G18" t="n">
-        <v>4163957.5</v>
+        <v>320259.33</v>
       </c>
       <c r="H18" t="n">
-        <v>27405.6</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>295215.94</v>
-      </c>
-      <c r="J18" t="n">
-        <v>322621.54</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1080,34 +1014,31 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>FAPEMIG</t>
+          <t>FAOP</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2071</v>
+        <v>2171</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>FUNDACAO DE AMPARO A PESQUISA DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDACAO DE ARTE DE OURO PRETO</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>475574938.69</v>
+        <v>1312452.15</v>
       </c>
       <c r="F19" t="n">
-        <v>469867300.36</v>
+        <v>1092086.13</v>
       </c>
       <c r="G19" t="n">
-        <v>420221524.1</v>
+        <v>925280.8</v>
       </c>
       <c r="H19" t="n">
-        <v>12738999.81</v>
+        <v>317350.98</v>
       </c>
       <c r="I19" t="n">
-        <v>7274018.25</v>
-      </c>
-      <c r="J19" t="n">
-        <v>20013018.06</v>
+        <v>322621.54</v>
       </c>
     </row>
     <row r="20">
@@ -1116,34 +1047,31 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>FCS</t>
+          <t>FAPEMIG</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2181</v>
+        <v>2071</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>FUNDACAO CLOVIS SALGADO</t>
+          <t>FUNDACAO DE AMPARO A PESQUISA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>49628398.03</v>
+        <v>26298387.48</v>
       </c>
       <c r="F20" t="n">
-        <v>47405823.66</v>
+        <v>23422466.9</v>
       </c>
       <c r="G20" t="n">
-        <v>46275247.85</v>
+        <v>21341751.16</v>
       </c>
       <c r="H20" t="n">
-        <v>253.4</v>
+        <v>7419079.68</v>
       </c>
       <c r="I20" t="n">
-        <v>878433.0699999999</v>
-      </c>
-      <c r="J20" t="n">
-        <v>878686.47</v>
+        <v>20013018.06</v>
       </c>
     </row>
     <row r="21">
@@ -1152,29 +1080,32 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>FDM</t>
+          <t>FCS</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>4331</v>
+        <v>2181</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>FUNDO DE DESENVOLVIMENTO METROPOLITANO</t>
+          <t>FUNDACAO CLOVIS SALGADO</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>652279.16</v>
+        <v>11729852.55</v>
       </c>
       <c r="F21" t="n">
-        <v>254203.16</v>
+        <v>9980347.220000001</v>
       </c>
       <c r="G21" t="n">
-        <v>245243.42</v>
-      </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+        <v>8900099.630000001</v>
+      </c>
+      <c r="H21" t="n">
+        <v>947318.47</v>
+      </c>
+      <c r="I21" t="n">
+        <v>878686.47</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1182,35 +1113,28 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>FEAM</t>
+          <t>FDM</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2091</v>
+        <v>4331</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>FUNDACAO ESTADUAL DO MEIO AMBIENTE</t>
+          <t>FUNDO DE DESENVOLVIMENTO METROPOLITANO</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>43259418.77</v>
+        <v>652279.16</v>
       </c>
       <c r="F22" t="n">
-        <v>38126464.75</v>
+        <v>254203.16</v>
       </c>
       <c r="G22" t="n">
-        <v>37435935.06</v>
-      </c>
-      <c r="H22" t="n">
-        <v>95.91</v>
-      </c>
-      <c r="I22" t="n">
-        <v>37153.49</v>
-      </c>
-      <c r="J22" t="n">
-        <v>37249.4</v>
-      </c>
+        <v>245243.42</v>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1218,34 +1142,31 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>FEAS</t>
+          <t>FEAM</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>4251</v>
+        <v>2091</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE ASSISTENCIA SOCIAL</t>
+          <t>FUNDACAO ESTADUAL DO MEIO AMBIENTE</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>110854339.85</v>
+        <v>8419527.17</v>
       </c>
       <c r="F23" t="n">
-        <v>106583471.83</v>
+        <v>3312068.51</v>
       </c>
       <c r="G23" t="n">
-        <v>105151900.42</v>
+        <v>2791249.95</v>
       </c>
       <c r="H23" t="n">
-        <v>12672808.3</v>
+        <v>37195.09</v>
       </c>
       <c r="I23" t="n">
-        <v>17248454.85</v>
-      </c>
-      <c r="J23" t="n">
-        <v>29921263.15</v>
+        <v>37249.4</v>
       </c>
     </row>
     <row r="24">
@@ -1254,34 +1175,31 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>FEC</t>
+          <t>FEAS</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>4491</v>
+        <v>4251</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE CULTURA</t>
+          <t>FUNDO ESTADUAL DE ASSISTENCIA SOCIAL</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3940069.61</v>
+        <v>9703419.59</v>
       </c>
       <c r="F24" t="n">
-        <v>3940069.61</v>
+        <v>8661158.18</v>
       </c>
       <c r="G24" t="n">
-        <v>3184573.65</v>
+        <v>7905938.68</v>
       </c>
       <c r="H24" t="n">
-        <v>390021.88</v>
+        <v>17299806.98</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>390021.88</v>
+        <v>29921263.15</v>
       </c>
     </row>
     <row r="25">
@@ -1290,34 +1208,25 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>FEH</t>
+          <t>FEC</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>4101</v>
+        <v>4491</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE HABITACAO</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>16882559.96</v>
-      </c>
-      <c r="F25" t="n">
-        <v>15883952.89</v>
-      </c>
-      <c r="G25" t="n">
-        <v>15883952.89</v>
-      </c>
+          <t>FUNDO ESTADUAL DE CULTURA</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>707987.39</v>
-      </c>
-      <c r="J25" t="n">
-        <v>707987.39</v>
+        <v>390021.88</v>
       </c>
     </row>
     <row r="26">
@@ -1326,34 +1235,25 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>FEI</t>
+          <t>FEH</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>4601</v>
+        <v>4101</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DOS DIREITOS DO IDOSO</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>2887433.54</v>
-      </c>
-      <c r="F26" t="n">
-        <v>2887433.54</v>
-      </c>
-      <c r="G26" t="n">
-        <v>0</v>
-      </c>
+          <t>FUNDO ESTADUAL DE HABITACAO</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
-        <v>180000</v>
+        <v>707987.39</v>
       </c>
       <c r="I26" t="n">
-        <v>45000</v>
-      </c>
-      <c r="J26" t="n">
-        <v>225000</v>
+        <v>707987.39</v>
       </c>
     </row>
     <row r="27">
@@ -1362,34 +1262,25 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>FEPDC</t>
+          <t>FEI</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>4451</v>
+        <v>4601</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE PROTECAO E DEFESA DO CONSUMIDOR</t>
-        </is>
-      </c>
-      <c r="E27" t="n">
-        <v>35323915.03</v>
-      </c>
-      <c r="F27" t="n">
-        <v>16775518.72</v>
-      </c>
-      <c r="G27" t="n">
-        <v>15712214.16</v>
-      </c>
+          <t>FUNDO ESTADUAL DOS DIREITOS DO IDOSO</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
-        <v>1711.42</v>
+        <v>45000</v>
       </c>
       <c r="I27" t="n">
-        <v>370032.98</v>
-      </c>
-      <c r="J27" t="n">
-        <v>371744.4</v>
+        <v>225000</v>
       </c>
     </row>
     <row r="28">
@@ -1398,34 +1289,31 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>FEPJ</t>
+          <t>FEPDC</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>4031</v>
+        <v>4451</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>FUNDO ESPECIAL DO PODER JUDICIARIO DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDO ESTADUAL DE PROTECAO E DEFESA DO CONSUMIDOR</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2021294271.44</v>
+        <v>31110073.49</v>
       </c>
       <c r="F28" t="n">
-        <v>1695364467.38</v>
+        <v>12760139.8</v>
       </c>
       <c r="G28" t="n">
-        <v>1541166557.69</v>
+        <v>11692026.64</v>
       </c>
       <c r="H28" t="n">
-        <v>1469990.01</v>
+        <v>400230.85</v>
       </c>
       <c r="I28" t="n">
-        <v>148541174.34</v>
-      </c>
-      <c r="J28" t="n">
-        <v>150011164.35</v>
+        <v>371744.4</v>
       </c>
     </row>
     <row r="29">
@@ -1434,34 +1322,31 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>FES</t>
+          <t>FEPJ</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>4291</v>
+        <v>4031</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE SAUDE</t>
+          <t>FUNDO ESPECIAL DO PODER JUDICIARIO DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>11302215537.53</v>
+        <v>1512280643.71</v>
       </c>
       <c r="F29" t="n">
-        <v>10567487751.92</v>
+        <v>1229297668.75</v>
       </c>
       <c r="G29" t="n">
-        <v>10368587376.49</v>
+        <v>1079431804.58</v>
       </c>
       <c r="H29" t="n">
-        <v>876192598.35</v>
+        <v>160959527.1</v>
       </c>
       <c r="I29" t="n">
-        <v>462749484.48</v>
-      </c>
-      <c r="J29" t="n">
-        <v>1338942082.83</v>
+        <v>150011164.35</v>
       </c>
     </row>
     <row r="30">
@@ -1470,34 +1355,31 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>FESP-MG</t>
+          <t>FES</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>4691</v>
+        <v>4291</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE SEGURANCA PUBLICA DE MINAS GERAIS</t>
+          <t>FUNDO ESTADUAL DE SAUDE</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>56928753.65</v>
+        <v>1192579460.08</v>
       </c>
       <c r="F30" t="n">
-        <v>13274144.7</v>
+        <v>720185708.16</v>
       </c>
       <c r="G30" t="n">
-        <v>11948730.27</v>
+        <v>664999649.55</v>
       </c>
       <c r="H30" t="n">
-        <v>2022500.23</v>
+        <v>463516472.37</v>
       </c>
       <c r="I30" t="n">
-        <v>11009074.78</v>
-      </c>
-      <c r="J30" t="n">
-        <v>13031575.01</v>
+        <v>1338942082.83</v>
       </c>
     </row>
     <row r="31">
@@ -1506,34 +1388,31 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>FET-MG</t>
+          <t>FESP-MG</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>4701</v>
+        <v>4691</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DO TRABALHO DE MINAS GERAIS</t>
+          <t>FUNDO ESTADUAL DE SEGURANCA PUBLICA DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>481821.71</v>
+        <v>56925986.61</v>
       </c>
       <c r="F31" t="n">
-        <v>79007.12</v>
+        <v>13271419.52</v>
       </c>
       <c r="G31" t="n">
-        <v>75725.75999999999</v>
+        <v>11946623.9</v>
       </c>
       <c r="H31" t="n">
-        <v>4212.69</v>
+        <v>11212883.98</v>
       </c>
       <c r="I31" t="n">
-        <v>950789.36</v>
-      </c>
-      <c r="J31" t="n">
-        <v>955002.05</v>
+        <v>13031575.01</v>
       </c>
     </row>
     <row r="32">
@@ -1542,34 +1421,31 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>FFP - MG</t>
+          <t>FET-MG</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>4711</v>
+        <v>4701</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>FUNDO FINANCEIRO DE PREVIDENCIA DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDO ESTADUAL DO TRABALHO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>16707308683.78</v>
+        <v>472592.79</v>
       </c>
       <c r="F32" t="n">
-        <v>16706043073.46</v>
+        <v>69778.2</v>
       </c>
       <c r="G32" t="n">
-        <v>16714373495.87</v>
+        <v>64650.96</v>
       </c>
       <c r="H32" t="n">
-        <v>3616.02</v>
+        <v>950820.42</v>
       </c>
       <c r="I32" t="n">
-        <v>637267.26</v>
-      </c>
-      <c r="J32" t="n">
-        <v>640883.28</v>
+        <v>955002.05</v>
       </c>
     </row>
     <row r="33">
@@ -1578,34 +1454,31 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>FHA</t>
+          <t>FFP - MG</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>2151</v>
+        <v>4711</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>FUNDACAO HELENA ANTIPOFF</t>
+          <t>FUNDO FINANCEIRO DE PREVIDENCIA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>64938007.38</v>
+        <v>7864083.09</v>
       </c>
       <c r="F33" t="n">
-        <v>62329642.07</v>
+        <v>6822892.09</v>
       </c>
       <c r="G33" t="n">
-        <v>61232129.22</v>
+        <v>6219462.1</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>675751.08</v>
       </c>
       <c r="I33" t="n">
-        <v>2676209.5</v>
-      </c>
-      <c r="J33" t="n">
-        <v>2676209.5</v>
+        <v>640883.28</v>
       </c>
     </row>
     <row r="34">
@@ -1614,34 +1487,31 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>FHEMIG</t>
+          <t>FHA</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>2271</v>
+        <v>2151</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>FUNDACAO HOSPITALAR DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDACAO HELENA ANTIPOFF</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2164150549.42</v>
+        <v>20275126.04</v>
       </c>
       <c r="F34" t="n">
-        <v>2059482648.7</v>
+        <v>17822038.56</v>
       </c>
       <c r="G34" t="n">
-        <v>2019538042.37</v>
+        <v>16736938.65</v>
       </c>
       <c r="H34" t="n">
-        <v>3347619.96</v>
+        <v>2756987.01</v>
       </c>
       <c r="I34" t="n">
-        <v>95082172.20999999</v>
-      </c>
-      <c r="J34" t="n">
-        <v>98429792.17</v>
+        <v>2676209.5</v>
       </c>
     </row>
     <row r="35">
@@ -1650,34 +1520,31 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>FHIDRO</t>
+          <t>FHEMIG</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>4341</v>
+        <v>2271</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>FUNDO DE RECUPERACAO, PROTECAO E DESENVOLVIMENTO SUSTENTAVEL DAS BACIAS HIDROGRAFICAS DO ESTADO DE M</t>
+          <t>FUNDACAO HOSPITALAR DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>3424799.42</v>
+        <v>622441315.26</v>
       </c>
       <c r="F35" t="n">
-        <v>2738104.88</v>
+        <v>527240530.81</v>
       </c>
       <c r="G35" t="n">
-        <v>2250014.71</v>
+        <v>491367462.18</v>
       </c>
       <c r="H35" t="n">
-        <v>68971.2</v>
+        <v>96877587.59</v>
       </c>
       <c r="I35" t="n">
-        <v>75798.71000000001</v>
-      </c>
-      <c r="J35" t="n">
-        <v>144769.91</v>
+        <v>98429792.17</v>
       </c>
     </row>
     <row r="36">
@@ -1686,34 +1553,31 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>FIA</t>
+          <t>FHIDRO</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>4091</v>
+        <v>4341</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>FUNDO PARA A INFANCIA E A ADOLESCENCIA</t>
+          <t>FUNDO DE RECUPERACAO, PROTECAO E DESENVOLVIMENTO SUSTENTAVEL DAS BACIAS HIDROGRAFICAS DO ESTADO DE M</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>7031581.25</v>
+        <v>1349576.2</v>
       </c>
       <c r="F36" t="n">
-        <v>5241364.07</v>
+        <v>1049169.96</v>
       </c>
       <c r="G36" t="n">
-        <v>3380577.21</v>
+        <v>886601.54</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>87836.32000000001</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" t="n">
-        <v>0</v>
+        <v>144769.91</v>
       </c>
     </row>
     <row r="37">
@@ -1722,34 +1586,31 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>FJP</t>
+          <t>FIA</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>2061</v>
+        <v>4091</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>FUNDACAO JOAO PINHEIRO</t>
+          <t>FUNDO PARA A INFANCIA E A ADOLESCENCIA</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>65473442.71</v>
+        <v>2513870.18</v>
       </c>
       <c r="F37" t="n">
-        <v>62245323.49</v>
+        <v>723653</v>
       </c>
       <c r="G37" t="n">
-        <v>61139568.08</v>
+        <v>723653</v>
       </c>
       <c r="H37" t="n">
-        <v>658090.65</v>
+        <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>5690027.08</v>
-      </c>
-      <c r="J37" t="n">
-        <v>6348117.73</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -1758,34 +1619,31 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>FPE</t>
+          <t>FJP</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>4141</v>
+        <v>2061</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>FUNDO PENITENCIARIO ESTADUAL</t>
+          <t>FUNDACAO JOAO PINHEIRO</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>40613382.55</v>
+        <v>11552052.49</v>
       </c>
       <c r="F38" t="n">
-        <v>23565562.32</v>
+        <v>8541021.57</v>
       </c>
       <c r="G38" t="n">
-        <v>22676692.22</v>
+        <v>7513881.05</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>5895454.18</v>
       </c>
       <c r="I38" t="n">
-        <v>11408560.88</v>
-      </c>
-      <c r="J38" t="n">
-        <v>11408560.88</v>
+        <v>6348117.73</v>
       </c>
     </row>
     <row r="39">
@@ -1794,34 +1652,31 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>FPP - MG</t>
+          <t>FPE</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>4631</v>
+        <v>4141</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>FUNDO DE PAGAMENTO DE PARCERIAS PUBLICO - PRIVADAS DE MINAS GERAIS</t>
+          <t>FUNDO PENITENCIARIO ESTADUAL</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>860717853.34</v>
+        <v>40613382.55</v>
       </c>
       <c r="F39" t="n">
-        <v>307011647.13</v>
+        <v>23565562.32</v>
       </c>
       <c r="G39" t="n">
-        <v>282507517.43</v>
+        <v>22676692.22</v>
       </c>
       <c r="H39" t="n">
-        <v>344621.26</v>
+        <v>11555960.52</v>
       </c>
       <c r="I39" t="n">
-        <v>28865269.27</v>
-      </c>
-      <c r="J39" t="n">
-        <v>29209890.53</v>
+        <v>11408560.88</v>
       </c>
     </row>
     <row r="40">
@@ -1830,34 +1685,31 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>FUCAM</t>
+          <t>FPP - MG</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>2161</v>
+        <v>4631</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>FUNDACAO EDUCACIONAL CAIO MARTINS</t>
+          <t>FUNDO DE PAGAMENTO DE PARCERIAS PUBLICO - PRIVADAS DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>10901641.69</v>
+        <v>860717853.34</v>
       </c>
       <c r="F40" t="n">
-        <v>10318773.13</v>
+        <v>307011647.13</v>
       </c>
       <c r="G40" t="n">
-        <v>8998548.609999999</v>
+        <v>282507517.43</v>
       </c>
       <c r="H40" t="n">
-        <v>121569.88</v>
+        <v>29793561.38</v>
       </c>
       <c r="I40" t="n">
-        <v>1346214.75</v>
-      </c>
-      <c r="J40" t="n">
-        <v>1467784.63</v>
+        <v>29209890.53</v>
       </c>
     </row>
     <row r="41">
@@ -1866,34 +1718,31 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>FUNAPEC</t>
+          <t>FUCAM</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>4551</v>
+        <v>2161</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>FUNDO DE ASSISTENCIA AO PECULIO DOS SERVIDORES DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDACAO EDUCACIONAL CAIO MARTINS</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>72736739.48</v>
+        <v>1793986.81</v>
       </c>
       <c r="F41" t="n">
-        <v>71196549.09</v>
+        <v>1311300.79</v>
       </c>
       <c r="G41" t="n">
-        <v>71168742.39</v>
+        <v>992361.65</v>
       </c>
       <c r="H41" t="n">
-        <v>6853309.77</v>
+        <v>1347146.36</v>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" t="n">
-        <v>6853309.77</v>
+        <v>1467784.63</v>
       </c>
     </row>
     <row r="42">
@@ -1902,34 +1751,25 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>FUNDHAB</t>
+          <t>FUNAPEC</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>4121</v>
+        <v>4551</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>FUNDO DE APOIO HABITACIONAL DA ASSEMBLEIA LEGISLATIVA DE MINAS GERAIS</t>
-        </is>
-      </c>
-      <c r="E42" t="n">
-        <v>9679354.34</v>
-      </c>
-      <c r="F42" t="n">
-        <v>8669954.34</v>
-      </c>
-      <c r="G42" t="n">
-        <v>7633039.44</v>
-      </c>
+          <t>FUNDO DE ASSISTENCIA AO PECULIO DOS SERVIDORES DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
       <c r="H42" t="n">
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>644000</v>
-      </c>
-      <c r="J42" t="n">
-        <v>644000</v>
+        <v>6853309.77</v>
       </c>
     </row>
     <row r="43">
@@ -1938,34 +1778,25 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>FUNED</t>
+          <t>FUNDHAB</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>2261</v>
+        <v>4121</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>FUNDACAO EZEQUIEL DIAS</t>
-        </is>
-      </c>
-      <c r="E43" t="n">
-        <v>368684570.21</v>
-      </c>
-      <c r="F43" t="n">
-        <v>273219748.02</v>
-      </c>
-      <c r="G43" t="n">
-        <v>269618135.07</v>
-      </c>
+          <t>FUNDO DE APOIO HABITACIONAL DA ASSEMBLEIA LEGISLATIVA DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
       <c r="H43" t="n">
-        <v>8154203.6</v>
+        <v>700000</v>
       </c>
       <c r="I43" t="n">
-        <v>41399163.16</v>
-      </c>
-      <c r="J43" t="n">
-        <v>49553366.76</v>
+        <v>644000</v>
       </c>
     </row>
     <row r="44">
@@ -1974,34 +1805,31 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>FUNEMP</t>
+          <t>FUNED</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>4441</v>
+        <v>2261</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>FUNDO ESPECIAL DO MINISTERIO PUBLICO DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDACAO EZEQUIEL DIAS</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>41979113.94</v>
+        <v>248031943.01</v>
       </c>
       <c r="F44" t="n">
-        <v>18233630.68</v>
+        <v>152580734.75</v>
       </c>
       <c r="G44" t="n">
-        <v>17916399.77</v>
+        <v>149204258.7</v>
       </c>
       <c r="H44" t="n">
-        <v>19771.3</v>
+        <v>41680476.1</v>
       </c>
       <c r="I44" t="n">
-        <v>9428804.08</v>
-      </c>
-      <c r="J44" t="n">
-        <v>9448575.380000001</v>
+        <v>49553366.76</v>
       </c>
     </row>
     <row r="45">
@@ -2010,34 +1838,31 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>FUNTRANS</t>
+          <t>FUNEMP</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>4381</v>
+        <v>4441</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE DESENVOLVIMENTO DE TRANSPORTES</t>
+          <t>FUNDO ESPECIAL DO MINISTERIO PUBLICO DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>93182744.76000001</v>
+        <v>19070818.43</v>
       </c>
       <c r="F45" t="n">
-        <v>73453457.05</v>
+        <v>6234527.02</v>
       </c>
       <c r="G45" t="n">
-        <v>71188066.92</v>
+        <v>6178669.28</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>9702716.73</v>
       </c>
       <c r="I45" t="n">
-        <v>8330157.76</v>
-      </c>
-      <c r="J45" t="n">
-        <v>8330157.76</v>
+        <v>9448575.380000001</v>
       </c>
     </row>
     <row r="46">
@@ -2046,34 +1871,31 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>GABINETE MILITAR</t>
+          <t>FUNTRANS</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1071</v>
+        <v>4381</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>GABINETE MILITAR DO GOVERNADOR DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDO ESTADUAL DE DESENVOLVIMENTO DE TRANSPORTES</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>46143197.21</v>
+        <v>81032531.59999999</v>
       </c>
       <c r="F46" t="n">
-        <v>35398463.11</v>
+        <v>61303243.89</v>
       </c>
       <c r="G46" t="n">
-        <v>34050957.79</v>
+        <v>59037853.76</v>
       </c>
       <c r="H46" t="n">
-        <v>211337.1</v>
+        <v>8505412.32</v>
       </c>
       <c r="I46" t="n">
-        <v>3943260.33</v>
-      </c>
-      <c r="J46" t="n">
-        <v>4154597.43</v>
+        <v>8330157.76</v>
       </c>
     </row>
     <row r="47">
@@ -2082,34 +1904,31 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>GDPE - SEF</t>
+          <t>GABINETE MILITAR</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1916</v>
+        <v>1071</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>GESTAO DA DIVIDA PUBLICA ESTADUAL</t>
+          <t>GABINETE MILITAR DO GOVERNADOR DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4151422885</v>
+        <v>33560071.03</v>
       </c>
       <c r="F47" t="n">
-        <v>4151422885</v>
+        <v>22857322.72</v>
       </c>
       <c r="G47" t="n">
-        <v>3992987258.55</v>
+        <v>21413297.18</v>
       </c>
       <c r="H47" t="n">
-        <v>316225142.59</v>
+        <v>3960666.69</v>
       </c>
       <c r="I47" t="n">
-        <v>123029711.28</v>
-      </c>
-      <c r="J47" t="n">
-        <v>439254853.87</v>
+        <v>4154597.43</v>
       </c>
     </row>
     <row r="48">
@@ -2118,34 +1937,25 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>HEMOMINAS</t>
+          <t>GDPE - SEF</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>2321</v>
+        <v>1916</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>FUNDACAO CENTRO DE HEMATOLOGIA E HEMOTERAPIA DE MINAS GERAIS</t>
-        </is>
-      </c>
-      <c r="E48" t="n">
-        <v>355203535.23</v>
-      </c>
-      <c r="F48" t="n">
-        <v>320246686.79</v>
-      </c>
-      <c r="G48" t="n">
-        <v>311999002.94</v>
-      </c>
+          <t>GESTAO DA DIVIDA PUBLICA ESTADUAL</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
       <c r="H48" t="n">
-        <v>1679096.03</v>
+        <v>123029711.28</v>
       </c>
       <c r="I48" t="n">
-        <v>28146659.99</v>
-      </c>
-      <c r="J48" t="n">
-        <v>29825756.02</v>
+        <v>439254853.87</v>
       </c>
     </row>
     <row r="49">
@@ -2154,34 +1964,31 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>IDENE</t>
+          <t>HEMOMINAS</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>2421</v>
+        <v>2321</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>INSTITUTO DE DESENVOLVIMENTO DO NORTE E NORDESTE DE MINAS GERAIS</t>
+          <t>FUNDACAO CENTRO DE HEMATOLOGIA E HEMOTERAPIA DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100992421.24</v>
+        <v>162643674.6</v>
       </c>
       <c r="F49" t="n">
-        <v>76969361.8</v>
+        <v>128777478.18</v>
       </c>
       <c r="G49" t="n">
-        <v>75625489.05</v>
+        <v>121159826.32</v>
       </c>
       <c r="H49" t="n">
-        <v>163906.27</v>
+        <v>28363979.58</v>
       </c>
       <c r="I49" t="n">
-        <v>6105648.21</v>
-      </c>
-      <c r="J49" t="n">
-        <v>6269554.48</v>
+        <v>29825756.02</v>
       </c>
     </row>
     <row r="50">
@@ -2190,34 +1997,31 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>IEF</t>
+          <t>IDENE</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>2101</v>
+        <v>2421</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>INSTITUTO ESTADUAL DE FLORESTAS</t>
+          <t>INSTITUTO DE DESENVOLVIMENTO DO NORTE E NORDESTE DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>206253448.79</v>
+        <v>42970991.11</v>
       </c>
       <c r="F50" t="n">
-        <v>201049210.28</v>
+        <v>19200015.14</v>
       </c>
       <c r="G50" t="n">
-        <v>193758815.18</v>
+        <v>17850244.56</v>
       </c>
       <c r="H50" t="n">
-        <v>2044943.53</v>
+        <v>6121786.87</v>
       </c>
       <c r="I50" t="n">
-        <v>3790350.53</v>
-      </c>
-      <c r="J50" t="n">
-        <v>5835294.06</v>
+        <v>6269554.48</v>
       </c>
     </row>
     <row r="51">
@@ -2226,34 +2030,31 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>IEPHA</t>
+          <t>IEF</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>2201</v>
+        <v>2101</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>INSTITUTO ESTADUAL DO PATRIMONIO HISTORICO E ARTISTICO DE MINAS GERAIS</t>
+          <t>INSTITUTO ESTADUAL DE FLORESTAS</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>20854647.15</v>
+        <v>58426156.98</v>
       </c>
       <c r="F51" t="n">
-        <v>19794515.12</v>
+        <v>53728361.41</v>
       </c>
       <c r="G51" t="n">
-        <v>18916412.23</v>
+        <v>46601094.35</v>
       </c>
       <c r="H51" t="n">
-        <v>0</v>
+        <v>3969129.21</v>
       </c>
       <c r="I51" t="n">
-        <v>2810067.14</v>
-      </c>
-      <c r="J51" t="n">
-        <v>2810067.14</v>
+        <v>5835294.06</v>
       </c>
     </row>
     <row r="52">
@@ -2262,34 +2063,31 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>IGAM</t>
+          <t>IEPHA</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>2241</v>
+        <v>2201</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>INSTITUTO MINEIRO DE GESTAO DAS AGUAS</t>
+          <t>INSTITUTO ESTADUAL DO PATRIMONIO HISTORICO E ARTISTICO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>106797429.43</v>
+        <v>5437673.62</v>
       </c>
       <c r="F52" t="n">
-        <v>101404974.15</v>
+        <v>4469812.69</v>
       </c>
       <c r="G52" t="n">
-        <v>100479945.84</v>
+        <v>4013117.11</v>
       </c>
       <c r="H52" t="n">
-        <v>10446834.76</v>
+        <v>2832402.52</v>
       </c>
       <c r="I52" t="n">
-        <v>3875281.47</v>
-      </c>
-      <c r="J52" t="n">
-        <v>14322116.23</v>
+        <v>2810067.14</v>
       </c>
     </row>
     <row r="53">
@@ -2298,34 +2096,31 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>IMA</t>
+          <t>IGAM</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>2371</v>
+        <v>2241</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>INSTITUTO MINEIRO DE AGROPECUARIA</t>
+          <t>INSTITUTO MINEIRO DE GESTAO DAS AGUAS</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>247119982.84</v>
+        <v>12207246.44</v>
       </c>
       <c r="F53" t="n">
-        <v>242894139.49</v>
+        <v>7136764.87</v>
       </c>
       <c r="G53" t="n">
-        <v>242543975.53</v>
+        <v>6274355.82</v>
       </c>
       <c r="H53" t="n">
-        <v>378714.11</v>
+        <v>3912639.56</v>
       </c>
       <c r="I53" t="n">
-        <v>3948517.78</v>
-      </c>
-      <c r="J53" t="n">
-        <v>4327231.89</v>
+        <v>14322116.23</v>
       </c>
     </row>
     <row r="54">
@@ -2334,34 +2129,31 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>IPEMMG</t>
+          <t>IMA</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>2331</v>
+        <v>2371</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>INSTITUTO DE METROLOGIA E QUALIDADE DO ESTADO DE MINAS GERAIS</t>
+          <t>INSTITUTO MINEIRO DE AGROPECUARIA</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>30989568.55</v>
+        <v>19550978.74</v>
       </c>
       <c r="F54" t="n">
-        <v>30394216.46</v>
+        <v>15544112.38</v>
       </c>
       <c r="G54" t="n">
-        <v>28953199.86</v>
+        <v>14760660.38</v>
       </c>
       <c r="H54" t="n">
-        <v>78441.50999999999</v>
+        <v>3975858.87</v>
       </c>
       <c r="I54" t="n">
-        <v>108549.11</v>
-      </c>
-      <c r="J54" t="n">
-        <v>186990.62</v>
+        <v>4327231.89</v>
       </c>
     </row>
     <row r="55">
@@ -2370,29 +2162,32 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>IPLEMG</t>
+          <t>IPEMMG</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>2361</v>
+        <v>2331</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>INSTITUTO DE PREVIDENCIA DO LEGISLATIVO DO ESTADO DE MINAS GERAIS</t>
+          <t>INSTITUTO DE METROLOGIA E QUALIDADE DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>60477343.11</v>
+        <v>11757137.13</v>
       </c>
       <c r="F55" t="n">
-        <v>60477343.11</v>
+        <v>11165764.45</v>
       </c>
       <c r="G55" t="n">
-        <v>60477343.11</v>
-      </c>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
+        <v>9635999.789999999</v>
+      </c>
+      <c r="H55" t="n">
+        <v>109677.26</v>
+      </c>
+      <c r="I55" t="n">
+        <v>186990.62</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -2400,35 +2195,28 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>IPSEMG</t>
+          <t>IPLEMG</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>2011</v>
+        <v>2361</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>INSTITUTO DE PREVIDENCIA DOS SERVIDORES DO ESTADO DE MINAS GERAIS</t>
+          <t>INSTITUTO DE PREVIDENCIA DO LEGISLATIVO DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1616992072.96</v>
+        <v>60477343.11</v>
       </c>
       <c r="F56" t="n">
-        <v>1414919735.8</v>
+        <v>60477343.11</v>
       </c>
       <c r="G56" t="n">
-        <v>1379497007.69</v>
-      </c>
-      <c r="H56" t="n">
-        <v>2730465.24</v>
-      </c>
-      <c r="I56" t="n">
-        <v>139505498.51</v>
-      </c>
-      <c r="J56" t="n">
-        <v>142235963.75</v>
-      </c>
+        <v>60477343.11</v>
+      </c>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -2436,34 +2224,31 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>IPSM</t>
+          <t>IPSEMG</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>2121</v>
+        <v>2011</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>INSTITUTO DE PREVIDENCIA DOS SERVIDORES MILITARES DO ESTADO DE MINAS GERAIS</t>
+          <t>INSTITUTO DE PREVIDENCIA DOS SERVIDORES DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2900878606.77</v>
+        <v>234090693.26</v>
       </c>
       <c r="F57" t="n">
-        <v>2876463795.17</v>
+        <v>196169728.33</v>
       </c>
       <c r="G57" t="n">
-        <v>2327341436.54</v>
+        <v>183138527.93</v>
       </c>
       <c r="H57" t="n">
-        <v>102308456.42</v>
+        <v>142256133.2</v>
       </c>
       <c r="I57" t="n">
-        <v>33347552.64</v>
-      </c>
-      <c r="J57" t="n">
-        <v>135656009.06</v>
+        <v>142235963.75</v>
       </c>
     </row>
     <row r="58">
@@ -2472,34 +2257,31 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>JUCEMG</t>
+          <t>IPSM</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>2251</v>
+        <v>2121</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>JUNTA COMERCIAL DO ESTADO DE MINAS GERAIS</t>
+          <t>INSTITUTO DE PREVIDENCIA DOS SERVIDORES MILITARES DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>30826852.4</v>
+        <v>103552127.73</v>
       </c>
       <c r="F58" t="n">
-        <v>29563968.03</v>
+        <v>91839707.87</v>
       </c>
       <c r="G58" t="n">
-        <v>29011549.3</v>
+        <v>78998672.90000001</v>
       </c>
       <c r="H58" t="n">
-        <v>565.47</v>
+        <v>34663079.88</v>
       </c>
       <c r="I58" t="n">
-        <v>746119.0600000001</v>
-      </c>
-      <c r="J58" t="n">
-        <v>746684.53</v>
+        <v>135656009.06</v>
       </c>
     </row>
     <row r="59">
@@ -2508,34 +2290,31 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>LEMG</t>
+          <t>JUCEMG</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>2041</v>
+        <v>2251</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LOTERIA DO ESTADO DE MINAS GERAIS</t>
+          <t>JUNTA COMERCIAL DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>3423162.82</v>
+        <v>8366577.93</v>
       </c>
       <c r="F59" t="n">
-        <v>3283189.87</v>
+        <v>7185812.87</v>
       </c>
       <c r="G59" t="n">
-        <v>3280441.52</v>
+        <v>6800385.69</v>
       </c>
       <c r="H59" t="n">
-        <v>0</v>
+        <v>775499.85</v>
       </c>
       <c r="I59" t="n">
-        <v>6507</v>
-      </c>
-      <c r="J59" t="n">
-        <v>6507</v>
+        <v>746684.53</v>
       </c>
     </row>
     <row r="60">
@@ -2544,34 +2323,31 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>OGE</t>
+          <t>LEMG</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1101</v>
+        <v>2041</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>OUVIDORIA-GERAL DO ESTADO DE MINAS GERAIS</t>
+          <t>LOTERIA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>14788301.67</v>
+        <v>213976.29</v>
       </c>
       <c r="F60" t="n">
-        <v>14630579.61</v>
+        <v>93912.67999999999</v>
       </c>
       <c r="G60" t="n">
-        <v>14490566</v>
+        <v>90842.75999999999</v>
       </c>
       <c r="H60" t="n">
-        <v>0</v>
+        <v>6561.01</v>
       </c>
       <c r="I60" t="n">
-        <v>94372.77</v>
-      </c>
-      <c r="J60" t="n">
-        <v>94372.77</v>
+        <v>6507</v>
       </c>
     </row>
     <row r="61">
@@ -2580,34 +2356,25 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>PARTICIPAÇÃO EMPRESAS</t>
+          <t>MG INVESTE</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1915</v>
+        <v>4621</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>PARTICIPACAO NO AUMENTO DO CAPITAL SOCIAL DE EMPRESAS</t>
-        </is>
-      </c>
-      <c r="E61" t="n">
-        <v>508647503.2</v>
-      </c>
-      <c r="F61" t="n">
-        <v>3647503.2</v>
-      </c>
-      <c r="G61" t="n">
-        <v>3647503.2</v>
-      </c>
+          <t>FUNDO DE INVESTIMENTO DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr"/>
       <c r="H61" t="n">
         <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>75202844.75</v>
-      </c>
-      <c r="J61" t="n">
-        <v>75202844.75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -2616,34 +2383,31 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>PCMG</t>
+          <t>OGE</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1511</v>
+        <v>1101</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>POLICIA CIVIL DO ESTADO DE MINAS GERAIS</t>
+          <t>OUVIDORIA-GERAL DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>3065566676.29</v>
+        <v>1731917.53</v>
       </c>
       <c r="F62" t="n">
-        <v>2994754625.68</v>
+        <v>1574195.47</v>
       </c>
       <c r="G62" t="n">
-        <v>2978077582.97</v>
+        <v>1432136.19</v>
       </c>
       <c r="H62" t="n">
-        <v>12864618.77</v>
+        <v>97893.33</v>
       </c>
       <c r="I62" t="n">
-        <v>79194935.12</v>
-      </c>
-      <c r="J62" t="n">
-        <v>92059553.89</v>
+        <v>94372.77</v>
       </c>
     </row>
     <row r="63">
@@ -2652,34 +2416,25 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>PGJ</t>
+          <t>PARTICIPAÇÃO EMPRESAS</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>1091</v>
+        <v>1915</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>PROCURADORIA GERAL DE JUSTICA</t>
-        </is>
-      </c>
-      <c r="E63" t="n">
-        <v>3497134160</v>
-      </c>
-      <c r="F63" t="n">
-        <v>3397602683.81</v>
-      </c>
-      <c r="G63" t="n">
-        <v>3372626349.55</v>
-      </c>
+          <t>PARTICIPACAO NO AUMENTO DO CAPITAL SOCIAL DE EMPRESAS</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr"/>
       <c r="H63" t="n">
-        <v>3341565.82</v>
+        <v>75202844.75</v>
       </c>
       <c r="I63" t="n">
-        <v>78964299.98999999</v>
-      </c>
-      <c r="J63" t="n">
-        <v>82305865.81</v>
+        <v>75202844.75</v>
       </c>
     </row>
     <row r="64">
@@ -2688,34 +2443,31 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>PMMG</t>
+          <t>PCMG</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1251</v>
+        <v>1511</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>POLICIA MILITAR DO ESTADO DE MINAS GERAIS</t>
+          <t>POLICIA CIVIL DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>13028366670.83</v>
+        <v>334343756.35</v>
       </c>
       <c r="F64" t="n">
-        <v>12841769394.38</v>
+        <v>264514139.86</v>
       </c>
       <c r="G64" t="n">
-        <v>12810307610.08</v>
+        <v>248476011.33</v>
       </c>
       <c r="H64" t="n">
-        <v>36489178.11</v>
+        <v>81114891.23</v>
       </c>
       <c r="I64" t="n">
-        <v>226080162.79</v>
-      </c>
-      <c r="J64" t="n">
-        <v>262569340.9</v>
+        <v>92059553.89</v>
       </c>
     </row>
     <row r="65">
@@ -2724,29 +2476,32 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>SCC</t>
+          <t>PGJ</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1721</v>
+        <v>1091</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DA CASA CIVIL</t>
+          <t>PROCURADORIA GERAL DE JUSTICA</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5572590.71</v>
+        <v>303672950.36</v>
       </c>
       <c r="F65" t="n">
-        <v>5270468.4</v>
+        <v>215585800.25</v>
       </c>
       <c r="G65" t="n">
-        <v>4983565.3</v>
-      </c>
-      <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
+        <v>190031025.58</v>
+      </c>
+      <c r="H65" t="n">
+        <v>81899096.16</v>
+      </c>
+      <c r="I65" t="n">
+        <v>82305865.81</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -2754,34 +2509,31 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>SEAPA</t>
+          <t>PMMG</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1231</v>
+        <v>1251</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE AGRICULTURA, PECUARIA E ABASTECIMENTO - SEAPA</t>
+          <t>POLICIA MILITAR DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>157335344.34</v>
+        <v>492130968.22</v>
       </c>
       <c r="F66" t="n">
-        <v>140995120.89</v>
+        <v>308691131.81</v>
       </c>
       <c r="G66" t="n">
-        <v>122957383.2</v>
+        <v>277874206.43</v>
       </c>
       <c r="H66" t="n">
-        <v>7823519.95</v>
+        <v>233612807.42</v>
       </c>
       <c r="I66" t="n">
-        <v>3775929.39</v>
-      </c>
-      <c r="J66" t="n">
-        <v>11599449.34</v>
+        <v>262569340.9</v>
       </c>
     </row>
     <row r="67">
@@ -2790,35 +2542,28 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>SEC. GERAL</t>
+          <t>SCC</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1631</v>
+        <v>1721</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>SECRETARIA-GERAL</t>
+          <t>SECRETARIA DE ESTADO DA CASA CIVIL</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>64901564.21</v>
+        <v>812801.22</v>
       </c>
       <c r="F67" t="n">
-        <v>59419458.57</v>
+        <v>517524.64</v>
       </c>
       <c r="G67" t="n">
-        <v>57509982.39</v>
-      </c>
-      <c r="H67" t="n">
-        <v>777.25</v>
-      </c>
-      <c r="I67" t="n">
-        <v>22162487.86</v>
-      </c>
-      <c r="J67" t="n">
-        <v>22163265.11</v>
-      </c>
+        <v>232284.7</v>
+      </c>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -2826,29 +2571,32 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>SECOM</t>
+          <t>SEAPA</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1711</v>
+        <v>1231</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE COMUNICACAO SOCIAL</t>
+          <t>SECRETARIA DE ESTADO DE AGRICULTURA, PECUARIA E ABASTECIMENTO - SEAPA</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>85247066.05</v>
+        <v>33295001.56</v>
       </c>
       <c r="F68" t="n">
-        <v>32467458.6</v>
+        <v>17060300.84</v>
       </c>
       <c r="G68" t="n">
-        <v>31192326.84</v>
-      </c>
-      <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
+        <v>15039673.84</v>
+      </c>
+      <c r="H68" t="n">
+        <v>3892020.4</v>
+      </c>
+      <c r="I68" t="n">
+        <v>11599449.34</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -2856,34 +2604,31 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>SECULT</t>
+          <t>SEC. GERAL</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1271</v>
+        <v>1631</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE CULTURA E TURISMO</t>
+          <t>SECRETARIA-GERAL</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>89313458.84</v>
+        <v>52732226.5</v>
       </c>
       <c r="F69" t="n">
-        <v>86513089.77</v>
+        <v>47250120.86</v>
       </c>
       <c r="G69" t="n">
-        <v>82380637.92</v>
+        <v>45310193.29</v>
       </c>
       <c r="H69" t="n">
-        <v>1333330.75</v>
+        <v>22393034.3</v>
       </c>
       <c r="I69" t="n">
-        <v>896505.38</v>
-      </c>
-      <c r="J69" t="n">
-        <v>2229836.13</v>
+        <v>22163265.11</v>
       </c>
     </row>
     <row r="70">
@@ -2892,35 +2637,28 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>SEDE</t>
+          <t>SECOM</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1221</v>
+        <v>1711</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONOMICO</t>
+          <t>SECRETARIA DE ESTADO DE COMUNICACAO SOCIAL</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>71019848</v>
+        <v>78816259.14</v>
       </c>
       <c r="F70" t="n">
-        <v>49587285.62</v>
+        <v>26036651.69</v>
       </c>
       <c r="G70" t="n">
-        <v>28903226.95</v>
-      </c>
-      <c r="H70" t="n">
-        <v>468159.26</v>
-      </c>
-      <c r="I70" t="n">
-        <v>8730755.23</v>
-      </c>
-      <c r="J70" t="n">
-        <v>9198914.49</v>
-      </c>
+        <v>24737770.32</v>
+      </c>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -2928,34 +2666,31 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>SEDESE</t>
+          <t>SECULT</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1481</v>
+        <v>1271</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL</t>
+          <t>SECRETARIA DE ESTADO DE CULTURA E TURISMO</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>278200685.86</v>
+        <v>16729709.42</v>
       </c>
       <c r="F71" t="n">
-        <v>258721057.71</v>
+        <v>13971161.93</v>
       </c>
       <c r="G71" t="n">
-        <v>187380767.61</v>
+        <v>12727787.31</v>
       </c>
       <c r="H71" t="n">
-        <v>13128483.79</v>
+        <v>924372.89</v>
       </c>
       <c r="I71" t="n">
-        <v>14858520.74</v>
-      </c>
-      <c r="J71" t="n">
-        <v>27987004.53</v>
+        <v>2229836.13</v>
       </c>
     </row>
     <row r="72">
@@ -2964,34 +2699,31 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>SEE</t>
+          <t>SEDE</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1261</v>
+        <v>1221</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE EDUCACAO</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONOMICO</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>17449007243.25</v>
+        <v>10870514</v>
       </c>
       <c r="F72" t="n">
-        <v>16913371691.71</v>
+        <v>5543251.1</v>
       </c>
       <c r="G72" t="n">
-        <v>16658293209.57</v>
+        <v>5269937.13</v>
       </c>
       <c r="H72" t="n">
-        <v>258732199.34</v>
+        <v>8800798.42</v>
       </c>
       <c r="I72" t="n">
-        <v>420280749.51</v>
-      </c>
-      <c r="J72" t="n">
-        <v>679012948.85</v>
+        <v>9198914.49</v>
       </c>
     </row>
     <row r="73">
@@ -3000,34 +2732,31 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>SEF</t>
+          <t>SEDESE</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1191</v>
+        <v>1481</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE FAZENDA</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1549832807.14</v>
+        <v>36950129.23</v>
       </c>
       <c r="F73" t="n">
-        <v>1487682339.64</v>
+        <v>19725876.63</v>
       </c>
       <c r="G73" t="n">
-        <v>1468478278.25</v>
+        <v>14166564.66</v>
       </c>
       <c r="H73" t="n">
-        <v>5469083</v>
+        <v>15102277.51</v>
       </c>
       <c r="I73" t="n">
-        <v>34680028.15</v>
-      </c>
-      <c r="J73" t="n">
-        <v>40149111.15</v>
+        <v>27987004.53</v>
       </c>
     </row>
     <row r="74">
@@ -3036,34 +2765,31 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>SEGOV</t>
+          <t>SEE</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>1491</v>
+        <v>1261</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE GOVERNO</t>
+          <t>SECRETARIA DE ESTADO DE EDUCACAO</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>614122774.96</v>
+        <v>1195468149.6</v>
       </c>
       <c r="F74" t="n">
-        <v>581433110.22</v>
+        <v>940226638.71</v>
       </c>
       <c r="G74" t="n">
-        <v>577033471.5</v>
+        <v>908110778.51</v>
       </c>
       <c r="H74" t="n">
-        <v>8649196.529999999</v>
+        <v>437854385.76</v>
       </c>
       <c r="I74" t="n">
-        <v>27927671.89</v>
-      </c>
-      <c r="J74" t="n">
-        <v>36576868.42</v>
+        <v>679012948.85</v>
       </c>
     </row>
     <row r="75">
@@ -3072,34 +2798,31 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>SEINFRA</t>
+          <t>SEF</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>1301</v>
+        <v>1191</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIAS</t>
+          <t>SECRETARIA DE ESTADO DE FAZENDA</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1210413287.27</v>
+        <v>221805187.87</v>
       </c>
       <c r="F75" t="n">
-        <v>948715257.75</v>
+        <v>165492398.6</v>
       </c>
       <c r="G75" t="n">
-        <v>820248138.33</v>
+        <v>146863725.11</v>
       </c>
       <c r="H75" t="n">
-        <v>79551005.90000001</v>
+        <v>35569421.6</v>
       </c>
       <c r="I75" t="n">
-        <v>47275927.88</v>
-      </c>
-      <c r="J75" t="n">
-        <v>126826933.78</v>
+        <v>40149111.15</v>
       </c>
     </row>
     <row r="76">
@@ -3108,34 +2831,31 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>SEJUSP</t>
+          <t>SEGOV</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>1451</v>
+        <v>1491</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE JUSTICA E SEGURANCA PUBLICA</t>
+          <t>SECRETARIA DE ESTADO DE GOVERNO</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>3781312622.12</v>
+        <v>26642634.36</v>
       </c>
       <c r="F76" t="n">
-        <v>3625298484.23</v>
+        <v>21120846.27</v>
       </c>
       <c r="G76" t="n">
-        <v>3596218710.39</v>
+        <v>18743084.11</v>
       </c>
       <c r="H76" t="n">
-        <v>19811807.26</v>
+        <v>28020339.85</v>
       </c>
       <c r="I76" t="n">
-        <v>100572066.62</v>
-      </c>
-      <c r="J76" t="n">
-        <v>120383873.88</v>
+        <v>36576868.42</v>
       </c>
     </row>
     <row r="77">
@@ -3144,34 +2864,31 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>SEMAD</t>
+          <t>SEINFRA</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1371</v>
+        <v>1301</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTAVEL</t>
+          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIAS</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>208856328.28</v>
+        <v>606296434.1799999</v>
       </c>
       <c r="F77" t="n">
-        <v>202130317.06</v>
+        <v>498520717.55</v>
       </c>
       <c r="G77" t="n">
-        <v>183745409.62</v>
+        <v>491967397.68</v>
       </c>
       <c r="H77" t="n">
-        <v>3452019.16</v>
+        <v>47789818.31</v>
       </c>
       <c r="I77" t="n">
-        <v>2453491.44</v>
-      </c>
-      <c r="J77" t="n">
-        <v>5905510.6</v>
+        <v>126826933.78</v>
       </c>
     </row>
     <row r="78">
@@ -3180,34 +2897,31 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>SEPLAG</t>
+          <t>SEJUSP</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1501</v>
+        <v>1451</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTAO</t>
+          <t>SECRETARIA DE ESTADO DE JUSTICA E SEGURANCA PUBLICA</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>558633697.6799999</v>
+        <v>702675173.38</v>
       </c>
       <c r="F78" t="n">
-        <v>499616023.57</v>
+        <v>559518450.85</v>
       </c>
       <c r="G78" t="n">
-        <v>469179324</v>
+        <v>535616107.6</v>
       </c>
       <c r="H78" t="n">
-        <v>3809874.58</v>
+        <v>104228871.59</v>
       </c>
       <c r="I78" t="n">
-        <v>18299317.45</v>
-      </c>
-      <c r="J78" t="n">
-        <v>22109192.03</v>
+        <v>120383873.88</v>
       </c>
     </row>
     <row r="79">
@@ -3216,34 +2930,31 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>TCEMG</t>
+          <t>SEMAD</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>1021</v>
+        <v>1371</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>TRIBUNAL DE CONTAS DO ESTADO DE MINAS GERAIS</t>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTAVEL</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1031554980.46</v>
+        <v>38922252.59</v>
       </c>
       <c r="F79" t="n">
-        <v>1011187631.34</v>
+        <v>32257018.32</v>
       </c>
       <c r="G79" t="n">
-        <v>1000081162.41</v>
+        <v>28940807.16</v>
       </c>
       <c r="H79" t="n">
-        <v>2349.38</v>
+        <v>2573565.18</v>
       </c>
       <c r="I79" t="n">
-        <v>13089699.04</v>
-      </c>
-      <c r="J79" t="n">
-        <v>13092048.42</v>
+        <v>5905510.6</v>
       </c>
     </row>
     <row r="80">
@@ -3252,29 +2963,32 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>TJMG</t>
+          <t>SEPLAG</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>1031</v>
+        <v>1501</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>TRIBUNAL DE JUSTICA DO ESTADO DE MINAS GERAIS</t>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTAO</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>8552007441.49</v>
+        <v>275494600.64</v>
       </c>
       <c r="F80" t="n">
-        <v>8552007441.49</v>
+        <v>218926765.88</v>
       </c>
       <c r="G80" t="n">
-        <v>8552432135.36</v>
-      </c>
-      <c r="H80" t="inlineStr"/>
-      <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
+        <v>193572592.87</v>
+      </c>
+      <c r="H80" t="n">
+        <v>18931152.42</v>
+      </c>
+      <c r="I80" t="n">
+        <v>22109192.03</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -3282,34 +2996,31 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>TJMMG</t>
+          <t>TCEMG</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1051</v>
+        <v>1021</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>TRIBUNAL DE JUSTICA MILITAR DO ESTADO DE MINAS GERAIS</t>
+          <t>TRIBUNAL DE CONTAS DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>105322332.72</v>
+        <v>105320744.15</v>
       </c>
       <c r="F81" t="n">
-        <v>100216812.04</v>
+        <v>85085345.03</v>
       </c>
       <c r="G81" t="n">
-        <v>99085341.56999999</v>
+        <v>72704365.86</v>
       </c>
       <c r="H81" t="n">
-        <v>103192.45</v>
+        <v>14044359.35</v>
       </c>
       <c r="I81" t="n">
-        <v>3844435.05</v>
-      </c>
-      <c r="J81" t="n">
-        <v>3947627.5</v>
+        <v>13092048.42</v>
       </c>
     </row>
     <row r="82">
@@ -3318,34 +3029,31 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>TV MINAS</t>
+          <t>TJMMG</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>2211</v>
+        <v>1051</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>FUNDACAO TV MINAS CULTURAL E EDUCATIVA</t>
+          <t>TRIBUNAL DE JUSTICA MILITAR DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>16156823.34</v>
+        <v>12254712.24</v>
       </c>
       <c r="F82" t="n">
-        <v>15396119.26</v>
+        <v>7319035.15</v>
       </c>
       <c r="G82" t="n">
-        <v>14519942.39</v>
+        <v>6264719.05</v>
       </c>
       <c r="H82" t="n">
-        <v>113058.43</v>
+        <v>3930391.56</v>
       </c>
       <c r="I82" t="n">
-        <v>599716.37</v>
-      </c>
-      <c r="J82" t="n">
-        <v>712774.8</v>
+        <v>3947627.5</v>
       </c>
     </row>
     <row r="83">
@@ -3354,34 +3062,31 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>UEMG</t>
+          <t>TV MINAS</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>2351</v>
+        <v>2211</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>UNIVERSIDADE DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDACAO TV MINAS CULTURAL E EDUCATIVA</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>404521667.47</v>
+        <v>6399973.22</v>
       </c>
       <c r="F83" t="n">
-        <v>384928295.57</v>
+        <v>5707786.34</v>
       </c>
       <c r="G83" t="n">
-        <v>374712336.29</v>
+        <v>4841793.87</v>
       </c>
       <c r="H83" t="n">
-        <v>6005270.76</v>
+        <v>629830.1</v>
       </c>
       <c r="I83" t="n">
-        <v>21210103.71</v>
-      </c>
-      <c r="J83" t="n">
-        <v>27215374.47</v>
+        <v>712774.8</v>
       </c>
     </row>
     <row r="84">
@@ -3390,34 +3095,31 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>UNIMONTES</t>
+          <t>UEMG</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>2311</v>
+        <v>2351</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>UNIVERSIDADE ESTADUAL DE MONTES CLAROS</t>
+          <t>UNIVERSIDADE DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>469927618.13</v>
+        <v>105976826.33</v>
       </c>
       <c r="F84" t="n">
-        <v>414313756.03</v>
+        <v>88195935.75</v>
       </c>
       <c r="G84" t="n">
-        <v>405713436.11</v>
+        <v>78262250.3</v>
       </c>
       <c r="H84" t="n">
-        <v>1205407.47</v>
+        <v>21647912.36</v>
       </c>
       <c r="I84" t="n">
-        <v>16962260.8</v>
-      </c>
-      <c r="J84" t="n">
-        <v>18167668.27</v>
+        <v>27215374.47</v>
       </c>
     </row>
     <row r="85">
@@ -3426,33 +3128,63 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
+          <t>UNIMONTES</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>2311</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>UNIVERSIDADE ESTADUAL DE MONTES CLAROS</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>104907358.44</v>
+      </c>
+      <c r="F85" t="n">
+        <v>54255664.76</v>
+      </c>
+      <c r="G85" t="n">
+        <v>48878511.34</v>
+      </c>
+      <c r="H85" t="n">
+        <v>18038044.58</v>
+      </c>
+      <c r="I85" t="n">
+        <v>18167668.27</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
           <t>UTRAMIG</t>
         </is>
       </c>
-      <c r="C85" t="n">
+      <c r="C86" t="n">
         <v>2281</v>
       </c>
-      <c r="D85" t="inlineStr">
+      <c r="D86" t="inlineStr">
         <is>
           <t>FUNDACAO DE EDUCACAO PARA O TRABALHO DE MINAS GERAIS</t>
         </is>
       </c>
-      <c r="E85" t="n">
-        <v>6125588.94</v>
-      </c>
-      <c r="F85" t="n">
-        <v>5821567.34</v>
-      </c>
-      <c r="G85" t="n">
-        <v>5483571.33</v>
-      </c>
-      <c r="H85" t="n">
-        <v>24344.67</v>
-      </c>
-      <c r="I85" t="n">
-        <v>193381.66</v>
-      </c>
-      <c r="J85" t="n">
+      <c r="E86" t="n">
+        <v>2916733.21</v>
+      </c>
+      <c r="F86" t="n">
+        <v>2626430.56</v>
+      </c>
+      <c r="G86" t="n">
+        <v>2349108.12</v>
+      </c>
+      <c r="H86" t="n">
+        <v>214521.73</v>
+      </c>
+      <c r="I86" t="n">
         <v>217726.33</v>
       </c>
     </row>
